--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="AL64" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="65">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="AL65" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="66">
@@ -9081,27 +9081,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="AL66" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="67">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9250,17 +9250,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="AL67" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="68">
@@ -9345,27 +9345,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="AL68" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="69">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="AL69" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="70">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="AL70" s="3" t="n">
-        <v>45871.41666666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="71">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="M91" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>1.64</v>
+        <v>4.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC91" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N97" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="M98" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="M99" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N99" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.11</v>
+        <v>2.41</v>
       </c>
       <c r="M100" t="n">
         <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.47916666666</v>
       </c>
     </row>
     <row r="102">
@@ -13833,27 +13833,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="103">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="104">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="105">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="AL105" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="106">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="AL106" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="107">
@@ -14493,12 +14493,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="M107" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AC107" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14616,7 +14616,7 @@
         </is>
       </c>
       <c r="AL107" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="108">
@@ -14625,27 +14625,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="AL108" s="3" t="n">
-        <v>45871.47916666666</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="109">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16209,12 +16209,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16332,7 +16332,7 @@
         </is>
       </c>
       <c r="AL120" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="121">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="M121" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="AL121" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="122">
@@ -16473,27 +16473,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16596,7 +16596,7 @@
         </is>
       </c>
       <c r="AL122" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="123">
@@ -16605,27 +16605,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N123" t="n">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="AL123" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="124">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="AL124" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="125">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16992,7 +16992,7 @@
         </is>
       </c>
       <c r="AL125" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.53125</v>
       </c>
     </row>
     <row r="126">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="AL126" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="127">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="AL127" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="128">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="M128" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N128" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17354,10 +17354,10 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="129">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="AL129" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="130">
@@ -17529,27 +17529,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="AL130" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="131">
@@ -17661,27 +17661,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17784,7 +17784,7 @@
         </is>
       </c>
       <c r="AL131" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="132">
@@ -17793,12 +17793,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="AL132" s="3" t="n">
-        <v>45871.53125</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="133">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18321,12 +18321,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="AL136" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.55208333334</v>
       </c>
     </row>
     <row r="137">
@@ -18453,27 +18453,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="AL137" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="138">
@@ -18585,27 +18585,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="AL138" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="139">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18812,10 +18812,10 @@
         <v>0</v>
       </c>
       <c r="AD139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF139" t="n">
         <v>0</v>
@@ -18840,7 +18840,7 @@
         </is>
       </c>
       <c r="AL139" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="140">
@@ -18849,27 +18849,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18972,7 +18972,7 @@
         </is>
       </c>
       <c r="AL140" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.58333333334</v>
       </c>
     </row>
     <row r="141">
@@ -18981,27 +18981,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>3.47</v>
+        <v>1.88</v>
       </c>
       <c r="M141" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N141" t="n">
-        <v>1.82</v>
+        <v>3.94</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,16 +19070,16 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE141" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF141" t="n">
         <v>0</v>
@@ -19104,7 +19104,7 @@
         </is>
       </c>
       <c r="AL141" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="142">
@@ -19113,12 +19113,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19208,10 +19208,10 @@
         <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF142" t="n">
         <v>0</v>
@@ -19236,7 +19236,7 @@
         </is>
       </c>
       <c r="AL142" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="143">
@@ -19245,12 +19245,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.68</v>
+        <v>5.75</v>
       </c>
       <c r="M143" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N143" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,16 +19334,16 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="AL143" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="144">
@@ -19377,27 +19377,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="AL144" s="3" t="n">
-        <v>45871.55208333334</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="145">
@@ -19509,27 +19509,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19632,7 +19632,7 @@
         </is>
       </c>
       <c r="AL145" s="3" t="n">
-        <v>45871.5625</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="146">
@@ -19641,27 +19641,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19764,7 +19764,7 @@
         </is>
       </c>
       <c r="AL146" s="3" t="n">
-        <v>45871.5625</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="147">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19868,10 +19868,10 @@
         <v>0</v>
       </c>
       <c r="AD147" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF147" t="n">
         <v>0</v>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="AL147" s="3" t="n">
-        <v>45871.5625</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="148">
@@ -19905,27 +19905,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="AL148" s="3" t="n">
-        <v>45871.58333333334</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="149">
@@ -20037,12 +20037,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
         <v>0</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AL149" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="150">
@@ -20169,27 +20169,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="AL150" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="151">
@@ -20301,12 +20301,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20424,7 +20424,7 @@
         </is>
       </c>
       <c r="AL151" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="152">
@@ -20433,12 +20433,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20474,13 +20474,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20528,10 +20528,10 @@
         <v>0</v>
       </c>
       <c r="AD152" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
         <v>0</v>
@@ -20556,7 +20556,7 @@
         </is>
       </c>
       <c r="AL152" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="153">
@@ -20565,12 +20565,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20660,10 +20660,10 @@
         <v>0</v>
       </c>
       <c r="AD153" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
         <v>0</v>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="AL153" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="154">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21584,10 +21584,10 @@
         <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF160" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M163" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N163" t="n">
-        <v>7.2</v>
+        <v>2.41</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,16 +21974,16 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD163" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF163" t="n">
         <v>0</v>
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25277,7 +25277,7 @@
         <v>2.2</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC204" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>1.64</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,22 +8954,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>1.64</v>
+        <v>3.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N74" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,58 +10442,58 @@
         </is>
       </c>
       <c r="L76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC76" t="n">
         <v>1.67</v>
-      </c>
-      <c r="M76" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1.57</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC78" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>1.83</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N80" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="M87" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N88" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="M93" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,22 +13046,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>3.35</v>
+        <v>2.65</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="M100" t="n">
         <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AC100" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N121" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17354,10 +17354,10 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17930,22 +17930,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18458,22 +18458,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18548,10 +18548,10 @@
         <v>0</v>
       </c>
       <c r="AD137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF137" t="n">
         <v>0</v>
@@ -18722,22 +18722,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18812,10 +18812,10 @@
         <v>0</v>
       </c>
       <c r="AD139" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
         <v>0</v>
@@ -19250,22 +19250,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19340,10 +19340,10 @@
         <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19382,22 +19382,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19472,10 +19472,10 @@
         <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF144" t="n">
         <v>0</v>
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.34</v>
+        <v>3.85</v>
       </c>
       <c r="M160" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="N160" t="n">
-        <v>7.2</v>
+        <v>1.95</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,16 +21578,16 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD160" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M163" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N163" t="n">
-        <v>2.41</v>
+        <v>7.2</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,16 +21974,16 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF163" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27338,13 +27338,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -27386,10 +27386,10 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,22 +8822,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="M71" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10049,10 +10049,10 @@
         <v>1.87</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N73" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N76" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC77" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>1.7</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.03</v>
+        <v>5</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N78" t="n">
-        <v>3.35</v>
+        <v>1.64</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,58 +10838,58 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
         <v>2.1</v>
       </c>
-      <c r="M79" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC79" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.81</v>
+        <v>2.41</v>
       </c>
       <c r="M80" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="M86" t="n">
         <v>3.5</v>
       </c>
       <c r="N86" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="M88" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="M94" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.71</v>
+        <v>2.11</v>
       </c>
       <c r="M95" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC95" t="n">
         <v>1.95</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="M100" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N100" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,58 +14138,58 @@
         </is>
       </c>
       <c r="L104" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M104" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC104" t="n">
         <v>1.8</v>
-      </c>
-      <c r="M104" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N104" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>2.34</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="M113" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N113" t="n">
-        <v>4.01</v>
+        <v>5.2</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,22 +17270,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18062,22 +18062,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18458,22 +18458,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18548,10 +18548,10 @@
         <v>0</v>
       </c>
       <c r="AD137" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
         <v>0</v>
@@ -18590,22 +18590,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18680,10 +18680,10 @@
         <v>0</v>
       </c>
       <c r="AD138" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -19250,22 +19250,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19340,10 +19340,10 @@
         <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19382,22 +19382,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19472,10 +19472,10 @@
         <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="n">
         <v>0</v>
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="M160" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N160" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC160" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>1.7</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M162" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N162" t="n">
-        <v>2.41</v>
+        <v>7.2</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,16 +21842,16 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF162" t="n">
         <v>0</v>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21980,10 +21980,10 @@
         <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF163" t="n">
         <v>0</v>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC169" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22814,22 +22814,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC187" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G208" t="n">

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL210"/>
+  <dimension ref="A1:AL214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4424,10 +4424,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
         <v>2.8</v>
@@ -4952,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>5.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5348,10 +5348,10 @@
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>9</v>
+        <v>2.42</v>
       </c>
       <c r="M56" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N56" t="n">
-        <v>1.28</v>
+        <v>2.32</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="AL64" s="3" t="n">
-        <v>45871.45833333334</v>
+        <v>45871.41666666666</v>
       </c>
     </row>
     <row r="65">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.87</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>3.7</v>
+        <v>1.64</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="M76" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N77" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>5</v>
+        <v>1.69</v>
       </c>
       <c r="M78" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>1.64</v>
+        <v>4.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="M80" t="n">
         <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC80" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N89" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N92" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
         <v>4.5</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13001,7 +13001,7 @@
         <v>1.8</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N96" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="M100" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45871.47916666666</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="102">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.45833333334</v>
       </c>
     </row>
     <row r="103">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.47916666666</v>
       </c>
     </row>
     <row r="104">
@@ -14097,27 +14097,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45871.5</v>
+        <v>45871.47916666666</v>
       </c>
     </row>
     <row r="105">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,58 +14534,58 @@
         </is>
       </c>
       <c r="L107" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC107" t="n">
         <v>1.8</v>
-      </c>
-      <c r="M107" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N107" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>2.34</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16209,27 +16209,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16332,7 +16332,7 @@
         </is>
       </c>
       <c r="AL120" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="121">
@@ -16341,27 +16341,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="AL121" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="122">
@@ -16473,27 +16473,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16596,7 +16596,7 @@
         </is>
       </c>
       <c r="AL122" s="3" t="n">
-        <v>45871.52083333334</v>
+        <v>45871.5</v>
       </c>
     </row>
     <row r="123">
@@ -16610,22 +16610,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -16992,7 +16992,7 @@
         </is>
       </c>
       <c r="AL125" s="3" t="n">
-        <v>45871.53125</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="126">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="AL126" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="127">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="AL127" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.52083333334</v>
       </c>
     </row>
     <row r="128">
@@ -17265,27 +17265,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45871.54166666666</v>
+        <v>45871.53125</v>
       </c>
     </row>
     <row r="129">
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17930,22 +17930,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18321,12 +18321,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="AL136" s="3" t="n">
-        <v>45871.55208333334</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="137">
@@ -18453,27 +18453,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="AL137" s="3" t="n">
-        <v>45871.5625</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="138">
@@ -18585,27 +18585,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>7.8</v>
+        <v>3.47</v>
       </c>
       <c r="M138" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="N138" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,16 +18674,16 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC138" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD138" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
         <v>0</v>
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="AL138" s="3" t="n">
-        <v>45871.5625</v>
+        <v>45871.54166666666</v>
       </c>
     </row>
     <row r="139">
@@ -18717,27 +18717,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18840,7 +18840,7 @@
         </is>
       </c>
       <c r="AL139" s="3" t="n">
-        <v>45871.5625</v>
+        <v>45871.55208333334</v>
       </c>
     </row>
     <row r="140">
@@ -18849,12 +18849,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Arsenal Dzyarzhynsk</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18972,7 +18972,7 @@
         </is>
       </c>
       <c r="AL140" s="3" t="n">
-        <v>45871.58333333334</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="141">
@@ -18981,12 +18981,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="M141" t="n">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="N141" t="n">
-        <v>3.94</v>
+        <v>1.36</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,16 +19070,16 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC141" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD141" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF141" t="n">
         <v>0</v>
@@ -19104,7 +19104,7 @@
         </is>
       </c>
       <c r="AL141" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="142">
@@ -19113,27 +19113,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19208,10 +19208,10 @@
         <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
         <v>0</v>
@@ -19236,7 +19236,7 @@
         </is>
       </c>
       <c r="AL142" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="143">
@@ -19245,12 +19245,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19340,10 +19340,10 @@
         <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="AL143" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.5625</v>
       </c>
     </row>
     <row r="144">
@@ -19377,12 +19377,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Arsenal Dzyarzhynsk</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="AL144" s="3" t="n">
-        <v>45871.60416666666</v>
+        <v>45871.58333333334</v>
       </c>
     </row>
     <row r="145">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19604,10 +19604,10 @@
         <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF145" t="n">
         <v>0</v>
@@ -19641,12 +19641,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19682,13 +19682,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19736,10 +19736,10 @@
         <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF146" t="n">
         <v>0</v>
@@ -19764,7 +19764,7 @@
         </is>
       </c>
       <c r="AL146" s="3" t="n">
-        <v>45871.625</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="147">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="AL147" s="3" t="n">
-        <v>45871.625</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="148">
@@ -19905,27 +19905,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="AL148" s="3" t="n">
-        <v>45871.625</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="149">
@@ -20037,12 +20037,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20074,17 +20074,17 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,16 +20126,16 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD149" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE149" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF149" t="n">
         <v>0</v>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AL149" s="3" t="n">
-        <v>45871.625</v>
+        <v>45871.60416666666</v>
       </c>
     </row>
     <row r="150">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20961,12 +20961,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="AL156" s="3" t="n">
-        <v>45871.63541666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="157">
@@ -21093,12 +21093,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21216,7 +21216,7 @@
         </is>
       </c>
       <c r="AL157" s="3" t="n">
-        <v>45871.63541666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="158">
@@ -21225,12 +21225,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21348,7 +21348,7 @@
         </is>
       </c>
       <c r="AL158" s="3" t="n">
-        <v>45871.63541666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="159">
@@ -21357,12 +21357,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="AL159" s="3" t="n">
-        <v>45871.63541666666</v>
+        <v>45871.625</v>
       </c>
     </row>
     <row r="160">
@@ -21489,12 +21489,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="M160" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N160" t="n">
-        <v>2.41</v>
+        <v>4.8</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="AL160" s="3" t="n">
-        <v>45871.64583333334</v>
+        <v>45871.63541666666</v>
       </c>
     </row>
     <row r="161">
@@ -21621,12 +21621,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="AL161" s="3" t="n">
-        <v>45871.64583333334</v>
+        <v>45871.63541666666</v>
       </c>
     </row>
     <row r="162">
@@ -21753,12 +21753,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21848,10 +21848,10 @@
         <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
         <v>0</v>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="AL162" s="3" t="n">
-        <v>45871.64583333334</v>
+        <v>45871.63541666666</v>
       </c>
     </row>
     <row r="163">
@@ -21885,12 +21885,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22008,7 +22008,7 @@
         </is>
       </c>
       <c r="AL163" s="3" t="n">
-        <v>45871.64583333334</v>
+        <v>45871.63541666666</v>
       </c>
     </row>
     <row r="164">
@@ -22017,27 +22017,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22140,7 +22140,7 @@
         </is>
       </c>
       <c r="AL164" s="3" t="n">
-        <v>45871.65625</v>
+        <v>45871.64583333334</v>
       </c>
     </row>
     <row r="165">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,10 +22238,10 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD165" t="n">
         <v>0</v>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="AL165" s="3" t="n">
-        <v>45871.65625</v>
+        <v>45871.64583333334</v>
       </c>
     </row>
     <row r="166">
@@ -22281,27 +22281,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         </is>
       </c>
       <c r="AL166" s="3" t="n">
-        <v>45871.66666666666</v>
+        <v>45871.64583333334</v>
       </c>
     </row>
     <row r="167">
@@ -22413,27 +22413,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22508,10 +22508,10 @@
         <v>0</v>
       </c>
       <c r="AD167" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF167" t="n">
         <v>0</v>
@@ -22536,7 +22536,7 @@
         </is>
       </c>
       <c r="AL167" s="3" t="n">
-        <v>45871.66666666666</v>
+        <v>45871.64583333334</v>
       </c>
     </row>
     <row r="168">
@@ -22545,27 +22545,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="AL168" s="3" t="n">
-        <v>45871.66666666666</v>
+        <v>45871.65625</v>
       </c>
     </row>
     <row r="169">
@@ -22677,12 +22677,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         </is>
       </c>
       <c r="AL169" s="3" t="n">
-        <v>45871.66666666666</v>
+        <v>45871.65625</v>
       </c>
     </row>
     <row r="170">
@@ -22941,12 +22941,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="AL171" s="3" t="n">
-        <v>45871.70833333334</v>
+        <v>45871.66666666666</v>
       </c>
     </row>
     <row r="172">
@@ -23073,12 +23073,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23196,7 +23196,7 @@
         </is>
       </c>
       <c r="AL172" s="3" t="n">
-        <v>45871.70833333334</v>
+        <v>45871.66666666666</v>
       </c>
     </row>
     <row r="173">
@@ -23205,12 +23205,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AL173" s="3" t="n">
-        <v>45871.70833333334</v>
+        <v>45871.66666666666</v>
       </c>
     </row>
     <row r="174">
@@ -23337,12 +23337,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="AL174" s="3" t="n">
-        <v>45871.70833333334</v>
+        <v>45871.66666666666</v>
       </c>
     </row>
     <row r="175">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24921,12 +24921,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="AL186" s="3" t="n">
-        <v>45871.75</v>
+        <v>45871.70833333334</v>
       </c>
     </row>
     <row r="187">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="AL187" s="3" t="n">
-        <v>45871.77083333334</v>
+        <v>45871.70833333334</v>
       </c>
     </row>
     <row r="188">
@@ -25185,12 +25185,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25308,7 +25308,7 @@
         </is>
       </c>
       <c r="AL188" s="3" t="n">
-        <v>45871.77083333334</v>
+        <v>45871.70833333334</v>
       </c>
     </row>
     <row r="189">
@@ -25317,12 +25317,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="AL189" s="3" t="n">
-        <v>45871.77083333334</v>
+        <v>45871.70833333334</v>
       </c>
     </row>
     <row r="190">
@@ -25449,12 +25449,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="AL190" s="3" t="n">
-        <v>45871.79166666666</v>
+        <v>45871.75</v>
       </c>
     </row>
     <row r="191">
@@ -25581,12 +25581,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25704,7 +25704,7 @@
         </is>
       </c>
       <c r="AL191" s="3" t="n">
-        <v>45871.79166666666</v>
+        <v>45871.77083333334</v>
       </c>
     </row>
     <row r="192">
@@ -25713,12 +25713,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="AL192" s="3" t="n">
-        <v>45871.79166666666</v>
+        <v>45871.77083333334</v>
       </c>
     </row>
     <row r="193">
@@ -25845,12 +25845,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,10 +25934,10 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC193" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD193" t="n">
         <v>0</v>
@@ -25968,7 +25968,7 @@
         </is>
       </c>
       <c r="AL193" s="3" t="n">
-        <v>45871.79166666666</v>
+        <v>45871.77083333334</v>
       </c>
     </row>
     <row r="194">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26241,12 +26241,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="AL196" s="3" t="n">
-        <v>45871.83333333334</v>
+        <v>45871.79166666666</v>
       </c>
     </row>
     <row r="197">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="AL197" s="3" t="n">
-        <v>45871.83333333334</v>
+        <v>45871.79166666666</v>
       </c>
     </row>
     <row r="198">
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="AL198" s="3" t="n">
-        <v>45871.83333333334</v>
+        <v>45871.79166666666</v>
       </c>
     </row>
     <row r="199">
@@ -26637,12 +26637,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26760,7 +26760,7 @@
         </is>
       </c>
       <c r="AL199" s="3" t="n">
-        <v>45871.83333333334</v>
+        <v>45871.79166666666</v>
       </c>
     </row>
     <row r="200">
@@ -26769,12 +26769,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="AL200" s="3" t="n">
-        <v>45871.85416666666</v>
+        <v>45871.83333333334</v>
       </c>
     </row>
     <row r="201">
@@ -26901,12 +26901,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="AL201" s="3" t="n">
-        <v>45871.85416666666</v>
+        <v>45871.83333333334</v>
       </c>
     </row>
     <row r="202">
@@ -27033,12 +27033,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27156,7 +27156,7 @@
         </is>
       </c>
       <c r="AL202" s="3" t="n">
-        <v>45871.85416666666</v>
+        <v>45871.83333333334</v>
       </c>
     </row>
     <row r="203">
@@ -27165,12 +27165,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="AL203" s="3" t="n">
-        <v>45871.875</v>
+        <v>45871.83333333334</v>
       </c>
     </row>
     <row r="204">
@@ -27297,12 +27297,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="AL204" s="3" t="n">
-        <v>45871.875</v>
+        <v>45871.85416666666</v>
       </c>
     </row>
     <row r="205">
@@ -27429,12 +27429,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27552,7 +27552,7 @@
         </is>
       </c>
       <c r="AL205" s="3" t="n">
-        <v>45871.875</v>
+        <v>45871.85416666666</v>
       </c>
     </row>
     <row r="206">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27684,7 +27684,7 @@
         </is>
       </c>
       <c r="AL206" s="3" t="n">
-        <v>45871.90625</v>
+        <v>45871.85416666666</v>
       </c>
     </row>
     <row r="207">
@@ -27693,7 +27693,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="AL207" s="3" t="n">
-        <v>45871.91666666666</v>
+        <v>45871.875</v>
       </c>
     </row>
     <row r="208">
@@ -27825,12 +27825,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27914,10 +27914,10 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC208" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD208" t="n">
         <v>0</v>
@@ -27948,7 +27948,7 @@
         </is>
       </c>
       <c r="AL208" s="3" t="n">
-        <v>45871.91666666666</v>
+        <v>45871.875</v>
       </c>
     </row>
     <row r="209">
@@ -27957,12 +27957,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="AL209" s="3" t="n">
-        <v>45871.95833333334</v>
+        <v>45871.875</v>
       </c>
     </row>
     <row r="210">
@@ -28089,129 +28089,657 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" t="n">
+        <v>0</v>
+      </c>
+      <c r="W210" t="n">
+        <v>0</v>
+      </c>
+      <c r="X210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL210" s="3" t="n">
+        <v>45871.90625</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL211" s="3" t="n">
+        <v>45871.91666666666</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL212" s="3" t="n">
+        <v>45871.91666666666</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0</v>
+      </c>
+      <c r="V213" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" t="n">
+        <v>0</v>
+      </c>
+      <c r="X213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL213" s="3" t="n">
+        <v>45871.95833333334</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Birmingham Legion</t>
         </is>
       </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" t="n">
-        <v>0</v>
-      </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="inlineStr">
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0</v>
-      </c>
-      <c r="T210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="n">
-        <v>0</v>
-      </c>
-      <c r="V210" t="n">
-        <v>0</v>
-      </c>
-      <c r="W210" t="n">
-        <v>0</v>
-      </c>
-      <c r="X210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL210" s="3" t="n">
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" t="n">
+        <v>0</v>
+      </c>
+      <c r="W214" t="n">
+        <v>0</v>
+      </c>
+      <c r="X214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL214" s="3" t="n">
         <v>45871.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.53</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.01</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3185,10 +3185,10 @@
         <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N31" t="n">
         <v>2.65</v>
@@ -4550,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5348,10 +5348,10 @@
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>9</v>
+        <v>2.42</v>
       </c>
       <c r="M55" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>1.28</v>
+        <v>2.32</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="M56" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="N56" t="n">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC68" t="n">
         <v>2</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>1.75</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>5</v>
+        <v>2.21</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>1.64</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC77" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>1.7</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC80" t="n">
         <v>1.95</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="M84" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.71</v>
+        <v>2.11</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>1.95</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N101" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,22 +17930,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18062,22 +18062,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,22 +18194,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,22 +18326,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="M136" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N136" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AC136" t="n">
-        <v>2.22</v>
+        <v>1.88</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18590,22 +18590,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -19118,22 +19118,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,22 +19250,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.88</v>
+        <v>6.8</v>
       </c>
       <c r="M145" t="n">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="N145" t="n">
-        <v>3.94</v>
+        <v>1.35</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19598,16 +19598,16 @@
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD145" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF145" t="n">
         <v>0</v>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>6.8</v>
+        <v>1.88</v>
       </c>
       <c r="M149" t="n">
-        <v>5.2</v>
+        <v>3.74</v>
       </c>
       <c r="N149" t="n">
-        <v>1.35</v>
+        <v>3.94</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,16 +20126,16 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22106,10 +22106,10 @@
         <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC164" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD164" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>3.85</v>
+        <v>1.34</v>
       </c>
       <c r="M166" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="N166" t="n">
-        <v>1.95</v>
+        <v>7.2</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,16 +22370,16 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF166" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22508,10 +22508,10 @@
         <v>0</v>
       </c>
       <c r="AD167" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
         <v>0</v>
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22814,22 +22814,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22982,13 +22982,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -23030,10 +23030,10 @@
         <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC171" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD171" t="n">
         <v>0</v>
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G212" t="n">

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.15</v>
+        <v>2.01</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.46</v>
+        <v>3.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>2.08</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2921,10 +2921,10 @@
         <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
         <v>2.65</v>
@@ -4550,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,64 +5030,64 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.25</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,22 +8954,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="M68" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M75" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC75" t="n">
         <v>1.91</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>1.64</v>
+        <v>3.9</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N81" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N92" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M93" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12737,7 +12737,7 @@
         <v>2</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N96" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M97" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N97" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC97" t="n">
         <v>1.85</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,58 +13346,58 @@
         </is>
       </c>
       <c r="L98" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC98" t="n">
         <v>1.67</v>
-      </c>
-      <c r="M98" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N98" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" t="n">
-        <v>0</v>
-      </c>
-      <c r="X98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC98" t="n">
-        <v>1.57</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="M101" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,22 +15818,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18326,22 +18326,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
       <c r="M145" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="N145" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19598,16 +19598,16 @@
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF145" t="n">
         <v>0</v>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19682,13 +19682,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
       <c r="M146" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="N146" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19730,16 +19730,16 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC146" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD146" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF146" t="n">
         <v>0</v>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19868,10 +19868,10 @@
         <v>0</v>
       </c>
       <c r="AD147" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE147" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF147" t="n">
         <v>0</v>
@@ -19910,22 +19910,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M165" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N165" t="n">
-        <v>2.41</v>
+        <v>7.2</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,16 +22238,16 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD165" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE165" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF165" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="M166" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="N166" t="n">
-        <v>7.2</v>
+        <v>2.41</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,16 +22370,16 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD166" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF166" t="n">
         <v>0</v>
@@ -22946,22 +22946,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22982,13 +22982,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -23030,10 +23030,10 @@
         <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD171" t="n">
         <v>0</v>
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD174" t="n">
         <v>0</v>
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25802,10 +25802,10 @@
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC192" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD192" t="n">
         <v>0</v>
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,10 +25934,10 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC193" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD193" t="n">
         <v>0</v>
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27782,10 +27782,10 @@
         <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC207" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD207" t="n">
         <v>0</v>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27914,10 +27914,10 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD208" t="n">
         <v>0</v>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G212" t="n">

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,14 +1070,14 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.25</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.15</v>
+        <v>1.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>2.02</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>1.53</v>
+        <v>2.11</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.02</v>
+        <v>5.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
         <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="M72" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N74" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10577,10 +10577,10 @@
         <v>1.87</v>
       </c>
       <c r="M77" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N77" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.71</v>
+        <v>5</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N80" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>1.71</v>
       </c>
       <c r="M83" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>1.64</v>
+        <v>4.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N102" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,22 +15422,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="M114" t="n">
         <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>4.01</v>
+        <v>2.82</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,22 +17798,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>6.2</v>
+        <v>3.47</v>
       </c>
       <c r="M132" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="N132" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC132" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,22 +17930,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,22 +18062,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="M134" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N134" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,22 +18194,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="M135" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="N135" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AC135" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,22 +18458,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18986,22 +18986,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,16 +19070,16 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF141" t="n">
         <v>0</v>
@@ -19250,22 +19250,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,16 +19334,16 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19514,22 +19514,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19604,10 +19604,10 @@
         <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -20000,10 +20000,10 @@
         <v>0</v>
       </c>
       <c r="AD148" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE148" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF148" t="n">
         <v>0</v>
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22106,10 +22106,10 @@
         <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
         <v>0</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.34</v>
+        <v>3.85</v>
       </c>
       <c r="M165" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="N165" t="n">
-        <v>7.2</v>
+        <v>1.95</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,16 +22238,16 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD165" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF165" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="M166" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N166" t="n">
-        <v>2.41</v>
+        <v>7.2</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,16 +22370,16 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF166" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22502,10 +22502,10 @@
         <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC167" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD167" t="n">
         <v>0</v>
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22814,22 +22814,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22946,22 +22946,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27782,10 +27782,10 @@
         <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD207" t="n">
         <v>0</v>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -265,12 +265,12 @@
     <t>China China League One</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>China Chinese Super League</t>
-  </si>
-  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
@@ -283,31 +283,37 @@
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Ukraine Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Ukraine Ukrainian Premier League</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
@@ -316,48 +322,42 @@
     <t>Scotland Championship</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>England EFL League Two</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Russia Russian Premier League</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Russia Russian Premier League</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -367,24 +367,24 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Slovakia Super Liga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
+    <t>Chile Primera B</t>
   </si>
   <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -430,12 +430,12 @@
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>V-Varen Nagasaki</t>
-  </si>
-  <si>
     <t>Kataller Toyama</t>
   </si>
   <si>
@@ -445,588 +445,588 @@
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Fujieda MYFC</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
     <t>Cheonan City</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Fujieda MYFC</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Paderborn</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Karlsruher SC</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Darmstadt 98</t>
   </si>
   <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
     <t>Cardiff City</t>
   </si>
   <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
   </si>
   <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Waldhof Mannheim</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Hoffenheim II</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Veres Rivne</t>
+  </si>
+  <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
-    <t>Veres Rivne</t>
-  </si>
-  <si>
     <t>Nieciecza</t>
   </si>
   <si>
+    <t>Ufa</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Naftan</t>
+  </si>
+  <si>
     <t>Trelleborg</t>
   </si>
   <si>
-    <t>Naftan</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
     <t>Utsikten</t>
   </si>
   <si>
-    <t>Ufa</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Plymouth Argyle</t>
+  </si>
+  <si>
+    <t>Huddersfield Town</t>
+  </si>
+  <si>
+    <t>Burton Albion</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
   </si>
   <si>
     <t>Kilmarnock</t>
   </si>
   <si>
+    <t>St. Johnstone</t>
+  </si>
+  <si>
     <t>Greenock Morton</t>
   </si>
   <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Raith Rovers</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>Lincoln City</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Termez Surkhon</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Shrewsbury Town</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
+  </si>
+  <si>
+    <t>Salford City</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Barnet</t>
   </si>
   <si>
-    <t>Shrewsbury Town</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Milton Keynes Dons</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Walsall</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Colchester United</t>
+  </si>
+  <si>
+    <t>Cambridge United</t>
+  </si>
+  <si>
+    <t>Grimsby Town</t>
+  </si>
+  <si>
+    <t>Start</t>
   </si>
   <si>
     <t>Airdrieonians</t>
   </si>
   <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Plymouth Argyle</t>
-  </si>
-  <si>
-    <t>Cambridge United</t>
-  </si>
-  <si>
-    <t>Grimsby Town</t>
-  </si>
-  <si>
-    <t>Raith Rovers</t>
-  </si>
-  <si>
-    <t>St. Johnstone</t>
-  </si>
-  <si>
-    <t>Termez Surkhon</t>
-  </si>
-  <si>
-    <t>Newport County</t>
-  </si>
-  <si>
-    <t>Salford City</t>
-  </si>
-  <si>
-    <t>Colchester United</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Huddersfield Town</t>
-  </si>
-  <si>
-    <t>Bristol Rovers</t>
-  </si>
-  <si>
-    <t>KuPS</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>KVC Westerlo</t>
-  </si>
-  <si>
-    <t>Blackpool</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Lincoln City</t>
-  </si>
-  <si>
-    <t>Chesterfield</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
     <t>KAMAZ</t>
   </si>
   <si>
+    <t>Rostov</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
+    <t>Levski Sofia</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Rijeka</t>
   </si>
   <si>
-    <t>Rostov</t>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
   </si>
   <si>
     <t>Varaždin</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Zorya</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
     <t>Slavia</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
     <t>Mura</t>
   </si>
   <si>
+    <t>Widzew Łódź</t>
+  </si>
+  <si>
     <t>Stal Rzeszów</t>
   </si>
   <si>
     <t>Argeș</t>
   </si>
   <si>
-    <t>Widzew Łódź</t>
-  </si>
-  <si>
     <t>Värnamo</t>
   </si>
   <si>
     <t>Diósgyőr</t>
   </si>
   <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Oulu</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
     <t>Winterthur</t>
   </si>
   <si>
-    <t>Oulu</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
-    <t>Zemplín Michalovce</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
     <t>Motherwell</t>
   </si>
   <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Olimpiyets</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
     <t>07 Vestur</t>
   </si>
   <si>
     <t>Ried</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Krasnodar</t>
-  </si>
-  <si>
-    <t>Olimpiyets</t>
-  </si>
-  <si>
     <t>Bačka Topola</t>
   </si>
   <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
     <t>OFK Beograd</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
     <t>Ludogorets</t>
   </si>
   <si>
+    <t>Primorje</t>
+  </si>
+  <si>
     <t>Ferencváros</t>
   </si>
   <si>
-    <t>Primorje</t>
+    <t>Dinamo Bucureşti</t>
   </si>
   <si>
     <t>Basel</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
+    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
+    <t>KAA Gent</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>KAA Gent</t>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Osijek</t>
   </si>
   <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
     <t>Novorizontino</t>
   </si>
   <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Sport Recife</t>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
   </si>
   <si>
     <t>Defensores Unidos</t>
   </si>
   <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Concepción</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
     <t>Santiago Morning</t>
   </si>
   <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Concepción</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
@@ -1042,30 +1042,30 @@
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
     <t>North Carolina Courage</t>
   </si>
   <si>
-    <t>Amazonas</t>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
   </si>
   <si>
     <t>Minnesota United II</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
     <t>North Texas</t>
   </si>
   <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>El Paso Locomotive</t>
   </si>
   <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Manly United</t>
   </si>
   <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Vegalta Sendai</t>
-  </si>
-  <si>
     <t>Omiya Ardija</t>
   </si>
   <si>
@@ -1096,496 +1096,502 @@
     <t>Montedio Yamagata</t>
   </si>
   <si>
+    <t>Imabari</t>
+  </si>
+  <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Ehime</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Imabari</t>
-  </si>
-  <si>
-    <t>Ehime</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
     <t>Gagra</t>
   </si>
   <si>
+    <t>Kolkheti Poti</t>
+  </si>
+  <si>
+    <t>Telavi</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Gareji</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Kolkheti Poti</t>
-  </si>
-  <si>
-    <t>Telavi</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Gareji</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
     <t>Peterborough United</t>
   </si>
   <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Jahn Regensburg</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Saarbrucken</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Jahn Regensburg</t>
-  </si>
-  <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Dynamo Kyiv</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
+    <t>Minsk</t>
+  </si>
+  <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>Minsk</t>
-  </si>
-  <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
-    <t>Shinnik</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Mansfield Town</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
   </si>
   <si>
     <t>Livingston</t>
   </si>
   <si>
+    <t>Partick Thistle</t>
+  </si>
+  <si>
     <t>Dunfermline Athletic</t>
   </si>
   <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Queen's Park</t>
+  </si>
+  <si>
+    <t>Oldham Athletic</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Swindon Town</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Crewe Alexandra</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
     <t>Fleetwood Town</t>
   </si>
   <si>
-    <t>Bromley</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Oldham Athletic</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>Swindon Town</t>
-  </si>
-  <si>
-    <t>Kokand-1912</t>
-  </si>
-  <si>
-    <t>KR</t>
+    <t>Notts County</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Tranmere Rovers</t>
+  </si>
+  <si>
+    <t>Cheltenham Town</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
   </si>
   <si>
     <t>Ross County</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Barnsley</t>
-  </si>
-  <si>
-    <t>Cheltenham Town</t>
-  </si>
-  <si>
-    <t>Crawley Town</t>
-  </si>
-  <si>
-    <t>Queen's Park</t>
-  </si>
-  <si>
-    <t>Partick Thistle</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Notts County</t>
-  </si>
-  <si>
-    <t>Crewe Alexandra</t>
-  </si>
-  <si>
-    <t>Tranmere Rovers</t>
-  </si>
-  <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Leyton Orient</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Haka</t>
-  </si>
-  <si>
-    <t>Exeter City</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Northampton Town</t>
-  </si>
-  <si>
-    <t>Mansfield Town</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
     <t>Stuttgart II</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
+    <t>Krylya Sovetov</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>LNZ Cherkasy</t>
+  </si>
+  <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Slaven Koprivnica</t>
   </si>
   <si>
-    <t>Krylya Sovetov</t>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
   </si>
   <si>
     <t>Gorica</t>
   </si>
   <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>LNZ Cherkasy</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
     <t>Isloch</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
     <t>Aluminij</t>
   </si>
   <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
     <t>GAIS</t>
   </si>
   <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>Skalica</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Brann</t>
+  </si>
+  <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
     <t>Young Boys</t>
   </si>
   <si>
-    <t>Jaro</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Brann</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>Komárno</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Skalica</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
+    <t>Curicó Unido</t>
+  </si>
+  <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
     <t>La Serena</t>
   </si>
   <si>
-    <t>Curicó Unido</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Dinamo Moskva</t>
+  </si>
+  <si>
     <t>Víkingur</t>
   </si>
   <si>
     <t>Salzburg</t>
   </si>
   <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Dinamo Moskva</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
     <t>Spartak Subotica</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Javor Ivanjica</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Bravo</t>
+  </si>
+  <si>
     <t>Kazincbarcika</t>
   </si>
   <si>
-    <t>Bravo</t>
+    <t>FCSB</t>
   </si>
   <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>FCSB</t>
+    <t>Podbrezová</t>
   </si>
   <si>
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
-    <t>Podbrezová</t>
+    <t>RAAL La Louvière</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
   </si>
   <si>
     <t>Deportes Limache</t>
@@ -1594,87 +1600,81 @@
     <t>Avaí</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Bahia</t>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
   </si>
   <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
@@ -1690,28 +1690,28 @@
     <t>New England II</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
     <t>San Diego Wave</t>
   </si>
   <si>
-    <t>Goiás</t>
+    <t>Grêmio</t>
+  </si>
+  <si>
+    <t>North Carolina FC</t>
   </si>
   <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
-    <t>North Carolina FC</t>
-  </si>
-  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
+    <t>Sacramento Republic</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
-  </si>
-  <si>
-    <t>Sacramento Republic</t>
   </si>
   <si>
     <t>Houston Dash</t>
@@ -2565,7 +2565,7 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>133</v>
@@ -2592,13 +2592,13 @@
         <v>568</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -2640,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -2708,13 +2708,13 @@
         <v>568</v>
       </c>
       <c r="L6">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>133</v>
@@ -3172,13 +3172,13 @@
         <v>568</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -3288,13 +3288,13 @@
         <v>568</v>
       </c>
       <c r="L11">
-        <v>3.25</v>
+        <v>2.01</v>
       </c>
       <c r="M11">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N11">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3336,10 +3336,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -3404,13 +3404,13 @@
         <v>568</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -3520,13 +3520,13 @@
         <v>568</v>
       </c>
       <c r="L13">
-        <v>3.25</v>
+        <v>1.46</v>
       </c>
       <c r="M13">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="N13">
-        <v>2.11</v>
+        <v>5.8</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3609,7 +3609,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>133</v>
@@ -3636,13 +3636,13 @@
         <v>568</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3957,7 +3957,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -4073,7 +4073,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4100,13 +4100,13 @@
         <v>568</v>
       </c>
       <c r="L18">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="M18">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N18">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4216,13 +4216,13 @@
         <v>568</v>
       </c>
       <c r="L19">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4421,7 +4421,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4448,13 +4448,13 @@
         <v>568</v>
       </c>
       <c r="L21">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4564,58 +4564,58 @@
         <v>568</v>
       </c>
       <c r="L22">
+        <v>3.23</v>
+      </c>
+      <c r="M22">
+        <v>3.38</v>
+      </c>
+      <c r="N22">
+        <v>1.94</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>1.77</v>
+      </c>
+      <c r="AC22">
         <v>1.93</v>
-      </c>
-      <c r="M22">
-        <v>3.45</v>
-      </c>
-      <c r="N22">
-        <v>3.35</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>1.94</v>
-      </c>
-      <c r="AC22">
-        <v>1.79</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4680,13 +4680,13 @@
         <v>568</v>
       </c>
       <c r="L23">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -5001,10 +5001,10 @@
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
         <v>159</v>
@@ -5028,13 +5028,13 @@
         <v>568</v>
       </c>
       <c r="L26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>160</v>
@@ -5144,13 +5144,13 @@
         <v>568</v>
       </c>
       <c r="L27">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -5465,10 +5465,10 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
         <v>163</v>
@@ -5492,13 +5492,13 @@
         <v>568</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5546,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -5697,10 +5697,10 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
         <v>165</v>
@@ -5724,13 +5724,13 @@
         <v>568</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5772,10 +5772,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>568</v>
       </c>
       <c r="L33">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="M33">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="N33">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5888,16 +5888,16 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD33">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE33">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -5929,10 +5929,10 @@
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
@@ -5956,13 +5956,13 @@
         <v>568</v>
       </c>
       <c r="L34">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -6277,10 +6277,10 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
         <v>170</v>
@@ -6304,13 +6304,13 @@
         <v>568</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -6352,16 +6352,16 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>568</v>
       </c>
       <c r="L38">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="M38">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="N38">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -6625,7 +6625,7 @@
         <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
         <v>133</v>
@@ -6741,7 +6741,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
         <v>133</v>
@@ -6860,7 +6860,7 @@
         <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
         <v>175</v>
@@ -6976,7 +6976,7 @@
         <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
         <v>176</v>
@@ -7092,7 +7092,7 @@
         <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
         <v>177</v>
@@ -7205,7 +7205,7 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
         <v>133</v>
@@ -7324,7 +7324,7 @@
         <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
         <v>179</v>
@@ -7440,7 +7440,7 @@
         <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E47" t="s">
         <v>180</v>
@@ -7553,10 +7553,10 @@
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E48" t="s">
         <v>181</v>
@@ -7580,13 +7580,13 @@
         <v>568</v>
       </c>
       <c r="L48">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E49" t="s">
         <v>182</v>
@@ -7785,7 +7785,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D50" t="s">
         <v>133</v>
@@ -7904,7 +7904,7 @@
         <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -8017,7 +8017,7 @@
         <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D52" t="s">
         <v>133</v>
@@ -8133,7 +8133,7 @@
         <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
         <v>133</v>
@@ -8160,13 +8160,13 @@
         <v>568</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -8249,7 +8249,7 @@
         <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
@@ -8392,13 +8392,13 @@
         <v>568</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -8508,13 +8508,13 @@
         <v>568</v>
       </c>
       <c r="L56">
-        <v>2.42</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M56">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="N56">
-        <v>2.32</v>
+        <v>1.36</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8556,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -8624,13 +8624,13 @@
         <v>568</v>
       </c>
       <c r="L57">
-        <v>9</v>
+        <v>2.38</v>
       </c>
       <c r="M57">
-        <v>4.8</v>
+        <v>3.76</v>
       </c>
       <c r="N57">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8672,16 +8672,16 @@
         <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -8829,10 +8829,10 @@
         <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E59" t="s">
         <v>192</v>
@@ -8856,13 +8856,13 @@
         <v>568</v>
       </c>
       <c r="L59">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D60" t="s">
         <v>133</v>
@@ -8972,13 +8972,13 @@
         <v>568</v>
       </c>
       <c r="L60">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -9177,7 +9177,7 @@
         <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D62" t="s">
         <v>133</v>
@@ -9204,13 +9204,13 @@
         <v>568</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -9293,10 +9293,10 @@
         <v>52</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
         <v>196</v>
@@ -9320,13 +9320,13 @@
         <v>568</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -9368,10 +9368,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
         <v>133</v>
@@ -9528,7 +9528,7 @@
         <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E65" t="s">
         <v>198</v>
@@ -9552,13 +9552,13 @@
         <v>568</v>
       </c>
       <c r="L65">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9641,7 +9641,7 @@
         <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D66" t="s">
         <v>134</v>
@@ -9668,13 +9668,13 @@
         <v>568</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -9784,13 +9784,13 @@
         <v>568</v>
       </c>
       <c r="L67">
-        <v>2.21</v>
+        <v>1.76</v>
       </c>
       <c r="M67">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9832,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC67">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9873,7 +9873,7 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
@@ -9900,13 +9900,13 @@
         <v>568</v>
       </c>
       <c r="L68">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="M68">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N68">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9948,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC68">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9989,7 +9989,7 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D69" t="s">
         <v>133</v>
@@ -10105,7 +10105,7 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s">
         <v>134</v>
@@ -10132,13 +10132,13 @@
         <v>568</v>
       </c>
       <c r="L70">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="M70">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="N70">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10180,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC70">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD70">
         <v>0</v>
@@ -10248,13 +10248,13 @@
         <v>568</v>
       </c>
       <c r="L71">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="M71">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N71">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC71">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -10364,13 +10364,13 @@
         <v>568</v>
       </c>
       <c r="L72">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N72">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10412,10 +10412,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -10453,10 +10453,10 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E73" t="s">
         <v>206</v>
@@ -10569,7 +10569,7 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D74" t="s">
         <v>133</v>
@@ -10685,10 +10685,10 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E75" t="s">
         <v>208</v>
@@ -10801,7 +10801,7 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D76" t="s">
         <v>133</v>
@@ -10917,7 +10917,7 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
         <v>134</v>
@@ -10944,13 +10944,13 @@
         <v>568</v>
       </c>
       <c r="L77">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="M77">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N77">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC77">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -11060,13 +11060,13 @@
         <v>568</v>
       </c>
       <c r="L78">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="M78">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="N78">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC78">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11149,10 +11149,10 @@
         <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E79" t="s">
         <v>212</v>
@@ -11176,13 +11176,13 @@
         <v>568</v>
       </c>
       <c r="L79">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M79">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N79">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D80" t="s">
         <v>134</v>
@@ -11292,13 +11292,13 @@
         <v>568</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11340,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -11381,7 +11381,7 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
         <v>134</v>
@@ -11408,13 +11408,13 @@
         <v>568</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11497,10 +11497,10 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E82" t="s">
         <v>215</v>
@@ -11524,13 +11524,13 @@
         <v>568</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11572,10 +11572,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11613,7 +11613,7 @@
         <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D83" t="s">
         <v>134</v>
@@ -11640,13 +11640,13 @@
         <v>568</v>
       </c>
       <c r="L83">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="M83">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="N83">
-        <v>1.64</v>
+        <v>2.92</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11688,10 +11688,10 @@
         <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11729,7 +11729,7 @@
         <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
         <v>134</v>
@@ -11756,13 +11756,13 @@
         <v>568</v>
       </c>
       <c r="L84">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="M84">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N84">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC84">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E85" t="s">
         <v>218</v>
@@ -11872,13 +11872,13 @@
         <v>568</v>
       </c>
       <c r="L85">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11961,10 +11961,10 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E86" t="s">
         <v>219</v>
@@ -11988,13 +11988,13 @@
         <v>568</v>
       </c>
       <c r="L86">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M86">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -12077,10 +12077,10 @@
         <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E87" t="s">
         <v>220</v>
@@ -12104,13 +12104,13 @@
         <v>568</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -12152,10 +12152,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -12193,10 +12193,10 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D88" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E88" t="s">
         <v>221</v>
@@ -12309,7 +12309,7 @@
         <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
         <v>133</v>
@@ -12425,10 +12425,10 @@
         <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E90" t="s">
         <v>223</v>
@@ -12452,13 +12452,13 @@
         <v>568</v>
       </c>
       <c r="L90">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N90">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -12500,10 +12500,10 @@
         <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC90">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD90">
         <v>0</v>
@@ -12541,7 +12541,7 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D91" t="s">
         <v>134</v>
@@ -12568,13 +12568,13 @@
         <v>568</v>
       </c>
       <c r="L91">
-        <v>1.64</v>
+        <v>2.74</v>
       </c>
       <c r="M91">
-        <v>3.75</v>
+        <v>2.91</v>
       </c>
       <c r="N91">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12616,10 +12616,10 @@
         <v>0</v>
       </c>
       <c r="AB91">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC91">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD91">
         <v>0</v>
@@ -12657,10 +12657,10 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E92" t="s">
         <v>225</v>
@@ -12684,13 +12684,13 @@
         <v>568</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12732,10 +12732,10 @@
         <v>0</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD92">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D93" t="s">
         <v>134</v>
@@ -12800,13 +12800,13 @@
         <v>568</v>
       </c>
       <c r="L93">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AB93">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD93">
         <v>0</v>
@@ -12889,10 +12889,10 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D94" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E94" t="s">
         <v>227</v>
@@ -12916,13 +12916,13 @@
         <v>568</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12964,10 +12964,10 @@
         <v>0</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD94">
         <v>0</v>
@@ -13005,10 +13005,10 @@
         <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E95" t="s">
         <v>228</v>
@@ -13121,7 +13121,7 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D96" t="s">
         <v>134</v>
@@ -13148,13 +13148,13 @@
         <v>568</v>
       </c>
       <c r="L96">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="M96">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="N96">
-        <v>4.8</v>
+        <v>3.47</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -13196,10 +13196,10 @@
         <v>0</v>
       </c>
       <c r="AB96">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC96">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13237,10 +13237,10 @@
         <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D97" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E97" t="s">
         <v>230</v>
@@ -13264,13 +13264,13 @@
         <v>568</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>0</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD97">
         <v>0</v>
@@ -13353,7 +13353,7 @@
         <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D98" t="s">
         <v>134</v>
@@ -13380,13 +13380,13 @@
         <v>568</v>
       </c>
       <c r="L98">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M98">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="N98">
-        <v>4.4</v>
+        <v>3.79</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC98">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AD98">
         <v>0</v>
@@ -13469,7 +13469,7 @@
         <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D99" t="s">
         <v>134</v>
@@ -13496,13 +13496,13 @@
         <v>568</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13585,7 +13585,7 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D100" t="s">
         <v>134</v>
@@ -13612,13 +13612,13 @@
         <v>568</v>
       </c>
       <c r="L100">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="M100">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="N100">
-        <v>5.3</v>
+        <v>3.34</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13660,10 +13660,10 @@
         <v>0</v>
       </c>
       <c r="AB100">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC100">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13701,7 +13701,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D101" t="s">
         <v>134</v>
@@ -13728,13 +13728,13 @@
         <v>568</v>
       </c>
       <c r="L101">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="M101">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N101">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC101">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13817,7 +13817,7 @@
         <v>53</v>
       </c>
       <c r="C102" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D102" t="s">
         <v>134</v>
@@ -13844,13 +13844,13 @@
         <v>568</v>
       </c>
       <c r="L102">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="M102">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N102">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13933,10 +13933,10 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E103" t="s">
         <v>236</v>
@@ -13960,13 +13960,13 @@
         <v>568</v>
       </c>
       <c r="L103">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M103">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N103">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -14008,10 +14008,10 @@
         <v>0</v>
       </c>
       <c r="AB103">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC103">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD103">
         <v>0</v>
@@ -14052,7 +14052,7 @@
         <v>101</v>
       </c>
       <c r="D104" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E104" t="s">
         <v>237</v>
@@ -14165,7 +14165,7 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D105" t="s">
         <v>134</v>
@@ -14281,7 +14281,7 @@
         <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D106" t="s">
         <v>134</v>
@@ -14424,13 +14424,13 @@
         <v>568</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -14472,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD107">
         <v>0</v>
@@ -14540,13 +14540,13 @@
         <v>568</v>
       </c>
       <c r="L108">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M108">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -14588,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="AB108">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD108">
         <v>0</v>
@@ -14629,10 +14629,10 @@
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D109" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E109" t="s">
         <v>242</v>
@@ -14656,13 +14656,13 @@
         <v>568</v>
       </c>
       <c r="L109">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD109">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D110" t="s">
         <v>134</v>
@@ -14888,13 +14888,13 @@
         <v>568</v>
       </c>
       <c r="L111">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14936,10 +14936,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14977,7 +14977,7 @@
         <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D112" t="s">
         <v>134</v>
@@ -15004,13 +15004,13 @@
         <v>568</v>
       </c>
       <c r="L112">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -15052,10 +15052,10 @@
         <v>0</v>
       </c>
       <c r="AB112">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -15093,7 +15093,7 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D113" t="s">
         <v>134</v>
@@ -15120,13 +15120,13 @@
         <v>568</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -15209,7 +15209,7 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D114" t="s">
         <v>134</v>
@@ -15325,7 +15325,7 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D115" t="s">
         <v>134</v>
@@ -15441,7 +15441,7 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D116" t="s">
         <v>134</v>
@@ -15557,7 +15557,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D117" t="s">
         <v>134</v>
@@ -15673,10 +15673,10 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D118" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E118" t="s">
         <v>251</v>
@@ -15789,7 +15789,7 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D119" t="s">
         <v>134</v>
@@ -15905,7 +15905,7 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D120" t="s">
         <v>134</v>
@@ -16021,7 +16021,7 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D121" t="s">
         <v>134</v>
@@ -16137,7 +16137,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D122" t="s">
         <v>134</v>
@@ -16164,13 +16164,13 @@
         <v>568</v>
       </c>
       <c r="L122">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N122">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -16253,7 +16253,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
@@ -16280,13 +16280,13 @@
         <v>568</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -16328,10 +16328,10 @@
         <v>0</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -16369,7 +16369,7 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D124" t="s">
         <v>134</v>
@@ -16396,13 +16396,13 @@
         <v>568</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -16444,10 +16444,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16485,7 +16485,7 @@
         <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D125" t="s">
         <v>133</v>
@@ -16512,13 +16512,13 @@
         <v>568</v>
       </c>
       <c r="L125">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M125">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16560,10 +16560,10 @@
         <v>0</v>
       </c>
       <c r="AB125">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD125">
         <v>0</v>
@@ -16628,13 +16628,13 @@
         <v>568</v>
       </c>
       <c r="L126">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16676,10 +16676,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16833,7 +16833,7 @@
         <v>55</v>
       </c>
       <c r="C128" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D128" t="s">
         <v>133</v>
@@ -16860,13 +16860,13 @@
         <v>568</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16908,10 +16908,10 @@
         <v>0</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -17065,7 +17065,7 @@
         <v>56</v>
       </c>
       <c r="C130" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D130" t="s">
         <v>134</v>
@@ -17092,13 +17092,13 @@
         <v>568</v>
       </c>
       <c r="L130">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="M130">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N130">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -17181,7 +17181,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -17208,13 +17208,13 @@
         <v>568</v>
       </c>
       <c r="L131">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="M131">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="N131">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17256,10 +17256,10 @@
         <v>0</v>
       </c>
       <c r="AB131">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC131">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD131">
         <v>0</v>
@@ -17297,7 +17297,7 @@
         <v>56</v>
       </c>
       <c r="C132" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D132" t="s">
         <v>134</v>
@@ -17324,13 +17324,13 @@
         <v>568</v>
       </c>
       <c r="L132">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M132">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="N132">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD132">
         <v>0</v>
@@ -17413,7 +17413,7 @@
         <v>56</v>
       </c>
       <c r="C133" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D133" t="s">
         <v>133</v>
@@ -17672,13 +17672,13 @@
         <v>568</v>
       </c>
       <c r="L135">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="M135">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N135">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17720,10 +17720,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC135">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17761,10 +17761,10 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D136" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E136" t="s">
         <v>269</v>
@@ -17788,13 +17788,13 @@
         <v>568</v>
       </c>
       <c r="L136">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M136">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N136">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17836,10 +17836,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC136">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17877,10 +17877,10 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E137" t="s">
         <v>270</v>
@@ -17904,13 +17904,13 @@
         <v>568</v>
       </c>
       <c r="L137">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M137">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N137">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -18020,13 +18020,13 @@
         <v>568</v>
       </c>
       <c r="L138">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="M138">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N138">
-        <v>4.3</v>
+        <v>3.47</v>
       </c>
       <c r="O138">
         <v>0</v>
@@ -18068,10 +18068,10 @@
         <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AC138">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="AD138">
         <v>0</v>
@@ -18109,10 +18109,10 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D139" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E139" t="s">
         <v>272</v>
@@ -18136,13 +18136,13 @@
         <v>568</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M139">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -18184,10 +18184,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -18225,10 +18225,10 @@
         <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D140" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E140" t="s">
         <v>273</v>
@@ -18341,7 +18341,7 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D141" t="s">
         <v>134</v>
@@ -18368,13 +18368,13 @@
         <v>568</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18457,10 +18457,10 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E142" t="s">
         <v>275</v>
@@ -18484,58 +18484,58 @@
         <v>568</v>
       </c>
       <c r="L142">
+        <v>1.89</v>
+      </c>
+      <c r="M142">
+        <v>3.26</v>
+      </c>
+      <c r="N142">
+        <v>3.53</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>0</v>
+      </c>
+      <c r="R142">
+        <v>0</v>
+      </c>
+      <c r="S142">
+        <v>0</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="U142">
+        <v>0</v>
+      </c>
+      <c r="V142">
+        <v>0</v>
+      </c>
+      <c r="W142">
+        <v>0</v>
+      </c>
+      <c r="X142">
+        <v>0</v>
+      </c>
+      <c r="Y142">
+        <v>0</v>
+      </c>
+      <c r="Z142">
+        <v>0</v>
+      </c>
+      <c r="AA142">
+        <v>0</v>
+      </c>
+      <c r="AB142">
         <v>1.83</v>
       </c>
-      <c r="M142">
-        <v>3.85</v>
-      </c>
-      <c r="N142">
-        <v>3.65</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>0</v>
-      </c>
-      <c r="R142">
-        <v>0</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142">
-        <v>0</v>
-      </c>
-      <c r="U142">
-        <v>0</v>
-      </c>
-      <c r="V142">
-        <v>0</v>
-      </c>
-      <c r="W142">
-        <v>0</v>
-      </c>
-      <c r="X142">
-        <v>0</v>
-      </c>
-      <c r="Y142">
-        <v>0</v>
-      </c>
-      <c r="Z142">
-        <v>0</v>
-      </c>
-      <c r="AA142">
-        <v>0</v>
-      </c>
-      <c r="AB142">
-        <v>1.82</v>
-      </c>
       <c r="AC142">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AD142">
         <v>0</v>
@@ -18576,7 +18576,7 @@
         <v>120</v>
       </c>
       <c r="D143" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
@@ -18600,13 +18600,13 @@
         <v>568</v>
       </c>
       <c r="L143">
-        <v>3.47</v>
+        <v>1.75</v>
       </c>
       <c r="M143">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N143">
-        <v>1.82</v>
+        <v>3.71</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -18648,10 +18648,10 @@
         <v>0</v>
       </c>
       <c r="AB143">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD143">
         <v>0</v>
@@ -18716,13 +18716,13 @@
         <v>568</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M144">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -18764,10 +18764,10 @@
         <v>0</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD144">
         <v>0</v>
@@ -18832,13 +18832,13 @@
         <v>568</v>
       </c>
       <c r="L145">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="M145">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N145">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="O145">
         <v>0</v>
@@ -18880,10 +18880,10 @@
         <v>0</v>
       </c>
       <c r="AB145">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC145">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD145">
         <v>0</v>
@@ -18921,10 +18921,10 @@
         <v>60</v>
       </c>
       <c r="C146" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E146" t="s">
         <v>279</v>
@@ -19037,10 +19037,10 @@
         <v>60</v>
       </c>
       <c r="C147" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E147" t="s">
         <v>280</v>
@@ -19269,7 +19269,7 @@
         <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D149" t="s">
         <v>134</v>
@@ -19296,13 +19296,13 @@
         <v>568</v>
       </c>
       <c r="L149">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="M149">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N149">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -19385,7 +19385,7 @@
         <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D150" t="s">
         <v>133</v>
@@ -19501,10 +19501,10 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D151" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E151" t="s">
         <v>284</v>
@@ -19528,13 +19528,13 @@
         <v>568</v>
       </c>
       <c r="L151">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M151">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -19576,10 +19576,10 @@
         <v>0</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD151">
         <v>0</v>
@@ -19617,7 +19617,7 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D152" t="s">
         <v>134</v>
@@ -19644,13 +19644,13 @@
         <v>568</v>
       </c>
       <c r="L152">
-        <v>6.8</v>
+        <v>4.88</v>
       </c>
       <c r="M152">
-        <v>5.2</v>
+        <v>4.24</v>
       </c>
       <c r="N152">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19692,16 +19692,16 @@
         <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC152">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD152">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AE152">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF152">
         <v>0</v>
@@ -19733,7 +19733,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D153" t="s">
         <v>134</v>
@@ -19760,13 +19760,13 @@
         <v>568</v>
       </c>
       <c r="L153">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M153">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -19814,10 +19814,10 @@
         <v>0</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF153">
         <v>0</v>
@@ -19849,10 +19849,10 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D154" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E154" t="s">
         <v>287</v>
@@ -19876,13 +19876,13 @@
         <v>568</v>
       </c>
       <c r="L154">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M154">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N154">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -19930,10 +19930,10 @@
         <v>0</v>
       </c>
       <c r="AD154">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE154">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF154">
         <v>0</v>
@@ -19965,7 +19965,7 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D155" t="s">
         <v>134</v>
@@ -19992,13 +19992,13 @@
         <v>568</v>
       </c>
       <c r="L155">
-        <v>4.88</v>
+        <v>6.9</v>
       </c>
       <c r="M155">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="N155">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -20040,16 +20040,16 @@
         <v>0</v>
       </c>
       <c r="AB155">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC155">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD155">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AE155">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF155">
         <v>0</v>
@@ -20221,7 +20221,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -20313,7 +20313,7 @@
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D158" t="s">
         <v>134</v>
@@ -20429,7 +20429,7 @@
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D159" t="s">
         <v>134</v>
@@ -20661,7 +20661,7 @@
         <v>63</v>
       </c>
       <c r="C161" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D161" t="s">
         <v>134</v>
@@ -20917,7 +20917,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -21036,10 +21036,10 @@
         <v>568</v>
       </c>
       <c r="L164">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M164">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N164">
         <v>4.8</v>
@@ -21125,7 +21125,7 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D165" t="s">
         <v>134</v>
@@ -21241,7 +21241,7 @@
         <v>64</v>
       </c>
       <c r="C166" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D166" t="s">
         <v>134</v>
@@ -21357,7 +21357,7 @@
         <v>64</v>
       </c>
       <c r="C167" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D167" t="s">
         <v>134</v>
@@ -21473,7 +21473,7 @@
         <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D168" t="s">
         <v>134</v>
@@ -21500,13 +21500,13 @@
         <v>568</v>
       </c>
       <c r="L168">
-        <v>1.34</v>
+        <v>3.71</v>
       </c>
       <c r="M168">
-        <v>5.2</v>
+        <v>3.08</v>
       </c>
       <c r="N168">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -21548,16 +21548,16 @@
         <v>0</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD168">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF168">
         <v>0</v>
@@ -21589,7 +21589,7 @@
         <v>65</v>
       </c>
       <c r="C169" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D169" t="s">
         <v>134</v>
@@ -21616,13 +21616,13 @@
         <v>568</v>
       </c>
       <c r="L169">
-        <v>3.85</v>
+        <v>1.33</v>
       </c>
       <c r="M169">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="N169">
-        <v>1.95</v>
+        <v>6.8</v>
       </c>
       <c r="O169">
         <v>0</v>
@@ -21664,16 +21664,16 @@
         <v>0</v>
       </c>
       <c r="AB169">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC169">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF169">
         <v>0</v>
@@ -21705,7 +21705,7 @@
         <v>65</v>
       </c>
       <c r="C170" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D170" t="s">
         <v>134</v>
@@ -21732,13 +21732,13 @@
         <v>568</v>
       </c>
       <c r="L170">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M170">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N170">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -21780,10 +21780,10 @@
         <v>0</v>
       </c>
       <c r="AB170">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC170">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD170">
         <v>0</v>
@@ -21821,7 +21821,7 @@
         <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="D171" t="s">
         <v>134</v>
@@ -21848,13 +21848,13 @@
         <v>568</v>
       </c>
       <c r="L171">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M171">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -21896,10 +21896,10 @@
         <v>0</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD171">
         <v>0</v>
@@ -21937,10 +21937,10 @@
         <v>66</v>
       </c>
       <c r="C172" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D172" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E172" t="s">
         <v>305</v>
@@ -22053,10 +22053,10 @@
         <v>66</v>
       </c>
       <c r="C173" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D173" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E173" t="s">
         <v>306</v>
@@ -22169,7 +22169,7 @@
         <v>67</v>
       </c>
       <c r="C174" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D174" t="s">
         <v>133</v>
@@ -22196,13 +22196,13 @@
         <v>568</v>
       </c>
       <c r="L174">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M174">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O174">
         <v>0</v>
@@ -22244,10 +22244,10 @@
         <v>0</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD174">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>67</v>
       </c>
       <c r="C175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D175" t="s">
         <v>133</v>
@@ -22401,10 +22401,10 @@
         <v>67</v>
       </c>
       <c r="C176" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D176" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E176" t="s">
         <v>309</v>
@@ -22517,10 +22517,10 @@
         <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D177" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E177" t="s">
         <v>310</v>
@@ -22660,13 +22660,13 @@
         <v>568</v>
       </c>
       <c r="L178">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M178">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N178">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O178">
         <v>0</v>
@@ -22708,10 +22708,10 @@
         <v>0</v>
       </c>
       <c r="AB178">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC178">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD178">
         <v>0</v>
@@ -24632,13 +24632,13 @@
         <v>568</v>
       </c>
       <c r="L195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M195">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -24680,10 +24680,10 @@
         <v>0</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD195">
         <v>0</v>
@@ -24748,13 +24748,13 @@
         <v>568</v>
       </c>
       <c r="L196">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M196">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N196">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O196">
         <v>0</v>
@@ -24796,10 +24796,10 @@
         <v>0</v>
       </c>
       <c r="AB196">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC196">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD196">
         <v>0</v>
@@ -24837,7 +24837,7 @@
         <v>70</v>
       </c>
       <c r="C197" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D197" t="s">
         <v>133</v>
@@ -24953,7 +24953,7 @@
         <v>71</v>
       </c>
       <c r="C198" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D198" t="s">
         <v>133</v>
@@ -25069,7 +25069,7 @@
         <v>71</v>
       </c>
       <c r="C199" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D199" t="s">
         <v>133</v>
@@ -25185,7 +25185,7 @@
         <v>71</v>
       </c>
       <c r="C200" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D200" t="s">
         <v>133</v>
@@ -25301,7 +25301,7 @@
         <v>71</v>
       </c>
       <c r="C201" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D201" t="s">
         <v>133</v>
@@ -25417,7 +25417,7 @@
         <v>71</v>
       </c>
       <c r="C202" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D202" t="s">
         <v>133</v>
@@ -25533,7 +25533,7 @@
         <v>71</v>
       </c>
       <c r="C203" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D203" t="s">
         <v>133</v>
@@ -26229,7 +26229,7 @@
         <v>73</v>
       </c>
       <c r="C209" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D209" t="s">
         <v>133</v>
@@ -26345,7 +26345,7 @@
         <v>73</v>
       </c>
       <c r="C210" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D210" t="s">
         <v>133</v>
@@ -26372,13 +26372,13 @@
         <v>568</v>
       </c>
       <c r="L210">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M210">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -26420,10 +26420,10 @@
         <v>0</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD210">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>74</v>
       </c>
       <c r="C211" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D211" t="s">
         <v>133</v>
@@ -26488,13 +26488,13 @@
         <v>568</v>
       </c>
       <c r="L211">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M211">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -26536,10 +26536,10 @@
         <v>0</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD211">
         <v>0</v>
@@ -26577,7 +26577,7 @@
         <v>74</v>
       </c>
       <c r="C212" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D212" t="s">
         <v>133</v>
@@ -26604,13 +26604,13 @@
         <v>568</v>
       </c>
       <c r="L212">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M212">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N212">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AB212">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC212">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD212">
         <v>0</v>
@@ -26693,7 +26693,7 @@
         <v>74</v>
       </c>
       <c r="C213" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D213" t="s">
         <v>133</v>
@@ -27184,13 +27184,13 @@
         <v>568</v>
       </c>
       <c r="L217">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M217">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O217">
         <v>0</v>
@@ -27232,10 +27232,10 @@
         <v>0</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD217">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -259,18 +259,18 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>China Chinese Super League</t>
-  </si>
-  <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
@@ -283,81 +283,81 @@
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
+    <t>England EFL League Two</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Scotland Championship</t>
   </si>
   <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>England EFL League Two</t>
-  </si>
-  <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
   </si>
   <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t>Slovakia Super Liga</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -430,583 +430,595 @@
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
+    <t>Kataller Toyama</t>
+  </si>
+  <si>
     <t>V-Varen Nagasaki</t>
   </si>
   <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Kataller Toyama</t>
-  </si>
-  <si>
     <t>St George City FA</t>
   </si>
   <si>
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
     <t>Oita Trinita</t>
   </si>
   <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
     <t>Fujieda MYFC</t>
   </si>
   <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
-    <t>Samgurali</t>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Paderborn</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Karlsruher SC</t>
+    <t>Shaanxi Union</t>
   </si>
   <si>
     <t>Elversberg</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
     <t>Cardiff City</t>
   </si>
   <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
+    <t>Qingdao Youth Island</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Qingdao Youth Island</t>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
   </si>
   <si>
     <t>Astana</t>
   </si>
   <si>
-    <t>Waldhof Mannheim</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
     <t>Zhetysu</t>
   </si>
   <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Hoffenheim II</t>
-  </si>
-  <si>
     <t>Osnabrück</t>
   </si>
   <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Schwarz-Weiß Bregenz</t>
+  </si>
+  <si>
     <t>Veres Rivne</t>
   </si>
   <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
     <t>Nieciecza</t>
   </si>
   <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Ufa</t>
   </si>
   <si>
+    <t>Naftan</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Naftan</t>
-  </si>
-  <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
-    <t>Utsikten</t>
+    <t>Salford City</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Plymouth Argyle</t>
+  </si>
+  <si>
+    <t>Lincoln City</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Shrewsbury Town</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
+  </si>
+  <si>
+    <t>St. Johnstone</t>
   </si>
   <si>
     <t>KuPS</t>
   </si>
   <si>
-    <t>Plymouth Argyle</t>
-  </si>
-  <si>
     <t>Huddersfield Town</t>
   </si>
   <si>
+    <t>Colchester United</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
     <t>Burton Albion</t>
   </si>
   <si>
+    <t>Raith Rovers</t>
+  </si>
+  <si>
+    <t>Grimsby Town</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Cambridge United</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>Greenock Morton</t>
+  </si>
+  <si>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>Airdrieonians</t>
+  </si>
+  <si>
     <t>Tromsø</t>
   </si>
   <si>
-    <t>Wigan Athletic</t>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Termez Surkhon</t>
   </si>
   <si>
     <t>Kilmarnock</t>
   </si>
   <si>
-    <t>St. Johnstone</t>
-  </si>
-  <si>
-    <t>Greenock Morton</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Raith Rovers</t>
-  </si>
-  <si>
-    <t>Milton Keynes Dons</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Blackpool</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>Walsall</t>
-  </si>
-  <si>
-    <t>Lincoln City</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Termez Surkhon</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Shrewsbury Town</t>
-  </si>
-  <si>
-    <t>KVC Westerlo</t>
-  </si>
-  <si>
-    <t>Salford City</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Barnet</t>
-  </si>
-  <si>
-    <t>Newport County</t>
-  </si>
-  <si>
-    <t>Bristol Rovers</t>
-  </si>
-  <si>
-    <t>Chesterfield</t>
-  </si>
-  <si>
-    <t>Colchester United</t>
-  </si>
-  <si>
-    <t>Cambridge United</t>
-  </si>
-  <si>
-    <t>Grimsby Town</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Airdrieonians</t>
+    <t>KAMAZ</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>KAMAZ</t>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
   </si>
   <si>
     <t>Rostov</t>
   </si>
   <si>
-    <t>Zrinjski</t>
+    <t>Levski Sofia</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>Slavia</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Teplice</t>
   </si>
   <si>
     <t>Sandviken</t>
   </si>
   <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
     <t>Karviná</t>
   </si>
   <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Zorya</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Varaždin</t>
-  </si>
-  <si>
-    <t>Slavia</t>
-  </si>
-  <si>
     <t>Mura</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Argeș</t>
+  </si>
+  <si>
     <t>Stal Rzeszów</t>
   </si>
   <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
     <t>Diósgyőr</t>
   </si>
   <si>
     <t>Ružomberok</t>
   </si>
   <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Oulu</t>
+  </si>
+  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
-    <t>Zemplín Michalovce</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Oulu</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
+    <t>Chayka</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Chayka</t>
+    <t>Motherwell</t>
   </si>
   <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Olimpiyets</t>
+  </si>
+  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
-    <t>Olimpiyets</t>
-  </si>
-  <si>
-    <t>Krasnodar</t>
-  </si>
-  <si>
     <t>07 Vestur</t>
   </si>
   <si>
-    <t>Ried</t>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
   </si>
   <si>
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
   </si>
   <si>
     <t>Austria Wien II</t>
   </si>
   <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
+    <t>Ludogorets</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Ludogorets</t>
-  </si>
-  <si>
     <t>Primorje</t>
   </si>
   <si>
     <t>Ferencváros</t>
   </si>
   <si>
+    <t>Arminia Bielefeld</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava</t>
+  </si>
+  <si>
     <t>Dinamo Bucureşti</t>
   </si>
   <si>
     <t>Basel</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
-    <t>Arminia Bielefeld</t>
-  </si>
-  <si>
     <t>KAA Gent</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
     <t>Osijek</t>
   </si>
   <si>
-    <t>Coquimbo Unido</t>
-  </si>
-  <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
+    <t>Racing Córdoba</t>
   </si>
   <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
   </si>
   <si>
     <t>All Boys</t>
   </si>
   <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
+    <t>Santiago Morning</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>Concepción</t>
+  </si>
+  <si>
+    <t>San Luis</t>
   </si>
   <si>
     <t>Santiago Wanderers</t>
@@ -1015,57 +1027,45 @@
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Concepción</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
-    <t>Santiago Morning</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Forge FC</t>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
   </si>
   <si>
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>North Carolina Courage</t>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
   </si>
   <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
     <t>North Texas</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
@@ -1081,580 +1081,592 @@
     <t>Manly United</t>
   </si>
   <si>
+    <t>Omiya Ardija</t>
+  </si>
+  <si>
     <t>Vegalta Sendai</t>
   </si>
   <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Omiya Ardija</t>
-  </si>
-  <si>
     <t>Sutherland Sharks</t>
   </si>
   <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
     <t>Imabari</t>
   </si>
   <si>
+    <t>Ehime</t>
+  </si>
+  <si>
     <t>Renofa Yamaguchi</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Ehime</t>
-  </si>
-  <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
+    <t>Kolkheti Poti</t>
+  </si>
+  <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Kolkheti Poti</t>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Gareji</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Preußen Münster</t>
   </si>
   <si>
     <t>Telavi</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Gareji</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Nürnberg</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
     <t>Peterborough United</t>
   </si>
   <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Jahn Regensburg</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Turan Turkistan</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
     <t>Alemannia Aachen</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Jahn Regensburg</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Saarbrucken</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
+    <t>Rapid Wien II</t>
+  </si>
+  <si>
     <t>Dynamo Kyiv</t>
   </si>
   <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>Shinnik</t>
   </si>
   <si>
+    <t>Minsk</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Minsk</t>
-  </si>
-  <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
+    <t>Crewe Alexandra</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Swindon Town</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Partick Thistle</t>
   </si>
   <si>
     <t>Haka</t>
   </si>
   <si>
-    <t>Barnsley</t>
-  </si>
-  <si>
     <t>Leyton Orient</t>
   </si>
   <si>
+    <t>Tranmere Rovers</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
     <t>Mansfield Town</t>
   </si>
   <si>
+    <t>Queen's Park</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Oldham Athletic</t>
+  </si>
+  <si>
+    <t>Notts County</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Cheltenham Town</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Dunfermline Athletic</t>
+  </si>
+  <si>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
-    <t>Northampton Town</t>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
   </si>
   <si>
     <t>Livingston</t>
   </si>
   <si>
-    <t>Partick Thistle</t>
-  </si>
-  <si>
-    <t>Dunfermline Athletic</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Queen's Park</t>
-  </si>
-  <si>
-    <t>Oldham Athletic</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
-    <t>Swindon Town</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Exeter City</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Kokand-1912</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>Bromley</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Crewe Alexandra</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Fleetwood Town</t>
-  </si>
-  <si>
-    <t>Notts County</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Tranmere Rovers</t>
-  </si>
-  <si>
-    <t>Cheltenham Town</t>
-  </si>
-  <si>
-    <t>Crawley Town</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Ross County</t>
+    <t>Chelyabinsk</t>
   </si>
   <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>LNZ Cherkasy</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
   </si>
   <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
-    <t>Sloga Doboj</t>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Isloch</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
     <t>Zlín</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>LNZ Cherkasy</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>Isloch</t>
-  </si>
-  <si>
     <t>Aluminij</t>
   </si>
   <si>
+    <t>GAIS</t>
+  </si>
+  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
     <t>Skalica</t>
   </si>
   <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Komárno</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Jaro</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Curicó Unido</t>
   </si>
   <si>
-    <t>Volga Ulyanovsk</t>
+    <t>Rangers</t>
   </si>
   <si>
     <t>La Serena</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
+    <t>Dinamo Moskva</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Dinamo Moskva</t>
-  </si>
-  <si>
     <t>Víkingur</t>
   </si>
   <si>
-    <t>Salzburg</t>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
   </si>
   <si>
     <t>Spartak Subotica</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
   </si>
   <si>
     <t>St. Pölten</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
     <t>IMT Novi Beograd</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
+    <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Bravo</t>
   </si>
   <si>
     <t>Kazincbarcika</t>
   </si>
   <si>
+    <t>Fortuna Düsseldorf</t>
+  </si>
+  <si>
+    <t>Podbrezová</t>
+  </si>
+  <si>
     <t>FCSB</t>
   </si>
   <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Podbrezová</t>
-  </si>
-  <si>
-    <t>Fortuna Düsseldorf</t>
-  </si>
-  <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
+    <t>Deportes Limache</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>Deportes Limache</t>
-  </si>
-  <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
     <t>Central Norte</t>
   </si>
   <si>
-    <t>San Martín Tucumán</t>
+    <t>Quilmes</t>
   </si>
   <si>
     <t>San Miguel</t>
   </si>
   <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
   </si>
   <si>
     <t>Patronato</t>
   </si>
   <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>Universidad Católica</t>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Univ. Concepción</t>
   </si>
   <si>
     <t>San Marcos</t>
@@ -1663,55 +1675,43 @@
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
     <t>Rhode Island</t>
   </si>
   <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Valour FC</t>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>San Diego Wave</t>
   </si>
   <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>San Diego Wave</t>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
+    <t>North Carolina FC</t>
   </si>
   <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>North Carolina FC</t>
-  </si>
-  <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>Sacramento Republic</t>
-  </si>
-  <si>
-    <t>Las Vegas Lights</t>
   </si>
   <si>
     <t>Houston Dash</t>
@@ -2592,13 +2592,13 @@
         <v>568</v>
       </c>
       <c r="L5">
-        <v>2.01</v>
+        <v>3.25</v>
       </c>
       <c r="M5">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -2640,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC5">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -2708,13 +2708,13 @@
         <v>568</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -2824,13 +2824,13 @@
         <v>568</v>
       </c>
       <c r="L7">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
         <v>133</v>
@@ -3172,13 +3172,13 @@
         <v>568</v>
       </c>
       <c r="L10">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -3288,13 +3288,13 @@
         <v>568</v>
       </c>
       <c r="L11">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -3404,13 +3404,13 @@
         <v>568</v>
       </c>
       <c r="L12">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3520,13 +3520,13 @@
         <v>568</v>
       </c>
       <c r="L13">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="M13">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N13">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3568,10 +3568,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         <v>568</v>
       </c>
       <c r="L14">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="M14">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N14">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -3752,13 +3752,13 @@
         <v>568</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3868,13 +3868,13 @@
         <v>568</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -4073,7 +4073,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4100,13 +4100,13 @@
         <v>568</v>
       </c>
       <c r="L18">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4216,13 +4216,13 @@
         <v>568</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4421,7 +4421,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4537,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4653,7 +4653,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4680,13 +4680,13 @@
         <v>568</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
         <v>160</v>
@@ -5144,13 +5144,13 @@
         <v>568</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5192,16 +5192,16 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -5233,7 +5233,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>133</v>
@@ -5465,10 +5465,10 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
         <v>163</v>
@@ -5492,13 +5492,13 @@
         <v>568</v>
       </c>
       <c r="L30">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5546,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="AD30">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>568</v>
       </c>
       <c r="L32">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="M32">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="N32">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5772,16 +5772,16 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -5813,10 +5813,10 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
         <v>166</v>
@@ -5840,13 +5840,13 @@
         <v>568</v>
       </c>
       <c r="L33">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5888,16 +5888,16 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -5929,10 +5929,10 @@
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
@@ -5956,13 +5956,13 @@
         <v>568</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -6045,7 +6045,7 @@
         <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
         <v>133</v>
@@ -6161,7 +6161,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
         <v>133</v>
@@ -6304,13 +6304,13 @@
         <v>568</v>
       </c>
       <c r="L37">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="M37">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="N37">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -6352,16 +6352,16 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC37">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD37">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE37">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
         <v>133</v>
@@ -6860,7 +6860,7 @@
         <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E42" t="s">
         <v>175</v>
@@ -6976,7 +6976,7 @@
         <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
         <v>176</v>
@@ -7089,7 +7089,7 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
         <v>133</v>
@@ -7208,7 +7208,7 @@
         <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E45" t="s">
         <v>178</v>
@@ -7321,7 +7321,7 @@
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
         <v>133</v>
@@ -7437,7 +7437,7 @@
         <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
         <v>133</v>
@@ -7464,13 +7464,13 @@
         <v>568</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -7556,7 +7556,7 @@
         <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E48" t="s">
         <v>181</v>
@@ -7669,7 +7669,7 @@
         <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
@@ -7785,7 +7785,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
         <v>133</v>
@@ -7904,7 +7904,7 @@
         <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -8017,7 +8017,7 @@
         <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
         <v>133</v>
@@ -8133,10 +8133,10 @@
         <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E53" t="s">
         <v>186</v>
@@ -8160,13 +8160,13 @@
         <v>568</v>
       </c>
       <c r="L53">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -8249,7 +8249,7 @@
         <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
@@ -8508,13 +8508,13 @@
         <v>568</v>
       </c>
       <c r="L56">
-        <v>8.699999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="M56">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="N56">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8556,16 +8556,16 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -8624,13 +8624,13 @@
         <v>568</v>
       </c>
       <c r="L57">
-        <v>2.38</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M57">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="N57">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8672,16 +8672,16 @@
         <v>0</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD57">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -8829,10 +8829,10 @@
         <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E59" t="s">
         <v>192</v>
@@ -8945,7 +8945,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
         <v>133</v>
@@ -8972,13 +8972,13 @@
         <v>568</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -9061,10 +9061,10 @@
         <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E61" t="s">
         <v>194</v>
@@ -9177,7 +9177,7 @@
         <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
         <v>133</v>
@@ -9320,13 +9320,13 @@
         <v>568</v>
       </c>
       <c r="L63">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -9368,10 +9368,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D64" t="s">
         <v>133</v>
@@ -9528,7 +9528,7 @@
         <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E65" t="s">
         <v>198</v>
@@ -9552,13 +9552,13 @@
         <v>568</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9641,7 +9641,7 @@
         <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
         <v>134</v>
@@ -9668,13 +9668,13 @@
         <v>568</v>
       </c>
       <c r="L66">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="M66">
-        <v>3.63</v>
+        <v>3.26</v>
       </c>
       <c r="N66">
-        <v>3.06</v>
+        <v>3.47</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AC66">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -9784,13 +9784,13 @@
         <v>568</v>
       </c>
       <c r="L67">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="M67">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="N67">
-        <v>3.47</v>
+        <v>2.92</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9832,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC67">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9900,13 +9900,13 @@
         <v>568</v>
       </c>
       <c r="L68">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="M68">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N68">
-        <v>2.63</v>
+        <v>3.59</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9948,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9989,10 +9989,10 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
         <v>202</v>
@@ -10016,13 +10016,13 @@
         <v>568</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10064,10 +10064,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -10132,13 +10132,13 @@
         <v>568</v>
       </c>
       <c r="L70">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="M70">
-        <v>3.01</v>
+        <v>3.36</v>
       </c>
       <c r="N70">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10180,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AC70">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD70">
         <v>0</v>
@@ -10221,7 +10221,7 @@
         <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D71" t="s">
         <v>134</v>
@@ -10248,13 +10248,13 @@
         <v>568</v>
       </c>
       <c r="L71">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="M71">
-        <v>3.23</v>
+        <v>3.01</v>
       </c>
       <c r="N71">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AC71">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -10364,13 +10364,13 @@
         <v>568</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10412,10 +10412,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -10453,7 +10453,7 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -10569,10 +10569,10 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E74" t="s">
         <v>207</v>
@@ -10685,7 +10685,7 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D75" t="s">
         <v>133</v>
@@ -10801,10 +10801,10 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D76" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E76" t="s">
         <v>209</v>
@@ -10828,13 +10828,13 @@
         <v>568</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10876,10 +10876,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10917,7 +10917,7 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D77" t="s">
         <v>134</v>
@@ -10944,13 +10944,13 @@
         <v>568</v>
       </c>
       <c r="L77">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="M77">
-        <v>4.7</v>
+        <v>3.03</v>
       </c>
       <c r="N77">
-        <v>8</v>
+        <v>3.34</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AC77">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -11060,13 +11060,13 @@
         <v>568</v>
       </c>
       <c r="L78">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="M78">
-        <v>3.79</v>
+        <v>3.06</v>
       </c>
       <c r="N78">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC78">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11149,10 +11149,10 @@
         <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D79" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E79" t="s">
         <v>212</v>
@@ -11176,13 +11176,13 @@
         <v>568</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D80" t="s">
         <v>134</v>
@@ -11292,13 +11292,13 @@
         <v>568</v>
       </c>
       <c r="L80">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="M80">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="N80">
-        <v>3.59</v>
+        <v>8</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11340,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC80">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -11381,7 +11381,7 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D81" t="s">
         <v>134</v>
@@ -11408,13 +11408,13 @@
         <v>568</v>
       </c>
       <c r="L81">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="M81">
         <v>3.45</v>
       </c>
       <c r="N81">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC81">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11524,13 +11524,13 @@
         <v>568</v>
       </c>
       <c r="L82">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="M82">
-        <v>3.06</v>
+        <v>3.45</v>
       </c>
       <c r="N82">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11572,10 +11572,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
+        <v>1.75</v>
+      </c>
+      <c r="AC82">
         <v>1.95</v>
-      </c>
-      <c r="AC82">
-        <v>1.85</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11613,7 +11613,7 @@
         <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D83" t="s">
         <v>134</v>
@@ -11640,13 +11640,13 @@
         <v>568</v>
       </c>
       <c r="L83">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="M83">
-        <v>3.32</v>
+        <v>3.79</v>
       </c>
       <c r="N83">
-        <v>2.92</v>
+        <v>3.89</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11688,10 +11688,10 @@
         <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC83">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11729,7 +11729,7 @@
         <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
         <v>134</v>
@@ -11756,13 +11756,13 @@
         <v>568</v>
       </c>
       <c r="L84">
-        <v>1.96</v>
+        <v>4.6</v>
       </c>
       <c r="M84">
-        <v>3.36</v>
+        <v>3.76</v>
       </c>
       <c r="N84">
-        <v>3.19</v>
+        <v>1.57</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC84">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D85" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E85" t="s">
         <v>218</v>
@@ -11872,13 +11872,13 @@
         <v>568</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11961,10 +11961,10 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D86" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E86" t="s">
         <v>219</v>
@@ -11988,13 +11988,13 @@
         <v>568</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -12077,10 +12077,10 @@
         <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E87" t="s">
         <v>220</v>
@@ -12104,13 +12104,13 @@
         <v>568</v>
       </c>
       <c r="L87">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -12152,10 +12152,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -12193,10 +12193,10 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E88" t="s">
         <v>221</v>
@@ -12309,7 +12309,7 @@
         <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D89" t="s">
         <v>133</v>
@@ -12425,7 +12425,7 @@
         <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
         <v>133</v>
@@ -12541,10 +12541,10 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E91" t="s">
         <v>224</v>
@@ -12568,13 +12568,13 @@
         <v>568</v>
       </c>
       <c r="L91">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="M91">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N91">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12616,10 +12616,10 @@
         <v>0</v>
       </c>
       <c r="AB91">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC91">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD91">
         <v>0</v>
@@ -12657,10 +12657,10 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E92" t="s">
         <v>225</v>
@@ -12684,13 +12684,13 @@
         <v>568</v>
       </c>
       <c r="L92">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M92">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N92">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12732,10 +12732,10 @@
         <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC92">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD92">
         <v>0</v>
@@ -12773,10 +12773,10 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E93" t="s">
         <v>226</v>
@@ -12889,10 +12889,10 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D94" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E94" t="s">
         <v>227</v>
@@ -12916,13 +12916,13 @@
         <v>568</v>
       </c>
       <c r="L94">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N94">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12964,10 +12964,10 @@
         <v>0</v>
       </c>
       <c r="AB94">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD94">
         <v>0</v>
@@ -13121,7 +13121,7 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s">
         <v>134</v>
@@ -13148,13 +13148,13 @@
         <v>568</v>
       </c>
       <c r="L96">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="M96">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="N96">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -13196,10 +13196,10 @@
         <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC96">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13237,7 +13237,7 @@
         <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D97" t="s">
         <v>134</v>
@@ -13264,13 +13264,13 @@
         <v>568</v>
       </c>
       <c r="L97">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="M97">
-        <v>3.76</v>
+        <v>3.32</v>
       </c>
       <c r="N97">
-        <v>1.57</v>
+        <v>3.79</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>0</v>
       </c>
       <c r="AB97">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AC97">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AD97">
         <v>0</v>
@@ -13353,7 +13353,7 @@
         <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D98" t="s">
         <v>134</v>
@@ -13380,13 +13380,13 @@
         <v>568</v>
       </c>
       <c r="L98">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M98">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N98">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC98">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD98">
         <v>0</v>
@@ -13469,7 +13469,7 @@
         <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D99" t="s">
         <v>134</v>
@@ -13496,13 +13496,13 @@
         <v>568</v>
       </c>
       <c r="L99">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="M99">
-        <v>3.61</v>
+        <v>3.34</v>
       </c>
       <c r="N99">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC99">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13585,7 +13585,7 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
         <v>134</v>
@@ -13612,13 +13612,13 @@
         <v>568</v>
       </c>
       <c r="L100">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M100">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N100">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13660,10 +13660,10 @@
         <v>0</v>
       </c>
       <c r="AB100">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC100">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13701,10 +13701,10 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E101" t="s">
         <v>234</v>
@@ -13728,13 +13728,13 @@
         <v>568</v>
       </c>
       <c r="L101">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M101">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N101">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC101">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13817,7 +13817,7 @@
         <v>53</v>
       </c>
       <c r="C102" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D102" t="s">
         <v>134</v>
@@ -13844,13 +13844,13 @@
         <v>568</v>
       </c>
       <c r="L102">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M102">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N102">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC102">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D103" t="s">
         <v>133</v>
@@ -14049,7 +14049,7 @@
         <v>53</v>
       </c>
       <c r="C104" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
         <v>134</v>
@@ -14076,13 +14076,13 @@
         <v>568</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD104">
         <v>0</v>
@@ -14165,7 +14165,7 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D105" t="s">
         <v>134</v>
@@ -14281,7 +14281,7 @@
         <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D106" t="s">
         <v>134</v>
@@ -14424,13 +14424,13 @@
         <v>568</v>
       </c>
       <c r="L107">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N107">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -14472,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="AB107">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC107">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD107">
         <v>0</v>
@@ -14629,10 +14629,10 @@
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D109" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E109" t="s">
         <v>242</v>
@@ -14861,7 +14861,7 @@
         <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D111" t="s">
         <v>134</v>
@@ -14977,7 +14977,7 @@
         <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D112" t="s">
         <v>134</v>
@@ -15093,7 +15093,7 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D113" t="s">
         <v>134</v>
@@ -15120,13 +15120,13 @@
         <v>568</v>
       </c>
       <c r="L113">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N113">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC113">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -15209,7 +15209,7 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D114" t="s">
         <v>134</v>
@@ -15325,7 +15325,7 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D115" t="s">
         <v>134</v>
@@ -15441,7 +15441,7 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D116" t="s">
         <v>134</v>
@@ -15468,13 +15468,13 @@
         <v>568</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -15516,10 +15516,10 @@
         <v>0</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD116">
         <v>0</v>
@@ -15557,7 +15557,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D117" t="s">
         <v>134</v>
@@ -15584,13 +15584,13 @@
         <v>568</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD117">
         <v>0</v>
@@ -15673,7 +15673,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D118" t="s">
         <v>134</v>
@@ -15700,13 +15700,13 @@
         <v>568</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M118">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15748,10 +15748,10 @@
         <v>0</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD118">
         <v>0</v>
@@ -15905,10 +15905,10 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E120" t="s">
         <v>253</v>
@@ -16021,10 +16021,10 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E121" t="s">
         <v>254</v>
@@ -16048,13 +16048,13 @@
         <v>568</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -16096,10 +16096,10 @@
         <v>0</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -16137,7 +16137,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D122" t="s">
         <v>134</v>
@@ -16164,13 +16164,13 @@
         <v>568</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -16253,7 +16253,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
@@ -16280,13 +16280,13 @@
         <v>568</v>
       </c>
       <c r="L123">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M123">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N123">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -16328,10 +16328,10 @@
         <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -16369,10 +16369,10 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E124" t="s">
         <v>257</v>
@@ -16396,13 +16396,13 @@
         <v>568</v>
       </c>
       <c r="L124">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M124">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N124">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -16444,10 +16444,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D125" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E125" t="s">
         <v>258</v>
@@ -16512,13 +16512,13 @@
         <v>568</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16560,10 +16560,10 @@
         <v>0</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD125">
         <v>0</v>
@@ -16601,7 +16601,7 @@
         <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D126" t="s">
         <v>134</v>
@@ -16628,13 +16628,13 @@
         <v>568</v>
       </c>
       <c r="L126">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N126">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16676,10 +16676,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16717,7 +16717,7 @@
         <v>55</v>
       </c>
       <c r="C127" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D127" t="s">
         <v>134</v>
@@ -16833,10 +16833,10 @@
         <v>55</v>
       </c>
       <c r="C128" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D128" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E128" t="s">
         <v>261</v>
@@ -16860,13 +16860,13 @@
         <v>568</v>
       </c>
       <c r="L128">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M128">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N128">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16908,10 +16908,10 @@
         <v>0</v>
       </c>
       <c r="AB128">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC128">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -17065,10 +17065,10 @@
         <v>56</v>
       </c>
       <c r="C130" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E130" t="s">
         <v>263</v>
@@ -17092,13 +17092,13 @@
         <v>568</v>
       </c>
       <c r="L130">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M130">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N130">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -17181,7 +17181,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -17208,13 +17208,13 @@
         <v>568</v>
       </c>
       <c r="L131">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="M131">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="N131">
-        <v>3.19</v>
+        <v>3.8</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17413,10 +17413,10 @@
         <v>56</v>
       </c>
       <c r="C133" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D133" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E133" t="s">
         <v>266</v>
@@ -17440,13 +17440,13 @@
         <v>568</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -17761,7 +17761,7 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D136" t="s">
         <v>134</v>
@@ -17788,13 +17788,13 @@
         <v>568</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17836,10 +17836,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17877,10 +17877,10 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D137" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E137" t="s">
         <v>270</v>
@@ -17993,7 +17993,7 @@
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D138" t="s">
         <v>134</v>
@@ -18020,13 +18020,13 @@
         <v>568</v>
       </c>
       <c r="L138">
-        <v>1.79</v>
+        <v>6</v>
       </c>
       <c r="M138">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="N138">
-        <v>3.47</v>
+        <v>1.43</v>
       </c>
       <c r="O138">
         <v>0</v>
@@ -18068,10 +18068,10 @@
         <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AC138">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="AD138">
         <v>0</v>
@@ -18109,10 +18109,10 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D139" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E139" t="s">
         <v>272</v>
@@ -18136,13 +18136,13 @@
         <v>568</v>
       </c>
       <c r="L139">
-        <v>3.39</v>
+        <v>1.75</v>
       </c>
       <c r="M139">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="N139">
-        <v>1.8</v>
+        <v>3.71</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -18184,10 +18184,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC139">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -18225,7 +18225,7 @@
         <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D140" t="s">
         <v>134</v>
@@ -18252,13 +18252,13 @@
         <v>568</v>
       </c>
       <c r="L140">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M140">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -18300,10 +18300,10 @@
         <v>0</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD140">
         <v>0</v>
@@ -18341,7 +18341,7 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D141" t="s">
         <v>134</v>
@@ -18368,13 +18368,13 @@
         <v>568</v>
       </c>
       <c r="L141">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M141">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N141">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC141">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18457,7 +18457,7 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D142" t="s">
         <v>133</v>
@@ -18484,13 +18484,13 @@
         <v>568</v>
       </c>
       <c r="L142">
-        <v>1.89</v>
+        <v>3.39</v>
       </c>
       <c r="M142">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="N142">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="O142">
         <v>0</v>
@@ -18532,10 +18532,10 @@
         <v>0</v>
       </c>
       <c r="AB142">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC142">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AD142">
         <v>0</v>
@@ -18573,10 +18573,10 @@
         <v>58</v>
       </c>
       <c r="C143" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D143" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
@@ -18600,13 +18600,13 @@
         <v>568</v>
       </c>
       <c r="L143">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="M143">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="N143">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -18648,10 +18648,10 @@
         <v>0</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD143">
         <v>0</v>
@@ -18689,10 +18689,10 @@
         <v>58</v>
       </c>
       <c r="C144" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E144" t="s">
         <v>277</v>
@@ -18716,13 +18716,13 @@
         <v>568</v>
       </c>
       <c r="L144">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M144">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N144">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -18764,10 +18764,10 @@
         <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC144">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD144">
         <v>0</v>
@@ -18805,7 +18805,7 @@
         <v>59</v>
       </c>
       <c r="C145" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D145" t="s">
         <v>134</v>
@@ -18921,10 +18921,10 @@
         <v>60</v>
       </c>
       <c r="C146" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D146" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E146" t="s">
         <v>279</v>
@@ -19037,10 +19037,10 @@
         <v>60</v>
       </c>
       <c r="C147" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E147" t="s">
         <v>280</v>
@@ -19153,10 +19153,10 @@
         <v>60</v>
       </c>
       <c r="C148" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D148" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E148" t="s">
         <v>281</v>
@@ -19180,13 +19180,13 @@
         <v>568</v>
       </c>
       <c r="L148">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M148">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -19228,16 +19228,16 @@
         <v>0</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF148">
         <v>0</v>
@@ -19269,10 +19269,10 @@
         <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D149" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E149" t="s">
         <v>282</v>
@@ -19296,13 +19296,13 @@
         <v>568</v>
       </c>
       <c r="L149">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M149">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N149">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -19344,16 +19344,16 @@
         <v>0</v>
       </c>
       <c r="AB149">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC149">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD149">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE149">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF149">
         <v>0</v>
@@ -19385,7 +19385,7 @@
         <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D150" t="s">
         <v>133</v>
@@ -19501,7 +19501,7 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D151" t="s">
         <v>134</v>
@@ -19528,13 +19528,13 @@
         <v>568</v>
       </c>
       <c r="L151">
-        <v>2.91</v>
+        <v>1.88</v>
       </c>
       <c r="M151">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="N151">
-        <v>2.23</v>
+        <v>3.94</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -19576,16 +19576,16 @@
         <v>0</v>
       </c>
       <c r="AB151">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC151">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF151">
         <v>0</v>
@@ -19617,7 +19617,7 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D152" t="s">
         <v>134</v>
@@ -19644,13 +19644,13 @@
         <v>568</v>
       </c>
       <c r="L152">
-        <v>4.88</v>
+        <v>6.9</v>
       </c>
       <c r="M152">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="N152">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19692,16 +19692,16 @@
         <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC152">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD152">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AE152">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF152">
         <v>0</v>
@@ -19733,7 +19733,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D153" t="s">
         <v>134</v>
@@ -19760,13 +19760,13 @@
         <v>568</v>
       </c>
       <c r="L153">
-        <v>1.88</v>
+        <v>4.88</v>
       </c>
       <c r="M153">
-        <v>3.74</v>
+        <v>4.24</v>
       </c>
       <c r="N153">
-        <v>3.94</v>
+        <v>1.63</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -19808,16 +19808,16 @@
         <v>0</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD153">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AE153">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF153">
         <v>0</v>
@@ -19849,10 +19849,10 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D154" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E154" t="s">
         <v>287</v>
@@ -19876,13 +19876,13 @@
         <v>568</v>
       </c>
       <c r="L154">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M154">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -19924,10 +19924,10 @@
         <v>0</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD154">
         <v>0</v>
@@ -19965,10 +19965,10 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D155" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E155" t="s">
         <v>288</v>
@@ -19992,13 +19992,13 @@
         <v>568</v>
       </c>
       <c r="L155">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="M155">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N155">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -20040,16 +20040,16 @@
         <v>0</v>
       </c>
       <c r="AB155">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC155">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD155">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE155">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF155">
         <v>0</v>
@@ -20105,7 +20105,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -20197,7 +20197,7 @@
         <v>63</v>
       </c>
       <c r="C157" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D157" t="s">
         <v>134</v>
@@ -20221,7 +20221,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -20313,7 +20313,7 @@
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D158" t="s">
         <v>134</v>
@@ -20429,7 +20429,7 @@
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="D159" t="s">
         <v>134</v>
@@ -20777,7 +20777,7 @@
         <v>63</v>
       </c>
       <c r="C162" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D162" t="s">
         <v>134</v>
@@ -21009,7 +21009,7 @@
         <v>64</v>
       </c>
       <c r="C164" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D164" t="s">
         <v>134</v>
@@ -21036,13 +21036,13 @@
         <v>568</v>
       </c>
       <c r="L164">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M164">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N164">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -21084,10 +21084,10 @@
         <v>0</v>
       </c>
       <c r="AB164">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC164">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD164">
         <v>0</v>
@@ -21125,7 +21125,7 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D165" t="s">
         <v>134</v>
@@ -21152,13 +21152,13 @@
         <v>568</v>
       </c>
       <c r="L165">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M165">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD165">
         <v>0</v>
@@ -21473,7 +21473,7 @@
         <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="D168" t="s">
         <v>134</v>
@@ -21500,13 +21500,13 @@
         <v>568</v>
       </c>
       <c r="L168">
-        <v>3.71</v>
+        <v>2.26</v>
       </c>
       <c r="M168">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N168">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -21548,10 +21548,10 @@
         <v>0</v>
       </c>
       <c r="AB168">
+        <v>1.57</v>
+      </c>
+      <c r="AC168">
         <v>2.15</v>
-      </c>
-      <c r="AC168">
-        <v>1.7</v>
       </c>
       <c r="AD168">
         <v>0</v>
@@ -21589,7 +21589,7 @@
         <v>65</v>
       </c>
       <c r="C169" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D169" t="s">
         <v>134</v>
@@ -21616,13 +21616,13 @@
         <v>568</v>
       </c>
       <c r="L169">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M169">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N169">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O169">
         <v>0</v>
@@ -21670,10 +21670,10 @@
         <v>0</v>
       </c>
       <c r="AD169">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE169">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF169">
         <v>0</v>
@@ -21705,7 +21705,7 @@
         <v>65</v>
       </c>
       <c r="C170" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D170" t="s">
         <v>134</v>
@@ -21732,13 +21732,13 @@
         <v>568</v>
       </c>
       <c r="L170">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="M170">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -21780,10 +21780,10 @@
         <v>0</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD170">
         <v>0</v>
@@ -21821,7 +21821,7 @@
         <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="D171" t="s">
         <v>134</v>
@@ -21848,13 +21848,13 @@
         <v>568</v>
       </c>
       <c r="L171">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="M171">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N171">
-        <v>2.83</v>
+        <v>6.8</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -21896,16 +21896,16 @@
         <v>0</v>
       </c>
       <c r="AB171">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC171">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD171">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE171">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF171">
         <v>0</v>
@@ -21937,7 +21937,7 @@
         <v>66</v>
       </c>
       <c r="C172" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D172" t="s">
         <v>134</v>
@@ -22169,7 +22169,7 @@
         <v>67</v>
       </c>
       <c r="C174" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D174" t="s">
         <v>133</v>
@@ -22178,7 +22178,7 @@
         <v>307</v>
       </c>
       <c r="F174" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -22196,13 +22196,13 @@
         <v>568</v>
       </c>
       <c r="L174">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M174">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N174">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O174">
         <v>0</v>
@@ -22244,10 +22244,10 @@
         <v>0</v>
       </c>
       <c r="AB174">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC174">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD174">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>67</v>
       </c>
       <c r="C175" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D175" t="s">
         <v>133</v>
@@ -22294,7 +22294,7 @@
         <v>308</v>
       </c>
       <c r="F175" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -22401,10 +22401,10 @@
         <v>67</v>
       </c>
       <c r="C176" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D176" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E176" t="s">
         <v>309</v>
@@ -22517,7 +22517,7 @@
         <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D177" t="s">
         <v>133</v>
@@ -22544,13 +22544,13 @@
         <v>568</v>
       </c>
       <c r="L177">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M177">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O177">
         <v>0</v>
@@ -22592,10 +22592,10 @@
         <v>0</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD177">
         <v>0</v>
@@ -22633,10 +22633,10 @@
         <v>67</v>
       </c>
       <c r="C178" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D178" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E178" t="s">
         <v>311</v>
@@ -24632,13 +24632,13 @@
         <v>568</v>
       </c>
       <c r="L195">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M195">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N195">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -24680,10 +24680,10 @@
         <v>0</v>
       </c>
       <c r="AB195">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC195">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD195">
         <v>0</v>
@@ -24721,7 +24721,7 @@
         <v>70</v>
       </c>
       <c r="C196" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D196" t="s">
         <v>133</v>
@@ -24837,7 +24837,7 @@
         <v>70</v>
       </c>
       <c r="C197" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D197" t="s">
         <v>133</v>
@@ -24864,13 +24864,13 @@
         <v>568</v>
       </c>
       <c r="L197">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M197">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -24912,10 +24912,10 @@
         <v>0</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD197">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>72</v>
       </c>
       <c r="C206" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D206" t="s">
         <v>133</v>
@@ -25997,7 +25997,7 @@
         <v>72</v>
       </c>
       <c r="C207" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D207" t="s">
         <v>133</v>
@@ -26113,7 +26113,7 @@
         <v>73</v>
       </c>
       <c r="C208" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D208" t="s">
         <v>133</v>
@@ -26229,7 +26229,7 @@
         <v>73</v>
       </c>
       <c r="C209" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D209" t="s">
         <v>133</v>
@@ -26256,13 +26256,13 @@
         <v>568</v>
       </c>
       <c r="L209">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M209">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O209">
         <v>0</v>
@@ -26304,10 +26304,10 @@
         <v>0</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD209">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>73</v>
       </c>
       <c r="C210" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D210" t="s">
         <v>133</v>
@@ -26372,13 +26372,13 @@
         <v>568</v>
       </c>
       <c r="L210">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M210">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N210">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -26420,10 +26420,10 @@
         <v>0</v>
       </c>
       <c r="AB210">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC210">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD210">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>74</v>
       </c>
       <c r="C211" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D211" t="s">
         <v>133</v>
@@ -26488,13 +26488,13 @@
         <v>568</v>
       </c>
       <c r="L211">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M211">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N211">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -26536,10 +26536,10 @@
         <v>0</v>
       </c>
       <c r="AB211">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC211">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD211">
         <v>0</v>
@@ -26693,7 +26693,7 @@
         <v>74</v>
       </c>
       <c r="C213" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D213" t="s">
         <v>133</v>
@@ -26720,13 +26720,13 @@
         <v>568</v>
       </c>
       <c r="L213">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M213">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O213">
         <v>0</v>
@@ -26768,10 +26768,10 @@
         <v>0</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD213">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -259,105 +259,105 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
-    <t>China Chinese Super League</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Ukraine Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Ukraine Ukrainian Premier League</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Scotland Championship</t>
   </si>
   <si>
     <t>England EFL League Two</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>Scotland Championship</t>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Russia Russian Premier League</t>
   </si>
   <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Russia Russian Premier League</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -367,18 +367,18 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -406,12 +406,12 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -445,474 +445,474 @@
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Fujieda MYFC</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
+    <t>JEF United</t>
+  </si>
+  <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
-    <t>Fujieda MYFC</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
+    <t>Karlsruher SC</t>
+  </si>
+  <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Samgurali</t>
   </si>
   <si>
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Shanghai Jiading</t>
+    <t>Elversberg</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
     <t>Paderborn</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
+    <t>Guangxi Baoyun</t>
   </si>
   <si>
     <t>Cardiff City</t>
   </si>
   <si>
-    <t>Guangxi Baoyun</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
     <t>Hoffenheim II</t>
   </si>
   <si>
-    <t>Kyzyl-Zhar</t>
+    <t>Waldhof Mannheim</t>
   </si>
   <si>
     <t>Ordabasy</t>
   </si>
   <si>
-    <t>Waldhof Mannheim</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Veres Rivne</t>
+  </si>
+  <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
-    <t>Veres Rivne</t>
-  </si>
-  <si>
     <t>Nieciecza</t>
   </si>
   <si>
     <t>Utsikten</t>
   </si>
   <si>
+    <t>Naftan</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Ufa</t>
+  </si>
+  <si>
     <t>Trelleborg</t>
   </si>
   <si>
-    <t>Ufa</t>
-  </si>
-  <si>
-    <t>Naftan</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Raith Rovers</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Termez Surkhon</t>
+  </si>
+  <si>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>Lincoln City</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Greenock Morton</t>
+  </si>
+  <si>
+    <t>Cambridge United</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Grimsby Town</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Shrewsbury Town</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Plymouth Argyle</t>
+  </si>
+  <si>
+    <t>Huddersfield Town</t>
+  </si>
+  <si>
+    <t>Airdrieonians</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Burton Albion</t>
   </si>
   <si>
     <t>Salford City</t>
   </si>
   <si>
-    <t>Barnet</t>
+    <t>St. Johnstone</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Colchester United</t>
   </si>
   <si>
     <t>Walsall</t>
   </si>
   <si>
-    <t>Blackpool</t>
-  </si>
-  <si>
-    <t>Plymouth Argyle</t>
-  </si>
-  <si>
-    <t>Lincoln City</t>
-  </si>
-  <si>
-    <t>Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Shrewsbury Town</t>
-  </si>
-  <si>
-    <t>KVC Westerlo</t>
-  </si>
-  <si>
-    <t>St. Johnstone</t>
-  </si>
-  <si>
-    <t>KuPS</t>
-  </si>
-  <si>
-    <t>Huddersfield Town</t>
-  </si>
-  <si>
-    <t>Colchester United</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Raith Rovers</t>
-  </si>
-  <si>
-    <t>Grimsby Town</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Milton Keynes Dons</t>
-  </si>
-  <si>
-    <t>Newport County</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Chesterfield</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Cambridge United</t>
-  </si>
-  <si>
-    <t>Bristol Rovers</t>
-  </si>
-  <si>
-    <t>Greenock Morton</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Airdrieonians</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Termez Surkhon</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
+    <t>MSV Duisburg</t>
   </si>
   <si>
     <t>KAMAZ</t>
   </si>
   <si>
-    <t>MSV Duisburg</t>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Levski Sofia</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Slavia</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
+    <t>Rostov</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Posusje</t>
   </si>
   <si>
     <t>Velež</t>
   </si>
   <si>
-    <t>Varaždin</t>
+    <t>Zorya</t>
   </si>
   <si>
     <t>Rudar Prijedor</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Zorya</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Rostov</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>Slavia</t>
-  </si>
-  <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Karviná</t>
+    <t>Widzew Łódź</t>
   </si>
   <si>
     <t>Mura</t>
   </si>
   <si>
+    <t>Argeș</t>
+  </si>
+  <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Widzew Łódź</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
     <t>Stal Rzeszów</t>
   </si>
   <si>
     <t>Diósgyőr</t>
   </si>
   <si>
+    <t>Oulu</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
     <t>Ružomberok</t>
   </si>
   <si>
-    <t>Zemplín Michalovce</t>
+    <t>Winterthur</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Oulu</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Olimpiyets</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
     <t>Krasnodar</t>
   </si>
   <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Olimpiyets</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
     <t>07 Vestur</t>
   </si>
   <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Ludogorets</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
     <t>Primorje</t>
   </si>
   <si>
@@ -922,121 +922,124 @@
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
-  </si>
-  <si>
-    <t>Basel</t>
+    <t>Sligo Rovers</t>
   </si>
   <si>
     <t>KAA Gent</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
+    <t>Novorizontino</t>
   </si>
   <si>
     <t>Cobreloa</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
+    <t>Osijek</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Osijek</t>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>All Boys</t>
   </si>
   <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Temperley</t>
   </si>
   <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
     <t>Colón</t>
   </si>
   <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>Santiago Morning</t>
   </si>
   <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Copiapó</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Concepción</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
+    <t>Forge FC</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
+    <t>Chattanooga FC</t>
   </si>
   <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
-    <t>Chattanooga FC</t>
+    <t>Carolina Core</t>
   </si>
   <si>
     <t>Amazonas</t>
@@ -1045,9 +1048,6 @@
     <t>North Carolina Courage</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
@@ -1096,474 +1096,474 @@
     <t>Montedio Yamagata</t>
   </si>
   <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
+    <t>Ehime</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Imabari</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Imabari</t>
-  </si>
-  <si>
-    <t>Ehime</t>
-  </si>
-  <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Gareji</t>
+  </si>
+  <si>
+    <t>Telavi</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Kolkheti Poti</t>
   </si>
   <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
+    <t>Nürnberg</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Gareji</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Telavi</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
+    <t>Shenzhen Juniors</t>
   </si>
   <si>
     <t>Peterborough United</t>
   </si>
   <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Saarbrucken</t>
+  </si>
+  <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
+    <t>Jahn Regensburg</t>
+  </si>
+  <si>
     <t>Havelse</t>
   </si>
   <si>
-    <t>Tobol</t>
+    <t>Verl</t>
   </si>
   <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Jahn Regensburg</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
-  </si>
-  <si>
-    <t>Saarbrucken</t>
-  </si>
-  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Dynamo Kyiv</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Minsk</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>Shinnik</t>
-  </si>
-  <si>
-    <t>Minsk</t>
-  </si>
-  <si>
     <t>Örgryte</t>
   </si>
   <si>
-    <t>Norrköping</t>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Queen's Park</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Dunfermline Athletic</t>
+  </si>
+  <si>
+    <t>Cheltenham Town</t>
+  </si>
+  <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Oldham Athletic</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>Mansfield Town</t>
   </si>
   <si>
     <t>Crewe Alexandra</t>
   </si>
   <si>
-    <t>Fleetwood Town</t>
+    <t>Partick Thistle</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Notts County</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Tranmere Rovers</t>
   </si>
   <si>
     <t>Swindon Town</t>
   </si>
   <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Barnsley</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Northampton Town</t>
-  </si>
-  <si>
-    <t>Bromley</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Partick Thistle</t>
-  </si>
-  <si>
-    <t>Haka</t>
-  </si>
-  <si>
-    <t>Leyton Orient</t>
-  </si>
-  <si>
-    <t>Tranmere Rovers</t>
-  </si>
-  <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
-    <t>Mansfield Town</t>
-  </si>
-  <si>
-    <t>Queen's Park</t>
-  </si>
-  <si>
-    <t>Crawley Town</t>
-  </si>
-  <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Oldham Athletic</t>
-  </si>
-  <si>
-    <t>Notts County</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Kokand-1912</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Cheltenham Town</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Dunfermline Athletic</t>
-  </si>
-  <si>
-    <t>Exeter City</t>
-  </si>
-  <si>
-    <t>Ross County</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Livingston</t>
+    <t>Stuttgart II</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
-    <t>Stuttgart II</t>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Isloch</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
+    <t>Krylya Sovetov</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
   </si>
   <si>
     <t>Borac Banja Luka</t>
   </si>
   <si>
-    <t>Gorica</t>
+    <t>LNZ Cherkasy</t>
   </si>
   <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>LNZ Cherkasy</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Krylya Sovetov</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
-    <t>Isloch</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Zlín</t>
+    <t>GKS Katowice</t>
   </si>
   <si>
     <t>Aluminij</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
     <t>GAIS</t>
   </si>
   <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>Jaro</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Brann</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
     <t>Skalica</t>
   </si>
   <si>
-    <t>Komárno</t>
+    <t>Young Boys</t>
   </si>
   <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Jaro</t>
-  </si>
-  <si>
-    <t>Brann</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Curicó Unido</t>
+  </si>
+  <si>
+    <t>La Serena</t>
+  </si>
+  <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
-    <t>Curicó Unido</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>La Serena</t>
-  </si>
-  <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
     <t>Dinamo Moskva</t>
   </si>
   <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
     <t>Víkingur</t>
   </si>
   <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
     <t>Radnički Niš</t>
   </si>
   <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
+    <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Górnik Zabrze</t>
-  </si>
-  <si>
     <t>Bravo</t>
   </si>
   <si>
@@ -1573,127 +1573,127 @@
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
     <t>Podbrezová</t>
   </si>
   <si>
-    <t>FCSB</t>
-  </si>
-  <si>
-    <t>Grasshopper</t>
+    <t>Shelbourne</t>
   </si>
   <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
     <t>Avaí</t>
   </si>
   <si>
     <t>Deportes Limache</t>
   </si>
   <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Patronato</t>
   </si>
   <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
     <t>Gimnasia Jujuy</t>
   </si>
   <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
     <t>San Telmo</t>
   </si>
   <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
     <t>América Mineiro</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
     <t>Recoleta</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
+    <t>Valour FC</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
   </si>
   <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
+    <t>New England II</t>
   </si>
   <si>
     <t>Goiás</t>
   </si>
   <si>
     <t>San Diego Wave</t>
-  </si>
-  <si>
-    <t>New England II</t>
   </si>
   <si>
     <t>Houston Dynamo FC II</t>
@@ -2244,13 +2244,13 @@
         <v>568</v>
       </c>
       <c r="L2">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="M2">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N2">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -2592,13 +2592,13 @@
         <v>568</v>
       </c>
       <c r="L5">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="M5">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N5">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -2640,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>568</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -3288,13 +3288,13 @@
         <v>568</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -3404,13 +3404,13 @@
         <v>568</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -3520,13 +3520,13 @@
         <v>568</v>
       </c>
       <c r="L13">
-        <v>1.93</v>
+        <v>3.18</v>
       </c>
       <c r="M13">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N13">
-        <v>3.35</v>
+        <v>2.09</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3568,10 +3568,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         <v>568</v>
       </c>
       <c r="L14">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="M14">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N14">
-        <v>2.08</v>
+        <v>2.77</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -3752,13 +3752,13 @@
         <v>568</v>
       </c>
       <c r="L15">
-        <v>1.46</v>
+        <v>4.9</v>
       </c>
       <c r="M15">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="N15">
-        <v>5.8</v>
+        <v>1.53</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3868,13 +3868,13 @@
         <v>568</v>
       </c>
       <c r="L16">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M16">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -3984,13 +3984,13 @@
         <v>568</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4032,10 +4032,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4100,13 +4100,13 @@
         <v>568</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4216,13 +4216,13 @@
         <v>568</v>
       </c>
       <c r="L19">
-        <v>4.9</v>
+        <v>3.23</v>
       </c>
       <c r="M19">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="N19">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4264,10 +4264,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4332,13 +4332,13 @@
         <v>568</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -4421,7 +4421,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4448,13 +4448,13 @@
         <v>568</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4564,13 +4564,13 @@
         <v>568</v>
       </c>
       <c r="L22">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4612,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4680,13 +4680,13 @@
         <v>568</v>
       </c>
       <c r="L23">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="M23">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="N23">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4728,10 +4728,10 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -4796,13 +4796,13 @@
         <v>568</v>
       </c>
       <c r="L24">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="M24">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N24">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4844,10 +4844,10 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC24">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
         <v>158</v>
@@ -4912,13 +4912,13 @@
         <v>568</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -5004,7 +5004,7 @@
         <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
         <v>159</v>
@@ -5028,13 +5028,13 @@
         <v>568</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>160</v>
@@ -5144,13 +5144,13 @@
         <v>568</v>
       </c>
       <c r="L27">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5192,16 +5192,16 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -5349,7 +5349,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
         <v>133</v>
@@ -5465,7 +5465,7 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>133</v>
@@ -5608,13 +5608,13 @@
         <v>568</v>
       </c>
       <c r="L31">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M31">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="N31">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5697,10 +5697,10 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
         <v>165</v>
@@ -5724,13 +5724,13 @@
         <v>568</v>
       </c>
       <c r="L32">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5778,10 +5778,10 @@
         <v>0</v>
       </c>
       <c r="AD32">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>133</v>
@@ -5932,7 +5932,7 @@
         <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
@@ -5956,13 +5956,13 @@
         <v>568</v>
       </c>
       <c r="L34">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
         <v>168</v>
@@ -6072,13 +6072,13 @@
         <v>568</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -6120,16 +6120,16 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
         <v>133</v>
@@ -6277,7 +6277,7 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
         <v>134</v>
@@ -6304,13 +6304,13 @@
         <v>568</v>
       </c>
       <c r="L37">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="M37">
-        <v>3.84</v>
+        <v>3.66</v>
       </c>
       <c r="N37">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -6352,16 +6352,16 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE37">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -6393,10 +6393,10 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
         <v>171</v>
@@ -6420,13 +6420,13 @@
         <v>568</v>
       </c>
       <c r="L38">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -6468,10 +6468,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -6509,10 +6509,10 @@
         <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
         <v>172</v>
@@ -6536,13 +6536,13 @@
         <v>568</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -6584,10 +6584,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -6625,7 +6625,7 @@
         <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
         <v>133</v>
@@ -6741,7 +6741,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
         <v>133</v>
@@ -6860,7 +6860,7 @@
         <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
         <v>175</v>
@@ -6973,7 +6973,7 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
         <v>133</v>
@@ -7089,7 +7089,7 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
         <v>133</v>
@@ -7208,7 +7208,7 @@
         <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E45" t="s">
         <v>178</v>
@@ -7321,7 +7321,7 @@
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
         <v>133</v>
@@ -7437,7 +7437,7 @@
         <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
         <v>133</v>
@@ -7464,13 +7464,13 @@
         <v>568</v>
       </c>
       <c r="L47">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -7556,7 +7556,7 @@
         <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E48" t="s">
         <v>181</v>
@@ -7669,10 +7669,10 @@
         <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E49" t="s">
         <v>182</v>
@@ -7696,13 +7696,13 @@
         <v>568</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -7788,7 +7788,7 @@
         <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E50" t="s">
         <v>183</v>
@@ -7904,7 +7904,7 @@
         <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -8020,7 +8020,7 @@
         <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E52" t="s">
         <v>185</v>
@@ -8133,7 +8133,7 @@
         <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s">
         <v>134</v>
@@ -8252,7 +8252,7 @@
         <v>89</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E54" t="s">
         <v>187</v>
@@ -8508,13 +8508,13 @@
         <v>568</v>
       </c>
       <c r="L56">
-        <v>2.38</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M56">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="N56">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8556,16 +8556,16 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD56">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -8624,13 +8624,13 @@
         <v>568</v>
       </c>
       <c r="L57">
-        <v>8.699999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="M57">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="N57">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8672,16 +8672,16 @@
         <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -8856,13 +8856,13 @@
         <v>568</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D60" t="s">
         <v>133</v>
@@ -8972,13 +8972,13 @@
         <v>568</v>
       </c>
       <c r="L60">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="M60">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N60">
-        <v>1.64</v>
+        <v>2.32</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC60">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -9061,10 +9061,10 @@
         <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E61" t="s">
         <v>194</v>
@@ -9088,13 +9088,13 @@
         <v>568</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -9142,10 +9142,10 @@
         <v>0</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF61">
         <v>0</v>
@@ -9177,10 +9177,10 @@
         <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E62" t="s">
         <v>195</v>
@@ -9204,13 +9204,13 @@
         <v>568</v>
       </c>
       <c r="L62">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -9320,13 +9320,13 @@
         <v>568</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -9368,10 +9368,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
         <v>133</v>
@@ -9436,13 +9436,13 @@
         <v>568</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -9528,7 +9528,7 @@
         <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E65" t="s">
         <v>198</v>
@@ -9552,13 +9552,13 @@
         <v>568</v>
       </c>
       <c r="L65">
-        <v>1.81</v>
+        <v>5.6</v>
       </c>
       <c r="M65">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="N65">
-        <v>3.45</v>
+        <v>1.46</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9641,10 +9641,10 @@
         <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E66" t="s">
         <v>199</v>
@@ -9668,13 +9668,13 @@
         <v>568</v>
       </c>
       <c r="L66">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M66">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="N66">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC66">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -9784,13 +9784,13 @@
         <v>568</v>
       </c>
       <c r="L67">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N67">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9832,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D68" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E68" t="s">
         <v>201</v>
@@ -9900,13 +9900,13 @@
         <v>568</v>
       </c>
       <c r="L68">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="M68">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N68">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9948,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9989,10 +9989,10 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E69" t="s">
         <v>202</v>
@@ -10016,13 +10016,13 @@
         <v>568</v>
       </c>
       <c r="L69">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="M69">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10064,10 +10064,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D70" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E70" t="s">
         <v>203</v>
@@ -10132,13 +10132,13 @@
         <v>568</v>
       </c>
       <c r="L70">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="M70">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="N70">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10180,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD70">
         <v>0</v>
@@ -10221,10 +10221,10 @@
         <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E71" t="s">
         <v>204</v>
@@ -10248,13 +10248,13 @@
         <v>568</v>
       </c>
       <c r="L71">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="M71">
-        <v>3.01</v>
+        <v>3.85</v>
       </c>
       <c r="N71">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC71">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -10364,13 +10364,13 @@
         <v>568</v>
       </c>
       <c r="L72">
-        <v>2.21</v>
+        <v>1.34</v>
       </c>
       <c r="M72">
-        <v>3.38</v>
+        <v>4.7</v>
       </c>
       <c r="N72">
-        <v>2.68</v>
+        <v>8</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10412,7 +10412,7 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC72">
         <v>1.91</v>
@@ -10453,7 +10453,7 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -10480,13 +10480,13 @@
         <v>568</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD73">
         <v>0</v>
@@ -10569,7 +10569,7 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -10596,13 +10596,13 @@
         <v>568</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10644,10 +10644,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10685,10 +10685,10 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
         <v>208</v>
@@ -10712,13 +10712,13 @@
         <v>568</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10760,10 +10760,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10801,10 +10801,10 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E76" t="s">
         <v>209</v>
@@ -10828,13 +10828,13 @@
         <v>568</v>
       </c>
       <c r="L76">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10876,10 +10876,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10917,7 +10917,7 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D77" t="s">
         <v>134</v>
@@ -10944,13 +10944,13 @@
         <v>568</v>
       </c>
       <c r="L77">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="M77">
-        <v>3.03</v>
+        <v>3.34</v>
       </c>
       <c r="N77">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11060,13 +11060,13 @@
         <v>568</v>
       </c>
       <c r="L78">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="M78">
-        <v>3.06</v>
+        <v>3.36</v>
       </c>
       <c r="N78">
-        <v>2.68</v>
+        <v>3.19</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC78">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11176,13 +11176,13 @@
         <v>568</v>
       </c>
       <c r="L79">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="M79">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N79">
-        <v>2.63</v>
+        <v>3.59</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC79">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D80" t="s">
         <v>134</v>
@@ -11292,13 +11292,13 @@
         <v>568</v>
       </c>
       <c r="L80">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N80">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11340,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -11381,7 +11381,7 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D81" t="s">
         <v>134</v>
@@ -11408,13 +11408,13 @@
         <v>568</v>
       </c>
       <c r="L81">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="M81">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N81">
-        <v>3.01</v>
+        <v>3.75</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AC81">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11497,10 +11497,10 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E82" t="s">
         <v>215</v>
@@ -11524,13 +11524,13 @@
         <v>568</v>
       </c>
       <c r="L82">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11572,10 +11572,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11613,7 +11613,7 @@
         <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D83" t="s">
         <v>134</v>
@@ -11640,58 +11640,58 @@
         <v>568</v>
       </c>
       <c r="L83">
+        <v>2.02</v>
+      </c>
+      <c r="M83">
+        <v>3.45</v>
+      </c>
+      <c r="N83">
+        <v>3.01</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+      <c r="AA83">
+        <v>0</v>
+      </c>
+      <c r="AB83">
         <v>1.67</v>
       </c>
-      <c r="M83">
-        <v>3.79</v>
-      </c>
-      <c r="N83">
-        <v>3.89</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>0</v>
-      </c>
-      <c r="R83">
-        <v>0</v>
-      </c>
-      <c r="S83">
-        <v>0</v>
-      </c>
-      <c r="T83">
-        <v>0</v>
-      </c>
-      <c r="U83">
-        <v>0</v>
-      </c>
-      <c r="V83">
-        <v>0</v>
-      </c>
-      <c r="W83">
-        <v>0</v>
-      </c>
-      <c r="X83">
-        <v>0</v>
-      </c>
-      <c r="Y83">
-        <v>0</v>
-      </c>
-      <c r="Z83">
-        <v>0</v>
-      </c>
-      <c r="AA83">
-        <v>0</v>
-      </c>
-      <c r="AB83">
-        <v>1.83</v>
-      </c>
       <c r="AC83">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11732,7 +11732,7 @@
         <v>98</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E84" t="s">
         <v>217</v>
@@ -11756,13 +11756,13 @@
         <v>568</v>
       </c>
       <c r="L84">
-        <v>4.6</v>
+        <v>1.66</v>
       </c>
       <c r="M84">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="N84">
-        <v>1.57</v>
+        <v>4</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11848,7 +11848,7 @@
         <v>98</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E85" t="s">
         <v>218</v>
@@ -11872,13 +11872,13 @@
         <v>568</v>
       </c>
       <c r="L85">
-        <v>2.74</v>
+        <v>1.39</v>
       </c>
       <c r="M85">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="N85">
-        <v>2.44</v>
+        <v>6.2</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D86" t="s">
         <v>134</v>
@@ -11988,13 +11988,13 @@
         <v>568</v>
       </c>
       <c r="L86">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="M86">
-        <v>3.61</v>
+        <v>3.26</v>
       </c>
       <c r="N86">
-        <v>4.5</v>
+        <v>3.47</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AC86">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -12080,7 +12080,7 @@
         <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E87" t="s">
         <v>220</v>
@@ -12104,13 +12104,13 @@
         <v>568</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -12152,10 +12152,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -12193,10 +12193,10 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D88" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E88" t="s">
         <v>221</v>
@@ -12220,13 +12220,13 @@
         <v>568</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -12268,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD88">
         <v>0</v>
@@ -12312,7 +12312,7 @@
         <v>102</v>
       </c>
       <c r="D89" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E89" t="s">
         <v>222</v>
@@ -12336,13 +12336,13 @@
         <v>568</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -12384,10 +12384,10 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD89">
         <v>0</v>
@@ -12425,10 +12425,10 @@
         <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D90" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E90" t="s">
         <v>223</v>
@@ -12452,13 +12452,13 @@
         <v>568</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -12500,10 +12500,10 @@
         <v>0</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD90">
         <v>0</v>
@@ -12541,10 +12541,10 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E91" t="s">
         <v>224</v>
@@ -12568,13 +12568,13 @@
         <v>568</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12616,10 +12616,10 @@
         <v>0</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD91">
         <v>0</v>
@@ -12657,10 +12657,10 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E92" t="s">
         <v>225</v>
@@ -12684,13 +12684,13 @@
         <v>568</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
         <v>133</v>
@@ -12889,10 +12889,10 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D94" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E94" t="s">
         <v>227</v>
@@ -12916,13 +12916,13 @@
         <v>568</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12964,10 +12964,10 @@
         <v>0</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD94">
         <v>0</v>
@@ -13008,7 +13008,7 @@
         <v>102</v>
       </c>
       <c r="D95" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E95" t="s">
         <v>228</v>
@@ -13032,13 +13032,13 @@
         <v>568</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD95">
         <v>0</v>
@@ -13121,7 +13121,7 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
         <v>134</v>
@@ -13148,13 +13148,13 @@
         <v>568</v>
       </c>
       <c r="L96">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="M96">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="N96">
-        <v>3.75</v>
+        <v>4.22</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -13196,10 +13196,10 @@
         <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13237,10 +13237,10 @@
         <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E97" t="s">
         <v>230</v>
@@ -13264,13 +13264,13 @@
         <v>568</v>
       </c>
       <c r="L97">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M97">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N97">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>0</v>
       </c>
       <c r="AB97">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC97">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD97">
         <v>0</v>
@@ -13353,7 +13353,7 @@
         <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D98" t="s">
         <v>134</v>
@@ -13380,13 +13380,13 @@
         <v>568</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD98">
         <v>0</v>
@@ -13469,7 +13469,7 @@
         <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D99" t="s">
         <v>134</v>
@@ -13496,13 +13496,13 @@
         <v>568</v>
       </c>
       <c r="L99">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M99">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="N99">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC99">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13585,7 +13585,7 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D100" t="s">
         <v>134</v>
@@ -13701,10 +13701,10 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D101" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E101" t="s">
         <v>234</v>
@@ -13728,13 +13728,13 @@
         <v>568</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13817,7 +13817,7 @@
         <v>53</v>
       </c>
       <c r="C102" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D102" t="s">
         <v>134</v>
@@ -13844,13 +13844,13 @@
         <v>568</v>
       </c>
       <c r="L102">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13933,10 +13933,10 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E103" t="s">
         <v>236</v>
@@ -13960,13 +13960,13 @@
         <v>568</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M103">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -14008,10 +14008,10 @@
         <v>0</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD103">
         <v>0</v>
@@ -14049,7 +14049,7 @@
         <v>53</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D104" t="s">
         <v>134</v>
@@ -14076,13 +14076,13 @@
         <v>568</v>
       </c>
       <c r="L104">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="M104">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="N104">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="AB104">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD104">
         <v>0</v>
@@ -14165,7 +14165,7 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D105" t="s">
         <v>134</v>
@@ -14281,7 +14281,7 @@
         <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D106" t="s">
         <v>134</v>
@@ -14513,10 +14513,10 @@
         <v>55</v>
       </c>
       <c r="C108" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E108" t="s">
         <v>241</v>
@@ -14629,7 +14629,7 @@
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D109" t="s">
         <v>134</v>
@@ -14656,13 +14656,13 @@
         <v>568</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD109">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D110" t="s">
         <v>134</v>
@@ -15093,7 +15093,7 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D113" t="s">
         <v>134</v>
@@ -15209,10 +15209,10 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D114" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E114" t="s">
         <v>247</v>
@@ -15236,13 +15236,13 @@
         <v>568</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M114">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -15284,10 +15284,10 @@
         <v>0</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD114">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D115" t="s">
         <v>134</v>
@@ -15352,13 +15352,13 @@
         <v>568</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -15400,10 +15400,10 @@
         <v>0</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD115">
         <v>0</v>
@@ -15441,10 +15441,10 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E116" t="s">
         <v>249</v>
@@ -15468,13 +15468,13 @@
         <v>568</v>
       </c>
       <c r="L116">
-        <v>2.39</v>
+        <v>1.66</v>
       </c>
       <c r="M116">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="N116">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -15516,10 +15516,10 @@
         <v>0</v>
       </c>
       <c r="AB116">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC116">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD116">
         <v>0</v>
@@ -15557,7 +15557,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D117" t="s">
         <v>134</v>
@@ -15584,13 +15584,13 @@
         <v>568</v>
       </c>
       <c r="L117">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N117">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="AB117">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC117">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD117">
         <v>0</v>
@@ -15673,7 +15673,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D118" t="s">
         <v>134</v>
@@ -15700,13 +15700,13 @@
         <v>568</v>
       </c>
       <c r="L118">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M118">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="N118">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D119" t="s">
         <v>134</v>
@@ -15905,10 +15905,10 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E120" t="s">
         <v>253</v>
@@ -16021,10 +16021,10 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D121" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E121" t="s">
         <v>254</v>
@@ -16048,13 +16048,13 @@
         <v>568</v>
       </c>
       <c r="L121">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="M121">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N121">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -16096,10 +16096,10 @@
         <v>0</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC121">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -16137,7 +16137,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D122" t="s">
         <v>134</v>
@@ -16164,13 +16164,13 @@
         <v>568</v>
       </c>
       <c r="L122">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N122">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -16253,7 +16253,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
@@ -16369,10 +16369,10 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D124" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E124" t="s">
         <v>257</v>
@@ -16485,7 +16485,7 @@
         <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D125" t="s">
         <v>134</v>
@@ -16512,13 +16512,13 @@
         <v>568</v>
       </c>
       <c r="L125">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M125">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N125">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16560,10 +16560,10 @@
         <v>0</v>
       </c>
       <c r="AB125">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD125">
         <v>0</v>
@@ -16601,7 +16601,7 @@
         <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D126" t="s">
         <v>134</v>
@@ -16717,7 +16717,7 @@
         <v>55</v>
       </c>
       <c r="C127" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D127" t="s">
         <v>134</v>
@@ -16744,13 +16744,13 @@
         <v>568</v>
       </c>
       <c r="L127">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M127">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16792,10 +16792,10 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD127">
         <v>0</v>
@@ -16833,7 +16833,7 @@
         <v>55</v>
       </c>
       <c r="C128" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D128" t="s">
         <v>134</v>
@@ -16949,7 +16949,7 @@
         <v>56</v>
       </c>
       <c r="C129" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D129" t="s">
         <v>134</v>
@@ -16976,13 +16976,13 @@
         <v>568</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -17065,10 +17065,10 @@
         <v>56</v>
       </c>
       <c r="C130" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E130" t="s">
         <v>263</v>
@@ -17181,7 +17181,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -17208,13 +17208,13 @@
         <v>568</v>
       </c>
       <c r="L131">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M131">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="N131">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17256,10 +17256,10 @@
         <v>0</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD131">
         <v>0</v>
@@ -17297,10 +17297,10 @@
         <v>56</v>
       </c>
       <c r="C132" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D132" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E132" t="s">
         <v>265</v>
@@ -17324,13 +17324,13 @@
         <v>568</v>
       </c>
       <c r="L132">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M132">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N132">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AB132">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC132">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD132">
         <v>0</v>
@@ -17645,10 +17645,10 @@
         <v>58</v>
       </c>
       <c r="C135" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D135" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E135" t="s">
         <v>268</v>
@@ -17672,13 +17672,13 @@
         <v>568</v>
       </c>
       <c r="L135">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17720,10 +17720,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17788,13 +17788,13 @@
         <v>568</v>
       </c>
       <c r="L136">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="M136">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N136">
-        <v>3.47</v>
+        <v>3.71</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17836,10 +17836,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC136">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17993,10 +17993,10 @@
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D138" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E138" t="s">
         <v>271</v>
@@ -18020,13 +18020,13 @@
         <v>568</v>
       </c>
       <c r="L138">
-        <v>6</v>
+        <v>2.41</v>
       </c>
       <c r="M138">
-        <v>3.97</v>
+        <v>3.39</v>
       </c>
       <c r="N138">
-        <v>1.43</v>
+        <v>2.44</v>
       </c>
       <c r="O138">
         <v>0</v>
@@ -18068,16 +18068,16 @@
         <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC138">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF138">
         <v>0</v>
@@ -18109,10 +18109,10 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D139" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E139" t="s">
         <v>272</v>
@@ -18136,13 +18136,13 @@
         <v>568</v>
       </c>
       <c r="L139">
-        <v>1.75</v>
+        <v>3.39</v>
       </c>
       <c r="M139">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="N139">
-        <v>3.71</v>
+        <v>1.8</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -18184,10 +18184,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -18225,7 +18225,7 @@
         <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D140" t="s">
         <v>134</v>
@@ -18252,58 +18252,58 @@
         <v>568</v>
       </c>
       <c r="L140">
+        <v>1.79</v>
+      </c>
+      <c r="M140">
+        <v>3.7</v>
+      </c>
+      <c r="N140">
+        <v>3.47</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>0</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="W140">
+        <v>0</v>
+      </c>
+      <c r="X140">
+        <v>0</v>
+      </c>
+      <c r="Y140">
+        <v>0</v>
+      </c>
+      <c r="Z140">
+        <v>0</v>
+      </c>
+      <c r="AA140">
+        <v>0</v>
+      </c>
+      <c r="AB140">
         <v>1.82</v>
       </c>
-      <c r="M140">
-        <v>3.5</v>
-      </c>
-      <c r="N140">
-        <v>3.53</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>1.56</v>
-      </c>
       <c r="AC140">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="AD140">
         <v>0</v>
@@ -18341,7 +18341,7 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D141" t="s">
         <v>134</v>
@@ -18368,13 +18368,13 @@
         <v>568</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18457,10 +18457,10 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D142" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E142" t="s">
         <v>275</v>
@@ -18484,13 +18484,13 @@
         <v>568</v>
       </c>
       <c r="L142">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M142">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N142">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O142">
         <v>0</v>
@@ -18532,10 +18532,10 @@
         <v>0</v>
       </c>
       <c r="AB142">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC142">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD142">
         <v>0</v>
@@ -18573,10 +18573,10 @@
         <v>58</v>
       </c>
       <c r="C143" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D143" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
@@ -18600,13 +18600,13 @@
         <v>568</v>
       </c>
       <c r="L143">
-        <v>1.89</v>
+        <v>6</v>
       </c>
       <c r="M143">
-        <v>3.26</v>
+        <v>3.97</v>
       </c>
       <c r="N143">
-        <v>3.53</v>
+        <v>1.43</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -18648,10 +18648,10 @@
         <v>0</v>
       </c>
       <c r="AB143">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AC143">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="AD143">
         <v>0</v>
@@ -18689,10 +18689,10 @@
         <v>58</v>
       </c>
       <c r="C144" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D144" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E144" t="s">
         <v>277</v>
@@ -18716,13 +18716,13 @@
         <v>568</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M144">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -18805,7 +18805,7 @@
         <v>59</v>
       </c>
       <c r="C145" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D145" t="s">
         <v>134</v>
@@ -18921,7 +18921,7 @@
         <v>60</v>
       </c>
       <c r="C146" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D146" t="s">
         <v>134</v>
@@ -18948,13 +18948,13 @@
         <v>568</v>
       </c>
       <c r="L146">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M146">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O146">
         <v>0</v>
@@ -18996,16 +18996,16 @@
         <v>0</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF146">
         <v>0</v>
@@ -19153,10 +19153,10 @@
         <v>60</v>
       </c>
       <c r="C148" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D148" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E148" t="s">
         <v>281</v>
@@ -19180,13 +19180,13 @@
         <v>568</v>
       </c>
       <c r="L148">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M148">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N148">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -19228,16 +19228,16 @@
         <v>0</v>
       </c>
       <c r="AB148">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC148">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD148">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE148">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF148">
         <v>0</v>
@@ -19269,10 +19269,10 @@
         <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="D149" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E149" t="s">
         <v>282</v>
@@ -19385,7 +19385,7 @@
         <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D150" t="s">
         <v>133</v>
@@ -19501,7 +19501,7 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D151" t="s">
         <v>134</v>
@@ -19528,13 +19528,13 @@
         <v>568</v>
       </c>
       <c r="L151">
-        <v>1.88</v>
+        <v>4.8</v>
       </c>
       <c r="M151">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N151">
-        <v>3.94</v>
+        <v>1.63</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -19576,16 +19576,16 @@
         <v>0</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD151">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AE151">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF151">
         <v>0</v>
@@ -19617,7 +19617,7 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D152" t="s">
         <v>134</v>
@@ -19644,13 +19644,13 @@
         <v>568</v>
       </c>
       <c r="L152">
-        <v>6.9</v>
+        <v>2.91</v>
       </c>
       <c r="M152">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="N152">
-        <v>1.34</v>
+        <v>2.23</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19692,16 +19692,16 @@
         <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC152">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD152">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE152">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF152">
         <v>0</v>
@@ -19733,7 +19733,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D153" t="s">
         <v>134</v>
@@ -19760,13 +19760,13 @@
         <v>568</v>
       </c>
       <c r="L153">
-        <v>4.88</v>
+        <v>6.9</v>
       </c>
       <c r="M153">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="N153">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -19808,16 +19808,16 @@
         <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC153">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD153">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AE153">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF153">
         <v>0</v>
@@ -19849,7 +19849,7 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D154" t="s">
         <v>134</v>
@@ -19876,13 +19876,13 @@
         <v>568</v>
       </c>
       <c r="L154">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="M154">
-        <v>3.05</v>
+        <v>3.51</v>
       </c>
       <c r="N154">
-        <v>2.23</v>
+        <v>3.61</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -19924,16 +19924,16 @@
         <v>0</v>
       </c>
       <c r="AB154">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC154">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF154">
         <v>0</v>
@@ -20081,7 +20081,7 @@
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D156" t="s">
         <v>134</v>
@@ -20105,7 +20105,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -20197,7 +20197,7 @@
         <v>63</v>
       </c>
       <c r="C157" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D157" t="s">
         <v>134</v>
@@ -20777,7 +20777,7 @@
         <v>63</v>
       </c>
       <c r="C162" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D162" t="s">
         <v>134</v>
@@ -20801,7 +20801,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -21009,7 +21009,7 @@
         <v>64</v>
       </c>
       <c r="C164" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D164" t="s">
         <v>134</v>
@@ -21036,13 +21036,13 @@
         <v>568</v>
       </c>
       <c r="L164">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M164">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -21084,10 +21084,10 @@
         <v>0</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD164">
         <v>0</v>
@@ -21125,7 +21125,7 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D165" t="s">
         <v>134</v>
@@ -21152,13 +21152,13 @@
         <v>568</v>
       </c>
       <c r="L165">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M165">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="N165">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="AB165">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC165">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD165">
         <v>0</v>
@@ -21473,7 +21473,7 @@
         <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D168" t="s">
         <v>134</v>
@@ -21589,7 +21589,7 @@
         <v>65</v>
       </c>
       <c r="C169" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D169" t="s">
         <v>134</v>
@@ -21616,13 +21616,13 @@
         <v>568</v>
       </c>
       <c r="L169">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M169">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O169">
         <v>0</v>
@@ -21670,10 +21670,10 @@
         <v>0</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF169">
         <v>0</v>
@@ -21821,7 +21821,7 @@
         <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D171" t="s">
         <v>134</v>
@@ -21848,13 +21848,13 @@
         <v>568</v>
       </c>
       <c r="L171">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M171">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N171">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -21902,10 +21902,10 @@
         <v>0</v>
       </c>
       <c r="AD171">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE171">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF171">
         <v>0</v>
@@ -21937,10 +21937,10 @@
         <v>66</v>
       </c>
       <c r="C172" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E172" t="s">
         <v>305</v>
@@ -21964,13 +21964,13 @@
         <v>568</v>
       </c>
       <c r="L172">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M172">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O172">
         <v>0</v>
@@ -22053,10 +22053,10 @@
         <v>66</v>
       </c>
       <c r="C173" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D173" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E173" t="s">
         <v>306</v>
@@ -22169,7 +22169,7 @@
         <v>67</v>
       </c>
       <c r="C174" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D174" t="s">
         <v>133</v>
@@ -22178,7 +22178,7 @@
         <v>307</v>
       </c>
       <c r="F174" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>67</v>
       </c>
       <c r="C175" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D175" t="s">
         <v>133</v>
@@ -22294,7 +22294,7 @@
         <v>308</v>
       </c>
       <c r="F175" t="s">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -22517,10 +22517,10 @@
         <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D177" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E177" t="s">
         <v>310</v>
@@ -22544,13 +22544,13 @@
         <v>568</v>
       </c>
       <c r="L177">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M177">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N177">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O177">
         <v>0</v>
@@ -22592,10 +22592,10 @@
         <v>0</v>
       </c>
       <c r="AB177">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC177">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD177">
         <v>0</v>
@@ -22633,10 +22633,10 @@
         <v>67</v>
       </c>
       <c r="C178" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D178" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E178" t="s">
         <v>311</v>
@@ -22660,13 +22660,13 @@
         <v>568</v>
       </c>
       <c r="L178">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M178">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O178">
         <v>0</v>
@@ -22708,10 +22708,10 @@
         <v>0</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD178">
         <v>0</v>
@@ -24721,7 +24721,7 @@
         <v>70</v>
       </c>
       <c r="C196" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D196" t="s">
         <v>133</v>
@@ -24748,13 +24748,13 @@
         <v>568</v>
       </c>
       <c r="L196">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M196">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O196">
         <v>0</v>
@@ -24796,10 +24796,10 @@
         <v>0</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD196">
         <v>0</v>
@@ -24837,7 +24837,7 @@
         <v>70</v>
       </c>
       <c r="C197" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D197" t="s">
         <v>133</v>
@@ -24864,13 +24864,13 @@
         <v>568</v>
       </c>
       <c r="L197">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M197">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N197">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -24912,10 +24912,10 @@
         <v>0</v>
       </c>
       <c r="AB197">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC197">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD197">
         <v>0</v>
@@ -25765,7 +25765,7 @@
         <v>72</v>
       </c>
       <c r="C205" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D205" t="s">
         <v>133</v>
@@ -25881,7 +25881,7 @@
         <v>72</v>
       </c>
       <c r="C206" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D206" t="s">
         <v>133</v>
@@ -25997,7 +25997,7 @@
         <v>72</v>
       </c>
       <c r="C207" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D207" t="s">
         <v>133</v>
@@ -26024,13 +26024,13 @@
         <v>568</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M207">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O207">
         <v>0</v>
@@ -26072,10 +26072,10 @@
         <v>0</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD207">
         <v>0</v>
@@ -26113,7 +26113,7 @@
         <v>73</v>
       </c>
       <c r="C208" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D208" t="s">
         <v>133</v>
@@ -26229,7 +26229,7 @@
         <v>73</v>
       </c>
       <c r="C209" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D209" t="s">
         <v>133</v>
@@ -26256,13 +26256,13 @@
         <v>568</v>
       </c>
       <c r="L209">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M209">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N209">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O209">
         <v>0</v>
@@ -26304,10 +26304,10 @@
         <v>0</v>
       </c>
       <c r="AB209">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC209">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD209">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>73</v>
       </c>
       <c r="C210" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D210" t="s">
         <v>133</v>
@@ -26372,13 +26372,13 @@
         <v>568</v>
       </c>
       <c r="L210">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M210">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -26420,10 +26420,10 @@
         <v>0</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD210">
         <v>0</v>
@@ -26577,7 +26577,7 @@
         <v>74</v>
       </c>
       <c r="C212" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D212" t="s">
         <v>133</v>
@@ -26604,13 +26604,13 @@
         <v>568</v>
       </c>
       <c r="L212">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M212">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -26925,7 +26925,7 @@
         <v>76</v>
       </c>
       <c r="C215" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D215" t="s">
         <v>133</v>
@@ -26952,13 +26952,13 @@
         <v>568</v>
       </c>
       <c r="L215">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M215">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -27000,10 +27000,10 @@
         <v>0</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD215">
         <v>0</v>
@@ -27041,7 +27041,7 @@
         <v>76</v>
       </c>
       <c r="C216" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D216" t="s">
         <v>133</v>
@@ -27068,13 +27068,13 @@
         <v>568</v>
       </c>
       <c r="L216">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M216">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O216">
         <v>0</v>
@@ -27273,7 +27273,7 @@
         <v>78</v>
       </c>
       <c r="C218" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D218" t="s">
         <v>133</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -259,27 +259,27 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
-    <t>China China League One</t>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
@@ -289,15 +289,15 @@
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Ukraine Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Ukraine Ukrainian Premier League</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -313,69 +313,69 @@
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>England EFL League Two</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
+    <t>Scotland Championship</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
-    <t>England EFL League Two</t>
-  </si>
-  <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
-    <t>Iceland Úrvalsdeild</t>
+    <t>Russia Russian Premier League</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Russia Russian Premier League</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Slovakia Super Liga</t>
-  </si>
-  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
@@ -406,12 +406,12 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -433,417 +433,417 @@
     <t>Kataller Toyama</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
     <t>V-Varen Nagasaki</t>
   </si>
   <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>St George City FA</t>
   </si>
   <si>
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
+    <t>Gyeongnam</t>
   </si>
   <si>
     <t>Fujieda MYFC</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Paderborn</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>Darmstadt 98</t>
-  </si>
-  <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
     <t>Cardiff City</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
     <t>Astana</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Aktobe</t>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
   </si>
   <si>
     <t>Zhetysu</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Osnabrück</t>
   </si>
   <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Hoffenheim II</t>
-  </si>
-  <si>
-    <t>Waldhof Mannheim</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
+    <t>Veres Rivne</t>
+  </si>
+  <si>
+    <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Veres Rivne</t>
-  </si>
-  <si>
-    <t>Schwarz-Weiß Bregenz</t>
-  </si>
-  <si>
     <t>Nieciecza</t>
   </si>
   <si>
+    <t>Naftan</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>Utsikten</t>
   </si>
   <si>
-    <t>Naftan</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Ufa</t>
   </si>
   <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Shrewsbury Town</t>
+  </si>
+  <si>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Termez Surkhon</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Newport County</t>
+  </si>
+  <si>
     <t>Åsane</t>
   </si>
   <si>
+    <t>Salford City</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Huddersfield Town</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Lincoln City</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Grimsby Town</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>Airdrieonians</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Cambridge United</t>
+  </si>
+  <si>
+    <t>Raith Rovers</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
     <t>Tromsø</t>
   </si>
   <si>
-    <t>KVC Westerlo</t>
+    <t>Greenock Morton</t>
+  </si>
+  <si>
+    <t>Colchester United</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Aalesund</t>
   </si>
   <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Raith Rovers</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Termez Surkhon</t>
+    <t>Burton Albion</t>
   </si>
   <si>
     <t>Doncaster Rovers</t>
   </si>
   <si>
-    <t>Lincoln City</t>
-  </si>
-  <si>
-    <t>Blackpool</t>
-  </si>
-  <si>
-    <t>Greenock Morton</t>
-  </si>
-  <si>
-    <t>Cambridge United</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Grimsby Town</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Barnet</t>
-  </si>
-  <si>
-    <t>Shrewsbury Town</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Milton Keynes Dons</t>
-  </si>
-  <si>
     <t>Plymouth Argyle</t>
   </si>
   <si>
-    <t>Huddersfield Town</t>
-  </si>
-  <si>
-    <t>Airdrieonians</t>
-  </si>
-  <si>
-    <t>KuPS</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Salford City</t>
-  </si>
-  <si>
     <t>St. Johnstone</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Newport County</t>
-  </si>
-  <si>
-    <t>Bristol Rovers</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Chesterfield</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>Colchester United</t>
-  </si>
-  <si>
-    <t>Walsall</t>
+    <t>KAMAZ</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
-    <t>KAMAZ</t>
+    <t>Rostov</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Slavia</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Teplice</t>
   </si>
   <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
     <t>Sogdiana</t>
   </si>
   <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Slavia</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Varaždin</t>
-  </si>
-  <si>
-    <t>Rostov</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Zorya</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Mura</t>
   </si>
   <si>
     <t>Widzew Łódź</t>
   </si>
   <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Argeș</t>
+    <t>Stal Rzeszów</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
     <t>Diósgyőr</t>
   </si>
   <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
     <t>Oulu</t>
   </si>
   <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Zemplín Michalovce</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
     <t>Winterthur</t>
   </si>
   <si>
@@ -853,34 +853,43 @@
     <t>Standard Liège</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
     <t>Olimpiyets</t>
   </si>
   <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Krasnodar</t>
-  </si>
-  <si>
-    <t>07 Vestur</t>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
   </si>
   <si>
     <t>Sigma Olomouc</t>
@@ -889,7 +898,7 @@
     <t>Austria Wien II</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
+    <t>Vojvodina</t>
   </si>
   <si>
     <t>OFK Beograd</t>
@@ -898,21 +907,12 @@
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
+    <t>Ludogorets</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Ludogorets</t>
-  </si>
-  <si>
     <t>Primorje</t>
   </si>
   <si>
@@ -940,132 +940,132 @@
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
     <t>Cobreloa</t>
   </si>
   <si>
-    <t>Coquimbo Unido</t>
-  </si>
-  <si>
-    <t>Osijek</t>
-  </si>
-  <si>
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
     <t>Alvarado</t>
   </si>
   <si>
-    <t>All Boys</t>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
   </si>
   <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Santiago Morning</t>
   </si>
   <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
+    <t>Concepción</t>
   </si>
   <si>
     <t>Copiapó</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Concepción</t>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
   </si>
   <si>
     <t>Forge FC</t>
   </si>
   <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
-    <t>North Carolina Courage</t>
+    <t>Louisville City</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
   </si>
   <si>
     <t>Minnesota United II</t>
   </si>
   <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>North Texas</t>
   </si>
   <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>El Paso Locomotive</t>
   </si>
   <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
@@ -1084,417 +1084,417 @@
     <t>Omiya Ardija</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
     <t>Vegalta Sendai</t>
   </si>
   <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
     <t>Sutherland Sharks</t>
   </si>
   <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Ehime</t>
+  </si>
+  <si>
+    <t>Imabari</t>
+  </si>
+  <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Seongnam</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
+    <t>Busan I'Park</t>
   </si>
   <si>
     <t>Renofa Yamaguchi</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Ehime</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Imabari</t>
-  </si>
-  <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
+    <t>Kolkheti Poti</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Gareji</t>
+  </si>
+  <si>
+    <t>Telavi</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Preußen Münster</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Gareji</t>
-  </si>
-  <si>
-    <t>Telavi</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Kolkheti Poti</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
     <t>Peterborough United</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Jahn Regensburg</t>
+  </si>
+  <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
-    <t>Zhenys</t>
+    <t>Havelse</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Saarbrucken</t>
   </si>
   <si>
     <t>Turan Turkistan</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Saarbrucken</t>
-  </si>
-  <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Alemannia Aachen</t>
   </si>
   <si>
-    <t>Jahn Regensburg</t>
-  </si>
-  <si>
-    <t>Havelse</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
+    <t>Rapid Wien II</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Dynamo Kyiv</t>
-  </si>
-  <si>
-    <t>Rapid Wien II</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
+    <t>Minsk</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
-    <t>Minsk</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Shinnik</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
     <t>Örgryte</t>
   </si>
   <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Notts County</t>
+  </si>
+  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
+    <t>Crewe Alexandra</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Oldham Athletic</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Swindon Town</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>Cheltenham Town</t>
+  </si>
+  <si>
+    <t>Queen's Park</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
-    <t>Zulte-Waregem</t>
+    <t>Dunfermline Athletic</t>
+  </si>
+  <si>
+    <t>Tranmere Rovers</t>
+  </si>
+  <si>
+    <t>Lyn</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Queen's Park</t>
-  </si>
-  <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>Northampton Town</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
+    <t>Mansfield Town</t>
   </si>
   <si>
     <t>Exeter City</t>
   </si>
   <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Dunfermline Athletic</t>
-  </si>
-  <si>
-    <t>Cheltenham Town</t>
-  </si>
-  <si>
-    <t>Kokand-1912</t>
-  </si>
-  <si>
-    <t>Crawley Town</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Fleetwood Town</t>
-  </si>
-  <si>
-    <t>Bromley</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Oldham Athletic</t>
-  </si>
-  <si>
     <t>Barnsley</t>
   </si>
   <si>
-    <t>Leyton Orient</t>
-  </si>
-  <si>
-    <t>Ross County</t>
-  </si>
-  <si>
-    <t>Haka</t>
-  </si>
-  <si>
-    <t>Mansfield Town</t>
-  </si>
-  <si>
-    <t>Crewe Alexandra</t>
-  </si>
-  <si>
     <t>Partick Thistle</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Notts County</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
-    <t>Tranmere Rovers</t>
-  </si>
-  <si>
-    <t>Swindon Town</t>
+    <t>Chelyabinsk</t>
   </si>
   <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>Chelyabinsk</t>
+    <t>Krylya Sovetov</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Isloch</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>LNZ Cherkasy</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
   </si>
   <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
     <t>Nasaf</t>
   </si>
   <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Isloch</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>Krylya Sovetov</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>LNZ Cherkasy</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Aluminij</t>
   </si>
   <si>
     <t>GKS Katowice</t>
   </si>
   <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>GAIS</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Brann</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Skalica</t>
+  </si>
+  <si>
     <t>Jaro</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Brann</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Komárno</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Skalica</t>
-  </si>
-  <si>
     <t>Young Boys</t>
   </si>
   <si>
@@ -1504,34 +1504,43 @@
     <t>FCV Dender EH</t>
   </si>
   <si>
+    <t>Curicó Unido</t>
+  </si>
+  <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Curicó Unido</t>
-  </si>
-  <si>
     <t>La Serena</t>
   </si>
   <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Dinamo Moskva</t>
+  </si>
+  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Dinamo Moskva</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
   </si>
   <si>
     <t>Slovan Liberec</t>
@@ -1540,7 +1549,7 @@
     <t>St. Pölten</t>
   </si>
   <si>
-    <t>IMT Novi Beograd</t>
+    <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Javor Ivanjica</t>
@@ -1549,21 +1558,12 @@
     <t>Spartak Subotica</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
+    <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Bravo</t>
   </si>
   <si>
@@ -1591,127 +1591,127 @@
     <t>Avaí</t>
   </si>
   <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
     <t>Bahia</t>
   </si>
   <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
     <t>Club Atlético Güemes</t>
   </si>
   <si>
-    <t>Patronato</t>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Universidad Católica</t>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
   </si>
   <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
+    <t>Deportes Santa Cruz</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
   </si>
   <si>
     <t>Valour FC</t>
   </si>
   <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
+    <t>San Diego Wave</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>San Diego Wave</t>
+    <t>North Carolina FC</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
   </si>
   <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>North Carolina FC</t>
-  </si>
-  <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
+    <t>Sacramento Republic</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
-  </si>
-  <si>
-    <t>Sacramento Republic</t>
   </si>
   <si>
     <t>Houston Dash</t>
@@ -2681,7 +2681,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -2708,13 +2708,13 @@
         <v>568</v>
       </c>
       <c r="L6">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -2824,13 +2824,13 @@
         <v>568</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>568</v>
       </c>
       <c r="L10">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="N10">
-        <v>3.51</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -3288,13 +3288,13 @@
         <v>568</v>
       </c>
       <c r="L11">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="M11">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="N11">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -3404,13 +3404,13 @@
         <v>568</v>
       </c>
       <c r="L12">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="M12">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="N12">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -3520,13 +3520,13 @@
         <v>568</v>
       </c>
       <c r="L13">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         <v>568</v>
       </c>
       <c r="L14">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="M14">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="N14">
-        <v>2.77</v>
+        <v>3.03</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -3752,13 +3752,13 @@
         <v>568</v>
       </c>
       <c r="L15">
-        <v>4.9</v>
+        <v>3.18</v>
       </c>
       <c r="M15">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="N15">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3868,13 +3868,13 @@
         <v>568</v>
       </c>
       <c r="L16">
-        <v>1.64</v>
+        <v>4.9</v>
       </c>
       <c r="M16">
-        <v>3.67</v>
+        <v>4.6</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -3984,13 +3984,13 @@
         <v>568</v>
       </c>
       <c r="L17">
-        <v>2.07</v>
+        <v>3.41</v>
       </c>
       <c r="M17">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="N17">
-        <v>3.03</v>
+        <v>1.88</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4032,10 +4032,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4100,13 +4100,13 @@
         <v>568</v>
       </c>
       <c r="L18">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="M18">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="N18">
-        <v>4.6</v>
+        <v>2.54</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4216,13 +4216,13 @@
         <v>568</v>
       </c>
       <c r="L19">
-        <v>3.23</v>
+        <v>2.57</v>
       </c>
       <c r="M19">
-        <v>3.38</v>
+        <v>3.03</v>
       </c>
       <c r="N19">
-        <v>1.94</v>
+        <v>2.49</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4264,10 +4264,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4332,13 +4332,13 @@
         <v>568</v>
       </c>
       <c r="L20">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="M20">
-        <v>3.26</v>
+        <v>4.3</v>
       </c>
       <c r="N20">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -4421,7 +4421,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4448,13 +4448,13 @@
         <v>568</v>
       </c>
       <c r="L21">
-        <v>2.86</v>
+        <v>1.88</v>
       </c>
       <c r="M21">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="N21">
-        <v>2.37</v>
+        <v>3.51</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4564,13 +4564,13 @@
         <v>568</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4612,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4680,13 +4680,13 @@
         <v>568</v>
       </c>
       <c r="L23">
-        <v>3.41</v>
+        <v>2.36</v>
       </c>
       <c r="M23">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="N23">
-        <v>1.88</v>
+        <v>2.77</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4728,10 +4728,10 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
         <v>158</v>
@@ -4912,13 +4912,13 @@
         <v>568</v>
       </c>
       <c r="L25">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4960,10 +4960,10 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -5004,7 +5004,7 @@
         <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
         <v>159</v>
@@ -5028,13 +5028,13 @@
         <v>568</v>
       </c>
       <c r="L26">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -5117,7 +5117,7 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
         <v>133</v>
@@ -5144,13 +5144,13 @@
         <v>568</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5192,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -5233,7 +5233,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
         <v>133</v>
@@ -5349,10 +5349,10 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
         <v>162</v>
@@ -5376,13 +5376,13 @@
         <v>568</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -5424,16 +5424,16 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF29">
         <v>0</v>
@@ -5465,10 +5465,10 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
         <v>163</v>
@@ -5492,13 +5492,13 @@
         <v>568</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5540,16 +5540,16 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -5581,7 +5581,7 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
         <v>133</v>
@@ -5608,13 +5608,13 @@
         <v>568</v>
       </c>
       <c r="L31">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5656,10 +5656,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -5697,7 +5697,7 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
         <v>133</v>
@@ -5813,10 +5813,10 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
         <v>166</v>
@@ -5840,13 +5840,13 @@
         <v>568</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5894,10 +5894,10 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -5929,7 +5929,7 @@
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
         <v>133</v>
@@ -6045,10 +6045,10 @@
         <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
         <v>168</v>
@@ -6072,13 +6072,13 @@
         <v>568</v>
       </c>
       <c r="L35">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -6120,16 +6120,16 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
         <v>133</v>
@@ -6277,7 +6277,7 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
         <v>134</v>
@@ -6304,13 +6304,13 @@
         <v>568</v>
       </c>
       <c r="L37">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="M37">
-        <v>3.66</v>
+        <v>4.1</v>
       </c>
       <c r="N37">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -6352,16 +6352,16 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>133</v>
@@ -6625,7 +6625,7 @@
         <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
         <v>133</v>
@@ -6741,7 +6741,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D41" t="s">
         <v>133</v>
@@ -7089,10 +7089,10 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
         <v>177</v>
@@ -7321,10 +7321,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
         <v>179</v>
@@ -7669,7 +7669,7 @@
         <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D49" t="s">
         <v>133</v>
@@ -7696,13 +7696,13 @@
         <v>568</v>
       </c>
       <c r="L49">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -7785,10 +7785,10 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E50" t="s">
         <v>183</v>
@@ -7812,13 +7812,13 @@
         <v>568</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -7901,10 +7901,10 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -8133,10 +8133,10 @@
         <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E53" t="s">
         <v>186</v>
@@ -8249,10 +8249,10 @@
         <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E54" t="s">
         <v>187</v>
@@ -8392,13 +8392,13 @@
         <v>568</v>
       </c>
       <c r="L55">
-        <v>2.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N55">
-        <v>2.41</v>
+        <v>1.36</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD55">
         <v>0</v>
@@ -8508,13 +8508,13 @@
         <v>568</v>
       </c>
       <c r="L56">
-        <v>8.699999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="M56">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="N56">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8556,16 +8556,16 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -8624,13 +8624,13 @@
         <v>568</v>
       </c>
       <c r="L57">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="M57">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8678,10 +8678,10 @@
         <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -8829,7 +8829,7 @@
         <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
         <v>133</v>
@@ -8856,13 +8856,13 @@
         <v>568</v>
       </c>
       <c r="L59">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="M59">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N59">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
         <v>133</v>
@@ -8972,13 +8972,13 @@
         <v>568</v>
       </c>
       <c r="L60">
-        <v>2.82</v>
+        <v>4.33</v>
       </c>
       <c r="M60">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="N60">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC60">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -9177,10 +9177,10 @@
         <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E62" t="s">
         <v>195</v>
@@ -9204,13 +9204,13 @@
         <v>568</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -9293,10 +9293,10 @@
         <v>52</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E63" t="s">
         <v>196</v>
@@ -9320,13 +9320,13 @@
         <v>568</v>
       </c>
       <c r="L63">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -9368,10 +9368,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
         <v>133</v>
@@ -9552,13 +9552,13 @@
         <v>568</v>
       </c>
       <c r="L65">
-        <v>5.6</v>
+        <v>1.66</v>
       </c>
       <c r="M65">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="N65">
-        <v>1.46</v>
+        <v>4</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>99</v>
       </c>
       <c r="D66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
         <v>199</v>
@@ -9668,13 +9668,13 @@
         <v>568</v>
       </c>
       <c r="L66">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M66">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="N66">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC66">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -9784,13 +9784,13 @@
         <v>568</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9832,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D68" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
         <v>201</v>
@@ -9900,13 +9900,13 @@
         <v>568</v>
       </c>
       <c r="L68">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="M68">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="N68">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9948,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9989,7 +9989,7 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D69" t="s">
         <v>133</v>
@@ -10016,13 +10016,13 @@
         <v>568</v>
       </c>
       <c r="L69">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N69">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10105,7 +10105,7 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D70" t="s">
         <v>133</v>
@@ -10132,13 +10132,13 @@
         <v>568</v>
       </c>
       <c r="L70">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -10364,13 +10364,13 @@
         <v>568</v>
       </c>
       <c r="L72">
-        <v>1.34</v>
+        <v>4.6</v>
       </c>
       <c r="M72">
-        <v>4.7</v>
+        <v>3.76</v>
       </c>
       <c r="N72">
-        <v>8</v>
+        <v>1.57</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10412,10 +10412,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC72">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -10453,10 +10453,10 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D73" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E73" t="s">
         <v>206</v>
@@ -10480,13 +10480,13 @@
         <v>568</v>
       </c>
       <c r="L73">
-        <v>2.11</v>
+        <v>5.6</v>
       </c>
       <c r="M73">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="N73">
-        <v>2.82</v>
+        <v>1.46</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="AB73">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC73">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD73">
         <v>0</v>
@@ -10569,7 +10569,7 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -10596,13 +10596,13 @@
         <v>568</v>
       </c>
       <c r="L74">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="M74">
-        <v>2.91</v>
+        <v>3.59</v>
       </c>
       <c r="N74">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10644,10 +10644,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10712,13 +10712,13 @@
         <v>568</v>
       </c>
       <c r="L75">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="M75">
-        <v>3.01</v>
+        <v>3.35</v>
       </c>
       <c r="N75">
-        <v>3.18</v>
+        <v>3.59</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10760,10 +10760,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC75">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10801,7 +10801,7 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D76" t="s">
         <v>133</v>
@@ -10828,13 +10828,13 @@
         <v>568</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10944,13 +10944,13 @@
         <v>568</v>
       </c>
       <c r="L77">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="M77">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="N77">
-        <v>3.72</v>
+        <v>2.68</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11060,13 +11060,13 @@
         <v>568</v>
       </c>
       <c r="L78">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="M78">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="N78">
-        <v>3.19</v>
+        <v>3.47</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC78">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11176,13 +11176,13 @@
         <v>568</v>
       </c>
       <c r="L79">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="M79">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N79">
-        <v>3.59</v>
+        <v>3.18</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D80" t="s">
         <v>134</v>
@@ -11381,7 +11381,7 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
         <v>134</v>
@@ -11408,13 +11408,13 @@
         <v>568</v>
       </c>
       <c r="L81">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="M81">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
       <c r="N81">
-        <v>3.75</v>
+        <v>3.19</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC81">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11497,7 +11497,7 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D82" t="s">
         <v>133</v>
@@ -11524,13 +11524,13 @@
         <v>568</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11613,7 +11613,7 @@
         <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D83" t="s">
         <v>134</v>
@@ -11640,13 +11640,13 @@
         <v>568</v>
       </c>
       <c r="L83">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="M83">
         <v>3.45</v>
       </c>
       <c r="N83">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11688,10 +11688,10 @@
         <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E84" t="s">
         <v>217</v>
@@ -11756,13 +11756,13 @@
         <v>568</v>
       </c>
       <c r="L84">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M84">
-        <v>4.4</v>
+        <v>3.79</v>
       </c>
       <c r="N84">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E85" t="s">
         <v>218</v>
@@ -11872,13 +11872,13 @@
         <v>568</v>
       </c>
       <c r="L85">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="M85">
-        <v>5</v>
+        <v>3.61</v>
       </c>
       <c r="N85">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D86" t="s">
         <v>134</v>
@@ -11988,13 +11988,13 @@
         <v>568</v>
       </c>
       <c r="L86">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="M86">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N86">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC86">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -12077,7 +12077,7 @@
         <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D87" t="s">
         <v>134</v>
@@ -12104,13 +12104,13 @@
         <v>568</v>
       </c>
       <c r="L87">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="M87">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N87">
-        <v>2.68</v>
+        <v>3.01</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -12152,10 +12152,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AC87">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -12193,7 +12193,7 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D88" t="s">
         <v>134</v>
@@ -12220,13 +12220,13 @@
         <v>568</v>
       </c>
       <c r="L88">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="M88">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="N88">
-        <v>3.45</v>
+        <v>3.79</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -12268,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC88">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AD88">
         <v>0</v>
@@ -12309,7 +12309,7 @@
         <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D89" t="s">
         <v>134</v>
@@ -12336,13 +12336,13 @@
         <v>568</v>
       </c>
       <c r="L89">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="M89">
-        <v>3.79</v>
+        <v>3.32</v>
       </c>
       <c r="N89">
-        <v>3.89</v>
+        <v>2.92</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -12384,10 +12384,10 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC89">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD89">
         <v>0</v>
@@ -12425,7 +12425,7 @@
         <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D90" t="s">
         <v>134</v>
@@ -12452,13 +12452,13 @@
         <v>568</v>
       </c>
       <c r="L90">
-        <v>1.93</v>
+        <v>3.65</v>
       </c>
       <c r="M90">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="N90">
-        <v>3.06</v>
+        <v>1.87</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -12500,10 +12500,10 @@
         <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC90">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD90">
         <v>0</v>
@@ -12541,10 +12541,10 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E91" t="s">
         <v>224</v>
@@ -12568,13 +12568,13 @@
         <v>568</v>
       </c>
       <c r="L91">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M91">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N91">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12616,10 +12616,10 @@
         <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC91">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD91">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D92" t="s">
         <v>134</v>
@@ -12684,13 +12684,13 @@
         <v>568</v>
       </c>
       <c r="L92">
-        <v>3.65</v>
+        <v>1.77</v>
       </c>
       <c r="M92">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="N92">
-        <v>1.87</v>
+        <v>3.75</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12732,10 +12732,10 @@
         <v>0</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD92">
         <v>0</v>
@@ -12773,10 +12773,10 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E93" t="s">
         <v>226</v>
@@ -12800,13 +12800,13 @@
         <v>568</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD93">
         <v>0</v>
@@ -12889,7 +12889,7 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D94" t="s">
         <v>134</v>
@@ -12916,13 +12916,13 @@
         <v>568</v>
       </c>
       <c r="L94">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N94">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12964,10 +12964,10 @@
         <v>0</v>
       </c>
       <c r="AB94">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD94">
         <v>0</v>
@@ -13005,10 +13005,10 @@
         <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E95" t="s">
         <v>228</v>
@@ -13032,13 +13032,13 @@
         <v>568</v>
       </c>
       <c r="L95">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M95">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N95">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AB95">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC95">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD95">
         <v>0</v>
@@ -13121,10 +13121,10 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E96" t="s">
         <v>229</v>
@@ -13148,13 +13148,13 @@
         <v>568</v>
       </c>
       <c r="L96">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="M96">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="N96">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -13196,10 +13196,10 @@
         <v>0</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13237,10 +13237,10 @@
         <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D97" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E97" t="s">
         <v>230</v>
@@ -13353,7 +13353,7 @@
         <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D98" t="s">
         <v>134</v>
@@ -13380,13 +13380,13 @@
         <v>568</v>
       </c>
       <c r="L98">
-        <v>4.6</v>
+        <v>2.04</v>
       </c>
       <c r="M98">
-        <v>3.76</v>
+        <v>3.03</v>
       </c>
       <c r="N98">
-        <v>1.57</v>
+        <v>3.34</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="AC98">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AD98">
         <v>0</v>
@@ -13469,10 +13469,10 @@
         <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E99" t="s">
         <v>232</v>
@@ -13496,13 +13496,13 @@
         <v>568</v>
       </c>
       <c r="L99">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="M99">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="N99">
-        <v>3.79</v>
+        <v>2.7</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13585,10 +13585,10 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E100" t="s">
         <v>233</v>
@@ -13612,13 +13612,13 @@
         <v>568</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13701,7 +13701,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D101" t="s">
         <v>134</v>
@@ -13728,13 +13728,13 @@
         <v>568</v>
       </c>
       <c r="L101">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="M101">
-        <v>3.61</v>
+        <v>3.31</v>
       </c>
       <c r="N101">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC101">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13844,13 +13844,13 @@
         <v>568</v>
       </c>
       <c r="L102">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="M102">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
       <c r="N102">
-        <v>2.68</v>
+        <v>3.72</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC102">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D103" t="s">
         <v>134</v>
@@ -13960,13 +13960,13 @@
         <v>568</v>
       </c>
       <c r="L103">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="M103">
-        <v>3.03</v>
+        <v>3.63</v>
       </c>
       <c r="N103">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -14008,10 +14008,10 @@
         <v>0</v>
       </c>
       <c r="AB103">
-        <v>2.37</v>
+        <v>1.61</v>
       </c>
       <c r="AC103">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AD103">
         <v>0</v>
@@ -14076,13 +14076,13 @@
         <v>568</v>
       </c>
       <c r="L104">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="M104">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="N104">
-        <v>2.92</v>
+        <v>4.22</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="AB104">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC104">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD104">
         <v>0</v>
@@ -14165,7 +14165,7 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D105" t="s">
         <v>134</v>
@@ -14281,7 +14281,7 @@
         <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D106" t="s">
         <v>134</v>
@@ -14424,13 +14424,13 @@
         <v>568</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -14472,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD107">
         <v>0</v>
@@ -14513,10 +14513,10 @@
         <v>55</v>
       </c>
       <c r="C108" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D108" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E108" t="s">
         <v>241</v>
@@ -14629,7 +14629,7 @@
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D109" t="s">
         <v>134</v>
@@ -14656,13 +14656,13 @@
         <v>568</v>
       </c>
       <c r="L109">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD109">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D110" t="s">
         <v>134</v>
@@ -14772,13 +14772,13 @@
         <v>568</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14820,10 +14820,10 @@
         <v>0</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD110">
         <v>0</v>
@@ -14861,10 +14861,10 @@
         <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D111" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E111" t="s">
         <v>244</v>
@@ -14888,13 +14888,13 @@
         <v>568</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14936,10 +14936,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14977,7 +14977,7 @@
         <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D112" t="s">
         <v>134</v>
@@ -15004,13 +15004,13 @@
         <v>568</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -15052,10 +15052,10 @@
         <v>0</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -15093,7 +15093,7 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D113" t="s">
         <v>134</v>
@@ -15120,13 +15120,13 @@
         <v>568</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -15209,10 +15209,10 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D114" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E114" t="s">
         <v>247</v>
@@ -15236,13 +15236,13 @@
         <v>568</v>
       </c>
       <c r="L114">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M114">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N114">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -15284,10 +15284,10 @@
         <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC114">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD114">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D115" t="s">
         <v>134</v>
@@ -15352,13 +15352,13 @@
         <v>568</v>
       </c>
       <c r="L115">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N115">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -15400,10 +15400,10 @@
         <v>0</v>
       </c>
       <c r="AB115">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC115">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD115">
         <v>0</v>
@@ -15441,7 +15441,7 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D116" t="s">
         <v>133</v>
@@ -15557,7 +15557,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D117" t="s">
         <v>134</v>
@@ -15673,7 +15673,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D118" t="s">
         <v>134</v>
@@ -15700,13 +15700,13 @@
         <v>568</v>
       </c>
       <c r="L118">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15748,10 +15748,10 @@
         <v>0</v>
       </c>
       <c r="AB118">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD118">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D119" t="s">
         <v>134</v>
@@ -15905,7 +15905,7 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D120" t="s">
         <v>134</v>
@@ -15932,13 +15932,13 @@
         <v>568</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15980,10 +15980,10 @@
         <v>0</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -16021,7 +16021,7 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D121" t="s">
         <v>134</v>
@@ -16048,13 +16048,13 @@
         <v>568</v>
       </c>
       <c r="L121">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M121">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -16096,10 +16096,10 @@
         <v>0</v>
       </c>
       <c r="AB121">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC121">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -16137,7 +16137,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D122" t="s">
         <v>134</v>
@@ -16253,7 +16253,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
@@ -16369,7 +16369,7 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D124" t="s">
         <v>134</v>
@@ -16485,7 +16485,7 @@
         <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D125" t="s">
         <v>134</v>
@@ -16601,7 +16601,7 @@
         <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D126" t="s">
         <v>134</v>
@@ -16717,10 +16717,10 @@
         <v>55</v>
       </c>
       <c r="C127" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D127" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E127" t="s">
         <v>260</v>
@@ -16744,13 +16744,13 @@
         <v>568</v>
       </c>
       <c r="L127">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M127">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N127">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16792,10 +16792,10 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC127">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD127">
         <v>0</v>
@@ -16833,7 +16833,7 @@
         <v>55</v>
       </c>
       <c r="C128" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D128" t="s">
         <v>134</v>
@@ -16949,7 +16949,7 @@
         <v>56</v>
       </c>
       <c r="C129" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D129" t="s">
         <v>134</v>
@@ -16976,13 +16976,13 @@
         <v>568</v>
       </c>
       <c r="L129">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M129">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="N129">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -17024,10 +17024,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -17065,7 +17065,7 @@
         <v>56</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" t="s">
         <v>134</v>
@@ -17181,7 +17181,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -17208,13 +17208,13 @@
         <v>568</v>
       </c>
       <c r="L131">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="M131">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="N131">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17256,10 +17256,10 @@
         <v>0</v>
       </c>
       <c r="AB131">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC131">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD131">
         <v>0</v>
@@ -17297,10 +17297,10 @@
         <v>56</v>
       </c>
       <c r="C132" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E132" t="s">
         <v>265</v>
@@ -17324,13 +17324,13 @@
         <v>568</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M132">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -17413,10 +17413,10 @@
         <v>56</v>
       </c>
       <c r="C133" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D133" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E133" t="s">
         <v>266</v>
@@ -17440,13 +17440,13 @@
         <v>568</v>
       </c>
       <c r="L133">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M133">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N133">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -17645,10 +17645,10 @@
         <v>58</v>
       </c>
       <c r="C135" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D135" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E135" t="s">
         <v>268</v>
@@ -17672,13 +17672,13 @@
         <v>568</v>
       </c>
       <c r="L135">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="M135">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="N135">
-        <v>3.53</v>
+        <v>3.71</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17720,10 +17720,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC135">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17761,7 +17761,7 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D136" t="s">
         <v>134</v>
@@ -17788,13 +17788,13 @@
         <v>568</v>
       </c>
       <c r="L136">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="M136">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N136">
-        <v>3.71</v>
+        <v>3.47</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17836,10 +17836,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17877,10 +17877,10 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E137" t="s">
         <v>270</v>
@@ -17904,13 +17904,13 @@
         <v>568</v>
       </c>
       <c r="L137">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M137">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD137">
         <v>0</v>
@@ -17993,7 +17993,7 @@
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D138" t="s">
         <v>133</v>
@@ -18109,10 +18109,10 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D139" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E139" t="s">
         <v>272</v>
@@ -18136,13 +18136,13 @@
         <v>568</v>
       </c>
       <c r="L139">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M139">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N139">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -18184,10 +18184,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC139">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -18225,7 +18225,7 @@
         <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D140" t="s">
         <v>134</v>
@@ -18252,13 +18252,13 @@
         <v>568</v>
       </c>
       <c r="L140">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="M140">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N140">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -18300,10 +18300,10 @@
         <v>0</v>
       </c>
       <c r="AB140">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AC140">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="AD140">
         <v>0</v>
@@ -18341,7 +18341,7 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D141" t="s">
         <v>134</v>
@@ -18368,13 +18368,13 @@
         <v>568</v>
       </c>
       <c r="L141">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M141">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N141">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC141">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18457,10 +18457,10 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E142" t="s">
         <v>275</v>
@@ -18484,13 +18484,13 @@
         <v>568</v>
       </c>
       <c r="L142">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M142">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O142">
         <v>0</v>
@@ -18532,10 +18532,10 @@
         <v>0</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD142">
         <v>0</v>
@@ -18689,7 +18689,7 @@
         <v>58</v>
       </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D144" t="s">
         <v>134</v>
@@ -18805,7 +18805,7 @@
         <v>59</v>
       </c>
       <c r="C145" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D145" t="s">
         <v>134</v>
@@ -18921,10 +18921,10 @@
         <v>60</v>
       </c>
       <c r="C146" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E146" t="s">
         <v>279</v>
@@ -18948,13 +18948,13 @@
         <v>568</v>
       </c>
       <c r="L146">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M146">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N146">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O146">
         <v>0</v>
@@ -18996,16 +18996,16 @@
         <v>0</v>
       </c>
       <c r="AB146">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC146">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD146">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE146">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF146">
         <v>0</v>
@@ -19037,10 +19037,10 @@
         <v>60</v>
       </c>
       <c r="C147" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E147" t="s">
         <v>280</v>
@@ -19153,10 +19153,10 @@
         <v>60</v>
       </c>
       <c r="C148" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D148" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E148" t="s">
         <v>281</v>
@@ -19180,13 +19180,13 @@
         <v>568</v>
       </c>
       <c r="L148">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M148">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -19228,16 +19228,16 @@
         <v>0</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF148">
         <v>0</v>
@@ -19269,10 +19269,10 @@
         <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D149" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E149" t="s">
         <v>282</v>
@@ -19501,7 +19501,7 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D151" t="s">
         <v>134</v>
@@ -19617,10 +19617,10 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D152" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E152" t="s">
         <v>285</v>
@@ -19644,13 +19644,13 @@
         <v>568</v>
       </c>
       <c r="L152">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M152">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N152">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19692,10 +19692,10 @@
         <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC152">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD152">
         <v>0</v>
@@ -19733,7 +19733,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D153" t="s">
         <v>134</v>
@@ -19849,7 +19849,7 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D154" t="s">
         <v>134</v>
@@ -19965,10 +19965,10 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="D155" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E155" t="s">
         <v>288</v>
@@ -19992,13 +19992,13 @@
         <v>568</v>
       </c>
       <c r="L155">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M155">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -20040,10 +20040,10 @@
         <v>0</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC155">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD155">
         <v>0</v>
@@ -20081,7 +20081,7 @@
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D156" t="s">
         <v>134</v>
@@ -20197,7 +20197,7 @@
         <v>63</v>
       </c>
       <c r="C157" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="D157" t="s">
         <v>134</v>
@@ -20429,7 +20429,7 @@
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D159" t="s">
         <v>134</v>
@@ -20545,7 +20545,7 @@
         <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D160" t="s">
         <v>134</v>
@@ -20685,7 +20685,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -20801,7 +20801,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -21009,7 +21009,7 @@
         <v>64</v>
       </c>
       <c r="C164" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D164" t="s">
         <v>134</v>
@@ -21036,13 +21036,13 @@
         <v>568</v>
       </c>
       <c r="L164">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M164">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="N164">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -21084,10 +21084,10 @@
         <v>0</v>
       </c>
       <c r="AB164">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC164">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD164">
         <v>0</v>
@@ -21125,7 +21125,7 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D165" t="s">
         <v>134</v>
@@ -21152,13 +21152,13 @@
         <v>568</v>
       </c>
       <c r="L165">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="M165">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="N165">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD165">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>64</v>
       </c>
       <c r="C166" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D166" t="s">
         <v>134</v>
@@ -21473,7 +21473,7 @@
         <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D168" t="s">
         <v>134</v>
@@ -21705,7 +21705,7 @@
         <v>65</v>
       </c>
       <c r="C170" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D170" t="s">
         <v>134</v>
@@ -21821,7 +21821,7 @@
         <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D171" t="s">
         <v>134</v>
@@ -22053,7 +22053,7 @@
         <v>66</v>
       </c>
       <c r="C173" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D173" t="s">
         <v>134</v>
@@ -22285,16 +22285,16 @@
         <v>67</v>
       </c>
       <c r="C175" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D175" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E175" t="s">
         <v>308</v>
       </c>
       <c r="F175" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -22410,7 +22410,7 @@
         <v>309</v>
       </c>
       <c r="F176" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -22517,16 +22517,16 @@
         <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D177" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E177" t="s">
         <v>310</v>
       </c>
       <c r="F177" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -24605,7 +24605,7 @@
         <v>70</v>
       </c>
       <c r="C195" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D195" t="s">
         <v>133</v>
@@ -24632,13 +24632,13 @@
         <v>568</v>
       </c>
       <c r="L195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M195">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -24680,10 +24680,10 @@
         <v>0</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD195">
         <v>0</v>
@@ -24721,7 +24721,7 @@
         <v>70</v>
       </c>
       <c r="C196" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D196" t="s">
         <v>133</v>
@@ -24748,13 +24748,13 @@
         <v>568</v>
       </c>
       <c r="L196">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M196">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N196">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O196">
         <v>0</v>
@@ -24796,10 +24796,10 @@
         <v>0</v>
       </c>
       <c r="AB196">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC196">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD196">
         <v>0</v>
@@ -24837,7 +24837,7 @@
         <v>70</v>
       </c>
       <c r="C197" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D197" t="s">
         <v>133</v>
@@ -25765,7 +25765,7 @@
         <v>72</v>
       </c>
       <c r="C205" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D205" t="s">
         <v>133</v>
@@ -25792,13 +25792,13 @@
         <v>568</v>
       </c>
       <c r="L205">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M205">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O205">
         <v>0</v>
@@ -25840,10 +25840,10 @@
         <v>0</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD205">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>72</v>
       </c>
       <c r="C206" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D206" t="s">
         <v>133</v>
@@ -25997,7 +25997,7 @@
         <v>72</v>
       </c>
       <c r="C207" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D207" t="s">
         <v>133</v>
@@ -26024,13 +26024,13 @@
         <v>568</v>
       </c>
       <c r="L207">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M207">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N207">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O207">
         <v>0</v>
@@ -26072,10 +26072,10 @@
         <v>0</v>
       </c>
       <c r="AB207">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC207">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD207">
         <v>0</v>
@@ -26229,7 +26229,7 @@
         <v>73</v>
       </c>
       <c r="C209" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D209" t="s">
         <v>133</v>
@@ -26256,13 +26256,13 @@
         <v>568</v>
       </c>
       <c r="L209">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M209">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O209">
         <v>0</v>
@@ -26304,10 +26304,10 @@
         <v>0</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD209">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>73</v>
       </c>
       <c r="C210" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D210" t="s">
         <v>133</v>
@@ -26372,13 +26372,13 @@
         <v>568</v>
       </c>
       <c r="L210">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M210">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N210">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -26420,10 +26420,10 @@
         <v>0</v>
       </c>
       <c r="AB210">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC210">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD210">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>74</v>
       </c>
       <c r="C211" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D211" t="s">
         <v>133</v>
@@ -26488,13 +26488,13 @@
         <v>568</v>
       </c>
       <c r="L211">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M211">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -26577,7 +26577,7 @@
         <v>74</v>
       </c>
       <c r="C212" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D212" t="s">
         <v>133</v>
@@ -26604,13 +26604,13 @@
         <v>568</v>
       </c>
       <c r="L212">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="M212">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N212">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC212">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD212">
         <v>0</v>
@@ -26693,7 +26693,7 @@
         <v>74</v>
       </c>
       <c r="C213" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D213" t="s">
         <v>133</v>
@@ -26720,13 +26720,13 @@
         <v>568</v>
       </c>
       <c r="L213">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M213">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N213">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O213">
         <v>0</v>
@@ -26768,10 +26768,10 @@
         <v>0</v>
       </c>
       <c r="AB213">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC213">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD213">
         <v>0</v>
@@ -26925,7 +26925,7 @@
         <v>76</v>
       </c>
       <c r="C215" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D215" t="s">
         <v>133</v>
@@ -26952,13 +26952,13 @@
         <v>568</v>
       </c>
       <c r="L215">
-        <v>1.61</v>
+        <v>2.95</v>
       </c>
       <c r="M215">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N215">
-        <v>4.6</v>
+        <v>2.29</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -27000,10 +27000,10 @@
         <v>0</v>
       </c>
       <c r="AB215">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC215">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD215">
         <v>0</v>
@@ -27041,7 +27041,7 @@
         <v>76</v>
       </c>
       <c r="C216" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D216" t="s">
         <v>133</v>
@@ -27068,13 +27068,13 @@
         <v>568</v>
       </c>
       <c r="L216">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="M216">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N216">
-        <v>2.29</v>
+        <v>4.6</v>
       </c>
       <c r="O216">
         <v>0</v>
@@ -27116,10 +27116,10 @@
         <v>0</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD216">
         <v>0</v>
@@ -27273,7 +27273,7 @@
         <v>78</v>
       </c>
       <c r="C218" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D218" t="s">
         <v>133</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -259,24 +259,24 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
-    <t>China Chinese Super League</t>
+    <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -310,63 +310,66 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>England EFL League Two</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
+    <t>Scotland Championship</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>England EFL League Two</t>
-  </si>
-  <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Scotland Championship</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
+    <t>Czech Republic First League</t>
   </si>
   <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Bulgaria First League</t>
+    <t>Slovenia PrvaLiga</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -376,9 +379,6 @@
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -394,12 +394,12 @@
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -433,165 +433,171 @@
     <t>Kataller Toyama</t>
   </si>
   <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>V-Varen Nagasaki</t>
-  </si>
-  <si>
     <t>St George City FA</t>
   </si>
   <si>
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Fujieda MYFC</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
     <t>Tokushima Vortis</t>
   </si>
   <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Fujieda MYFC</t>
-  </si>
-  <si>
     <t>Jubilo Iwata</t>
   </si>
   <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Darmstadt 98</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Darmstadt 98</t>
+    <t>Karlsruher SC</t>
+  </si>
+  <si>
+    <t>Paderborn</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
   </si>
   <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
     <t>Cardiff City</t>
   </si>
   <si>
+    <t>Qingdao Youth Island</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Qingdao Youth Island</t>
-  </si>
-  <si>
     <t>Astana</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Hoffenheim II</t>
+    <t>Meizhou Hakka</t>
   </si>
   <si>
     <t>Ordabasy</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Waldhof Mannheim</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
     <t>Veres Rivne</t>
   </si>
   <si>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
     <t>Schwarz-Weiß Bregenz</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
     <t>Nieciecza</t>
   </si>
   <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
     <t>Naftan</t>
   </si>
   <si>
@@ -601,286 +607,295 @@
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Utsikten</t>
-  </si>
-  <si>
     <t>Ufa</t>
   </si>
   <si>
-    <t>Varberg</t>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Salford City</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>Shrewsbury Town</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Colchester United</t>
+  </si>
+  <si>
+    <t>Burton Albion</t>
+  </si>
+  <si>
+    <t>Lincoln City</t>
+  </si>
+  <si>
+    <t>Cambridge United</t>
+  </si>
+  <si>
+    <t>Grimsby Town</t>
+  </si>
+  <si>
+    <t>Termez Surkhon</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Plymouth Argyle</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Raith Rovers</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Ural</t>
   </si>
   <si>
     <t>Stabæk</t>
   </si>
   <si>
-    <t>Barnet</t>
-  </si>
-  <si>
-    <t>Shrewsbury Town</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Termez Surkhon</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Newport County</t>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Greenock Morton</t>
   </si>
   <si>
     <t>Åsane</t>
   </si>
   <si>
-    <t>Salford City</t>
-  </si>
-  <si>
-    <t>Blackpool</t>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
     <t>Huddersfield Town</t>
   </si>
   <si>
-    <t>Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Lincoln City</t>
+    <t>St. Johnstone</t>
+  </si>
+  <si>
+    <t>Airdrieonians</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Milton Keynes Dons</t>
-  </si>
-  <si>
-    <t>Chesterfield</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Grimsby Town</t>
-  </si>
-  <si>
-    <t>Bristol Rovers</t>
-  </si>
-  <si>
-    <t>Walsall</t>
-  </si>
-  <si>
-    <t>Airdrieonians</t>
-  </si>
-  <si>
-    <t>KuPS</t>
-  </si>
-  <si>
-    <t>Cambridge United</t>
-  </si>
-  <si>
-    <t>Raith Rovers</t>
-  </si>
-  <si>
     <t>KVC Westerlo</t>
   </si>
   <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Greenock Morton</t>
-  </si>
-  <si>
-    <t>Colchester United</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Plymouth Argyle</t>
-  </si>
-  <si>
-    <t>St. Johnstone</t>
-  </si>
-  <si>
     <t>KAMAZ</t>
   </si>
   <si>
     <t>MSV Duisburg</t>
   </si>
   <si>
+    <t>Karviná</t>
+  </si>
+  <si>
     <t>Rostov</t>
   </si>
   <si>
-    <t>Karviná</t>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
   </si>
   <si>
     <t>Posusje</t>
   </si>
   <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
     <t>Slavia</t>
   </si>
   <si>
-    <t>Rijeka</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Zorya</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Varaždin</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
+    <t>Levski Sofia</t>
   </si>
   <si>
     <t>Teplice</t>
   </si>
   <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Widzew Łódź</t>
+  </si>
+  <si>
+    <t>Stal Rzeszów</t>
   </si>
   <si>
     <t>Argeș</t>
   </si>
   <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Widzew Łódź</t>
-  </si>
-  <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
     <t>Värnamo</t>
   </si>
   <si>
     <t>Diósgyőr</t>
   </si>
   <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Oulu</t>
+  </si>
+  <si>
     <t>Bellinzona</t>
   </si>
   <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
     <t>Zemplín Michalovce</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
-    <t>Oulu</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
     <t>Magallanes</t>
   </si>
   <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
     <t>Olimpiyets</t>
   </si>
   <si>
-    <t>07 Vestur</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Krasnodar</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
   </si>
   <si>
     <t>Čukarički</t>
@@ -892,180 +907,165 @@
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
+    <t>Primorje</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
+  </si>
+  <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Primorje</t>
-  </si>
-  <si>
-    <t>Ferencváros</t>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Basel</t>
-  </si>
-  <si>
     <t>Dinamo Bucureşti</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
     <t>KAA Gent</t>
   </si>
   <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
     <t>Novorizontino</t>
   </si>
   <si>
-    <t>Osijek</t>
-  </si>
-  <si>
-    <t>Coquimbo Unido</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Sport Recife</t>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
   </si>
   <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
     <t>San Luis</t>
   </si>
   <si>
+    <t>Concepción</t>
+  </si>
+  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Santiago Morning</t>
   </si>
   <si>
-    <t>Concepción</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>North Carolina Courage</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>North Carolina Courage</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
+    <t>Fluminense</t>
   </si>
   <si>
     <t>Louisville City</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
     <t>North Texas</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
@@ -1084,165 +1084,171 @@
     <t>Omiya Ardija</t>
   </si>
   <si>
+    <t>Vegalta Sendai</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Vegalta Sendai</t>
-  </si>
-  <si>
     <t>Sutherland Sharks</t>
   </si>
   <si>
     <t>Montedio Yamagata</t>
   </si>
   <si>
+    <t>Renofa Yamaguchi</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
+    <t>Imabari</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
     <t>Ehime</t>
   </si>
   <si>
-    <t>Imabari</t>
-  </si>
-  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
     <t>Kolkheti Poti</t>
   </si>
   <si>
+    <t>Telavi</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Bochum</t>
+    <t>Preußen Münster</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
   </si>
   <si>
     <t>Gareji</t>
   </si>
   <si>
-    <t>Telavi</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
     <t>Peterborough United</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
+    <t>Saarbrucken</t>
+  </si>
+  <si>
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Havelse</t>
+  </si>
+  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Havelse</t>
+    <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Saarbrucken</t>
-  </si>
-  <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
-  </si>
-  <si>
     <t>Dynamo Kyiv</t>
   </si>
   <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
     <t>Rapid Wien II</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
     <t>Minsk</t>
   </si>
   <si>
@@ -1252,286 +1258,295 @@
     <t>Norrköping</t>
   </si>
   <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
     <t>Shinnik</t>
   </si>
   <si>
-    <t>Örgryte</t>
+    <t>Oldham Athletic</t>
+  </si>
+  <si>
+    <t>Swindon Town</t>
+  </si>
+  <si>
+    <t>Notts County</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Crewe Alexandra</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Tranmere Rovers</t>
+  </si>
+  <si>
+    <t>Mansfield Town</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Cheltenham Town</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Queen's Park</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Rodina Moskva</t>
   </si>
   <si>
     <t>Moss</t>
   </si>
   <si>
-    <t>Fleetwood Town</t>
-  </si>
-  <si>
-    <t>Bromley</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>Kokand-1912</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Notts County</t>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
+  </si>
+  <si>
+    <t>Dunfermline Athletic</t>
   </si>
   <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Crewe Alexandra</t>
-  </si>
-  <si>
-    <t>Stevenage</t>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
   </si>
   <si>
     <t>Mjøndalen</t>
   </si>
   <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
     <t>Leyton Orient</t>
   </si>
   <si>
-    <t>Northampton Town</t>
-  </si>
-  <si>
-    <t>Rodina Moskva</t>
-  </si>
-  <si>
-    <t>Reading</t>
+    <t>Partick Thistle</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
+    <t>Lyn</t>
   </si>
   <si>
     <t>Hødd</t>
   </si>
   <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Oldham Athletic</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Crawley Town</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Swindon Town</t>
-  </si>
-  <si>
-    <t>Ross County</t>
-  </si>
-  <si>
-    <t>Haka</t>
-  </si>
-  <si>
-    <t>Cheltenham Town</t>
-  </si>
-  <si>
-    <t>Queen's Park</t>
-  </si>
-  <si>
     <t>Zulte-Waregem</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Dunfermline Athletic</t>
-  </si>
-  <si>
-    <t>Tranmere Rovers</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Mansfield Town</t>
-  </si>
-  <si>
-    <t>Exeter City</t>
-  </si>
-  <si>
-    <t>Barnsley</t>
-  </si>
-  <si>
-    <t>Partick Thistle</t>
-  </si>
-  <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
     <t>Stuttgart II</t>
   </si>
   <si>
+    <t>Zlín</t>
+  </si>
+  <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
-    <t>Zlín</t>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>LNZ Cherkasy</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
   </si>
   <si>
     <t>Željezničar</t>
   </si>
   <si>
+    <t>Gorica</t>
+  </si>
+  <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
     <t>Isloch</t>
   </si>
   <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>LNZ Cherkasy</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>Slavia Sofia</t>
   </si>
   <si>
     <t>Bohemians 1905</t>
   </si>
   <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
+    <t>Aluminij</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Csikszereda</t>
   </si>
   <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
     <t>GAIS</t>
   </si>
   <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
+    <t>Skalica</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Brann</t>
+  </si>
+  <si>
     <t>Komárno</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Brann</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>St. Gallen</t>
-  </si>
-  <si>
-    <t>Skalica</t>
-  </si>
-  <si>
-    <t>Jaro</t>
-  </si>
-  <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
     <t>Curicó Unido</t>
   </si>
   <si>
+    <t>La Serena</t>
+  </si>
+  <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>La Serena</t>
-  </si>
-  <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
+    <t>Salzburg</t>
+  </si>
+  <si>
+    <t>Dinamo Moskva</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>Salzburg</t>
-  </si>
-  <si>
-    <t>Dinamo Moskva</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
+    <t>Spartak Subotica</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Radnički Niš</t>
@@ -1543,175 +1558,160 @@
     <t>IMT Novi Beograd</t>
   </si>
   <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Spartak Subotica</t>
-  </si>
-  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Kazincbarcika</t>
+  </si>
+  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Kazincbarcika</t>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Podbrezová</t>
   </si>
   <si>
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
     <t>FCSB</t>
   </si>
   <si>
-    <t>Podbrezová</t>
-  </si>
-  <si>
     <t>Shelbourne</t>
   </si>
   <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Deportes Limache</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Deportes Limache</t>
-  </si>
-  <si>
-    <t>Bahia</t>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>San Telmo</t>
   </si>
   <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
-    <t>Universidad Católica</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
     <t>San Marcos</t>
   </si>
   <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
     <t>Univ. Concepción</t>
   </si>
   <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
     <t>Antofagasta</t>
   </si>
   <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
-  </si>
-  <si>
     <t>Rhode Island</t>
   </si>
   <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
     <t>Toronto II</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>San Diego Wave</t>
+  </si>
+  <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>San Diego Wave</t>
-  </si>
-  <si>
-    <t>Goiás</t>
+    <t>Grêmio</t>
   </si>
   <si>
     <t>North Carolina FC</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>Sacramento Republic</t>
-  </si>
-  <si>
-    <t>Las Vegas Lights</t>
   </si>
   <si>
     <t>Houston Dash</t>
@@ -2681,7 +2681,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -2708,13 +2708,13 @@
         <v>568</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -2824,13 +2824,13 @@
         <v>568</v>
       </c>
       <c r="L7">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>133</v>
@@ -3172,13 +3172,13 @@
         <v>568</v>
       </c>
       <c r="L10">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="M10">
-        <v>3.67</v>
+        <v>2.98</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>2.77</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -3288,13 +3288,13 @@
         <v>568</v>
       </c>
       <c r="L11">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="M11">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N11">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3336,10 +3336,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -3404,13 +3404,13 @@
         <v>568</v>
       </c>
       <c r="L12">
-        <v>2.86</v>
+        <v>2.07</v>
       </c>
       <c r="M12">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N12">
-        <v>2.37</v>
+        <v>3.03</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3452,10 +3452,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -3520,13 +3520,13 @@
         <v>568</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3609,7 +3609,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>133</v>
@@ -3636,13 +3636,13 @@
         <v>568</v>
       </c>
       <c r="L14">
-        <v>2.07</v>
+        <v>3.41</v>
       </c>
       <c r="M14">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="N14">
-        <v>3.03</v>
+        <v>1.88</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC14">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -3752,13 +3752,13 @@
         <v>568</v>
       </c>
       <c r="L15">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="M15">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="N15">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3868,13 +3868,13 @@
         <v>568</v>
       </c>
       <c r="L16">
-        <v>4.9</v>
+        <v>1.64</v>
       </c>
       <c r="M16">
-        <v>4.6</v>
+        <v>3.67</v>
       </c>
       <c r="N16">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -3984,13 +3984,13 @@
         <v>568</v>
       </c>
       <c r="L17">
-        <v>3.41</v>
+        <v>2.57</v>
       </c>
       <c r="M17">
-        <v>3.38</v>
+        <v>3.03</v>
       </c>
       <c r="N17">
-        <v>1.88</v>
+        <v>2.49</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4032,10 +4032,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4100,13 +4100,13 @@
         <v>568</v>
       </c>
       <c r="L18">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="M18">
-        <v>3.26</v>
+        <v>4.3</v>
       </c>
       <c r="N18">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -4216,13 +4216,13 @@
         <v>568</v>
       </c>
       <c r="L19">
-        <v>2.57</v>
+        <v>4.9</v>
       </c>
       <c r="M19">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="N19">
-        <v>2.49</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4332,13 +4332,13 @@
         <v>568</v>
       </c>
       <c r="L20">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="M20">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="N20">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4421,7 +4421,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4448,13 +4448,13 @@
         <v>568</v>
       </c>
       <c r="L21">
-        <v>1.88</v>
+        <v>3.23</v>
       </c>
       <c r="M21">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N21">
-        <v>3.51</v>
+        <v>1.94</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AC21">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4564,13 +4564,13 @@
         <v>568</v>
       </c>
       <c r="L22">
-        <v>3.23</v>
+        <v>1.62</v>
       </c>
       <c r="M22">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="N22">
-        <v>1.94</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4612,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4680,13 +4680,13 @@
         <v>568</v>
       </c>
       <c r="L23">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4885,7 +4885,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -5028,13 +5028,13 @@
         <v>568</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -5144,13 +5144,13 @@
         <v>568</v>
       </c>
       <c r="L27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5192,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -5233,7 +5233,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
         <v>133</v>
@@ -5376,13 +5376,13 @@
         <v>568</v>
       </c>
       <c r="L29">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="M29">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="N29">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -5424,16 +5424,16 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC29">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD29">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE29">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF29">
         <v>0</v>
@@ -5465,10 +5465,10 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
         <v>163</v>
@@ -5492,13 +5492,13 @@
         <v>568</v>
       </c>
       <c r="L30">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5540,16 +5540,16 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -5581,10 +5581,10 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
         <v>164</v>
@@ -5608,13 +5608,13 @@
         <v>568</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5656,16 +5656,16 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -5697,7 +5697,7 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
         <v>133</v>
@@ -5813,10 +5813,10 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
         <v>166</v>
@@ -5840,13 +5840,13 @@
         <v>568</v>
       </c>
       <c r="L33">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5894,10 +5894,10 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -5929,10 +5929,10 @@
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
@@ -5956,13 +5956,13 @@
         <v>568</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -6045,10 +6045,10 @@
         <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
         <v>168</v>
@@ -6072,13 +6072,13 @@
         <v>568</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
         <v>133</v>
@@ -6277,10 +6277,10 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
         <v>170</v>
@@ -6304,13 +6304,13 @@
         <v>568</v>
       </c>
       <c r="L37">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -6352,10 +6352,10 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
         <v>133</v>
@@ -6625,7 +6625,7 @@
         <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
         <v>133</v>
@@ -6741,7 +6741,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
         <v>133</v>
@@ -6973,10 +6973,10 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
         <v>176</v>
@@ -7089,10 +7089,10 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
         <v>177</v>
@@ -7553,10 +7553,10 @@
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E48" t="s">
         <v>181</v>
@@ -7785,10 +7785,10 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E50" t="s">
         <v>183</v>
@@ -7812,13 +7812,13 @@
         <v>568</v>
       </c>
       <c r="L50">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -7901,10 +7901,10 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
@@ -8133,7 +8133,7 @@
         <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
         <v>133</v>
@@ -8160,13 +8160,13 @@
         <v>568</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -8249,10 +8249,10 @@
         <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E54" t="s">
         <v>187</v>
@@ -8508,13 +8508,13 @@
         <v>568</v>
       </c>
       <c r="L56">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="M56">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8562,10 +8562,10 @@
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -8624,13 +8624,13 @@
         <v>568</v>
       </c>
       <c r="L57">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>3.76</v>
       </c>
       <c r="N57">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8678,10 +8678,10 @@
         <v>0</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -8829,7 +8829,7 @@
         <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
         <v>133</v>
@@ -8856,13 +8856,13 @@
         <v>568</v>
       </c>
       <c r="L59">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="M59">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N59">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC59">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
         <v>133</v>
@@ -8972,13 +8972,13 @@
         <v>568</v>
       </c>
       <c r="L60">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="M60">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="N60">
-        <v>1.6</v>
+        <v>3.07</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -9061,7 +9061,7 @@
         <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61" t="s">
         <v>133</v>
@@ -9088,13 +9088,13 @@
         <v>568</v>
       </c>
       <c r="L61">
-        <v>1.73</v>
+        <v>2.82</v>
       </c>
       <c r="M61">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N61">
-        <v>3.47</v>
+        <v>2.32</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -9136,16 +9136,16 @@
         <v>0</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD61">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE61">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF61">
         <v>0</v>
@@ -9177,7 +9177,7 @@
         <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
         <v>133</v>
@@ -9204,13 +9204,13 @@
         <v>568</v>
       </c>
       <c r="L62">
-        <v>2.12</v>
+        <v>4.33</v>
       </c>
       <c r="M62">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="N62">
-        <v>2.76</v>
+        <v>1.6</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC62">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -9293,10 +9293,10 @@
         <v>52</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
         <v>196</v>
@@ -9320,13 +9320,13 @@
         <v>568</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -9374,10 +9374,10 @@
         <v>0</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF63">
         <v>0</v>
@@ -9409,10 +9409,10 @@
         <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
         <v>197</v>
@@ -9436,13 +9436,13 @@
         <v>568</v>
       </c>
       <c r="L64">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M64">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -9528,7 +9528,7 @@
         <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E65" t="s">
         <v>198</v>
@@ -9552,13 +9552,13 @@
         <v>568</v>
       </c>
       <c r="L65">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M65">
-        <v>4.4</v>
+        <v>3.79</v>
       </c>
       <c r="N65">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9641,7 +9641,7 @@
         <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
         <v>134</v>
@@ -9668,13 +9668,13 @@
         <v>568</v>
       </c>
       <c r="L66">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M66">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N66">
-        <v>3.47</v>
+        <v>2.92</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC66">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -9784,13 +9784,13 @@
         <v>568</v>
       </c>
       <c r="L67">
-        <v>2.21</v>
+        <v>4.6</v>
       </c>
       <c r="M67">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="N67">
-        <v>2.68</v>
+        <v>1.57</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9832,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AC67">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9873,7 +9873,7 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
@@ -9900,13 +9900,13 @@
         <v>568</v>
       </c>
       <c r="L68">
-        <v>2.74</v>
+        <v>1.84</v>
       </c>
       <c r="M68">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="N68">
-        <v>2.44</v>
+        <v>3.59</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9948,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9989,10 +9989,10 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
         <v>202</v>
@@ -10016,13 +10016,13 @@
         <v>568</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10064,10 +10064,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -10105,7 +10105,7 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D70" t="s">
         <v>133</v>
@@ -10224,7 +10224,7 @@
         <v>98</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E71" t="s">
         <v>204</v>
@@ -10248,13 +10248,13 @@
         <v>568</v>
       </c>
       <c r="L71">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="M71">
-        <v>3.85</v>
+        <v>3.26</v>
       </c>
       <c r="N71">
-        <v>2.6</v>
+        <v>3.47</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -10364,13 +10364,13 @@
         <v>568</v>
       </c>
       <c r="L72">
-        <v>4.6</v>
+        <v>1.81</v>
       </c>
       <c r="M72">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="N72">
-        <v>1.57</v>
+        <v>3.45</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10412,10 +10412,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC72">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -10456,7 +10456,7 @@
         <v>98</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E73" t="s">
         <v>206</v>
@@ -10480,13 +10480,13 @@
         <v>568</v>
       </c>
       <c r="L73">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="M73">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N73">
-        <v>1.46</v>
+        <v>3.79</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD73">
         <v>0</v>
@@ -10569,7 +10569,7 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -10596,13 +10596,13 @@
         <v>568</v>
       </c>
       <c r="L74">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="M74">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="N74">
-        <v>3.45</v>
+        <v>2.68</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC74">
         <v>1.91</v>
@@ -10685,7 +10685,7 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -10712,58 +10712,58 @@
         <v>568</v>
       </c>
       <c r="L75">
+        <v>1.62</v>
+      </c>
+      <c r="M75">
+        <v>3.61</v>
+      </c>
+      <c r="N75">
+        <v>4.5</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
         <v>1.84</v>
       </c>
-      <c r="M75">
-        <v>3.35</v>
-      </c>
-      <c r="N75">
-        <v>3.59</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>0</v>
-      </c>
-      <c r="AB75">
-        <v>2</v>
-      </c>
       <c r="AC75">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10804,7 +10804,7 @@
         <v>98</v>
       </c>
       <c r="D76" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E76" t="s">
         <v>209</v>
@@ -10828,13 +10828,13 @@
         <v>568</v>
       </c>
       <c r="L76">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>3.03</v>
       </c>
       <c r="N76">
-        <v>6.2</v>
+        <v>3.34</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10876,10 +10876,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10944,13 +10944,13 @@
         <v>568</v>
       </c>
       <c r="L77">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="M77">
-        <v>3.06</v>
+        <v>3.31</v>
       </c>
       <c r="N77">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC77">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11060,13 +11060,13 @@
         <v>568</v>
       </c>
       <c r="L78">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="M78">
-        <v>3.77</v>
+        <v>3.36</v>
       </c>
       <c r="N78">
-        <v>3.47</v>
+        <v>3.19</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC78">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11149,7 +11149,7 @@
         <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D79" t="s">
         <v>134</v>
@@ -11176,13 +11176,13 @@
         <v>568</v>
       </c>
       <c r="L79">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="M79">
-        <v>3.01</v>
+        <v>3.47</v>
       </c>
       <c r="N79">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC79">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D80" t="s">
         <v>134</v>
@@ -11292,13 +11292,13 @@
         <v>568</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11340,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -11381,10 +11381,10 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E81" t="s">
         <v>214</v>
@@ -11408,13 +11408,13 @@
         <v>568</v>
       </c>
       <c r="L81">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11497,10 +11497,10 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E82" t="s">
         <v>215</v>
@@ -11524,13 +11524,13 @@
         <v>568</v>
       </c>
       <c r="L82">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="M82">
-        <v>4</v>
+        <v>3.06</v>
       </c>
       <c r="N82">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11572,10 +11572,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11640,13 +11640,13 @@
         <v>568</v>
       </c>
       <c r="L83">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="M83">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N83">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11688,10 +11688,10 @@
         <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E84" t="s">
         <v>217</v>
@@ -11756,13 +11756,13 @@
         <v>568</v>
       </c>
       <c r="L84">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11845,7 +11845,7 @@
         <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D85" t="s">
         <v>134</v>
@@ -11872,13 +11872,13 @@
         <v>568</v>
       </c>
       <c r="L85">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="M85">
-        <v>3.61</v>
+        <v>4.7</v>
       </c>
       <c r="N85">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11961,10 +11961,10 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E86" t="s">
         <v>219</v>
@@ -11988,13 +11988,13 @@
         <v>568</v>
       </c>
       <c r="L86">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="M86">
-        <v>3.23</v>
+        <v>3.85</v>
       </c>
       <c r="N86">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -12077,10 +12077,10 @@
         <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E87" t="s">
         <v>220</v>
@@ -12104,13 +12104,13 @@
         <v>568</v>
       </c>
       <c r="L87">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="M87">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="N87">
-        <v>3.01</v>
+        <v>4.2</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -12152,10 +12152,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC87">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -12193,7 +12193,7 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D88" t="s">
         <v>134</v>
@@ -12220,13 +12220,13 @@
         <v>568</v>
       </c>
       <c r="L88">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M88">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N88">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -12268,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC88">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD88">
         <v>0</v>
@@ -12309,10 +12309,10 @@
         <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E89" t="s">
         <v>222</v>
@@ -12336,13 +12336,13 @@
         <v>568</v>
       </c>
       <c r="L89">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="M89">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="N89">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -12384,10 +12384,10 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD89">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>102</v>
       </c>
       <c r="D90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E90" t="s">
         <v>223</v>
@@ -12452,13 +12452,13 @@
         <v>568</v>
       </c>
       <c r="L90">
-        <v>3.65</v>
+        <v>2.08</v>
       </c>
       <c r="M90">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N90">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -12541,7 +12541,7 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D91" t="s">
         <v>133</v>
@@ -12657,7 +12657,7 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D92" t="s">
         <v>134</v>
@@ -12684,13 +12684,13 @@
         <v>568</v>
       </c>
       <c r="L92">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="M92">
-        <v>3.47</v>
+        <v>3.23</v>
       </c>
       <c r="N92">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12732,10 +12732,10 @@
         <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC92">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AD92">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D93" t="s">
         <v>134</v>
@@ -12800,13 +12800,13 @@
         <v>568</v>
       </c>
       <c r="L93">
-        <v>1.34</v>
+        <v>2.11</v>
       </c>
       <c r="M93">
-        <v>4.7</v>
+        <v>3.01</v>
       </c>
       <c r="N93">
-        <v>8</v>
+        <v>3.18</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AB93">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC93">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD93">
         <v>0</v>
@@ -12889,7 +12889,7 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
         <v>134</v>
@@ -13005,7 +13005,7 @@
         <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D95" t="s">
         <v>133</v>
@@ -13032,13 +13032,13 @@
         <v>568</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -13121,10 +13121,10 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E96" t="s">
         <v>229</v>
@@ -13148,13 +13148,13 @@
         <v>568</v>
       </c>
       <c r="L96">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="M96">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="N96">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -13196,10 +13196,10 @@
         <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC96">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13237,7 +13237,7 @@
         <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D97" t="s">
         <v>134</v>
@@ -13264,13 +13264,13 @@
         <v>568</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>0</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD97">
         <v>0</v>
@@ -13353,10 +13353,10 @@
         <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E98" t="s">
         <v>231</v>
@@ -13380,13 +13380,13 @@
         <v>568</v>
       </c>
       <c r="L98">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="M98">
-        <v>3.03</v>
+        <v>5</v>
       </c>
       <c r="N98">
-        <v>3.34</v>
+        <v>6.2</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC98">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD98">
         <v>0</v>
@@ -13469,10 +13469,10 @@
         <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D99" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E99" t="s">
         <v>232</v>
@@ -13496,13 +13496,13 @@
         <v>568</v>
       </c>
       <c r="L99">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="M99">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="N99">
-        <v>2.7</v>
+        <v>3.47</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13585,10 +13585,10 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D100" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E100" t="s">
         <v>233</v>
@@ -13612,13 +13612,13 @@
         <v>568</v>
       </c>
       <c r="L100">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="M100">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="N100">
-        <v>2.9</v>
+        <v>4.22</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13701,7 +13701,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D101" t="s">
         <v>134</v>
@@ -13728,13 +13728,13 @@
         <v>568</v>
       </c>
       <c r="L101">
-        <v>2.28</v>
+        <v>3.65</v>
       </c>
       <c r="M101">
-        <v>3.31</v>
+        <v>3.65</v>
       </c>
       <c r="N101">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC101">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13817,10 +13817,10 @@
         <v>53</v>
       </c>
       <c r="C102" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E102" t="s">
         <v>235</v>
@@ -13844,13 +13844,13 @@
         <v>568</v>
       </c>
       <c r="L102">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="M102">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N102">
-        <v>3.72</v>
+        <v>2.7</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC102">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13933,10 +13933,10 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E103" t="s">
         <v>236</v>
@@ -13960,13 +13960,13 @@
         <v>568</v>
       </c>
       <c r="L103">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="M103">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="N103">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -14008,10 +14008,10 @@
         <v>0</v>
       </c>
       <c r="AB103">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC103">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD103">
         <v>0</v>
@@ -14049,7 +14049,7 @@
         <v>53</v>
       </c>
       <c r="C104" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
         <v>134</v>
@@ -14076,13 +14076,13 @@
         <v>568</v>
       </c>
       <c r="L104">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M104">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -14424,13 +14424,13 @@
         <v>568</v>
       </c>
       <c r="L107">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N107">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -14472,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="AB107">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC107">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD107">
         <v>0</v>
@@ -14540,13 +14540,13 @@
         <v>568</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -14588,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD108">
         <v>0</v>
@@ -14656,13 +14656,13 @@
         <v>568</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD109">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D110" t="s">
         <v>134</v>
@@ -14772,58 +14772,58 @@
         <v>568</v>
       </c>
       <c r="L110">
+        <v>2.39</v>
+      </c>
+      <c r="M110">
+        <v>3.25</v>
+      </c>
+      <c r="N110">
+        <v>2.92</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110">
+        <v>0</v>
+      </c>
+      <c r="V110">
+        <v>0</v>
+      </c>
+      <c r="W110">
+        <v>0</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>0</v>
+      </c>
+      <c r="AA110">
+        <v>0</v>
+      </c>
+      <c r="AB110">
+        <v>2.13</v>
+      </c>
+      <c r="AC110">
         <v>1.72</v>
-      </c>
-      <c r="M110">
-        <v>3.64</v>
-      </c>
-      <c r="N110">
-        <v>3.8</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>0</v>
-      </c>
-      <c r="R110">
-        <v>0</v>
-      </c>
-      <c r="S110">
-        <v>0</v>
-      </c>
-      <c r="T110">
-        <v>0</v>
-      </c>
-      <c r="U110">
-        <v>0</v>
-      </c>
-      <c r="V110">
-        <v>0</v>
-      </c>
-      <c r="W110">
-        <v>0</v>
-      </c>
-      <c r="X110">
-        <v>0</v>
-      </c>
-      <c r="Y110">
-        <v>0</v>
-      </c>
-      <c r="Z110">
-        <v>0</v>
-      </c>
-      <c r="AA110">
-        <v>0</v>
-      </c>
-      <c r="AB110">
-        <v>1.77</v>
-      </c>
-      <c r="AC110">
-        <v>1.93</v>
       </c>
       <c r="AD110">
         <v>0</v>
@@ -14861,10 +14861,10 @@
         <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D111" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E111" t="s">
         <v>244</v>
@@ -14888,13 +14888,13 @@
         <v>568</v>
       </c>
       <c r="L111">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14936,10 +14936,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14977,7 +14977,7 @@
         <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D112" t="s">
         <v>134</v>
@@ -15093,7 +15093,7 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D113" t="s">
         <v>134</v>
@@ -15120,13 +15120,13 @@
         <v>568</v>
       </c>
       <c r="L113">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N113">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC113">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -15209,7 +15209,7 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D114" t="s">
         <v>134</v>
@@ -15325,10 +15325,10 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E115" t="s">
         <v>248</v>
@@ -15441,10 +15441,10 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E116" t="s">
         <v>249</v>
@@ -15468,13 +15468,13 @@
         <v>568</v>
       </c>
       <c r="L116">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M116">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N116">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -15557,7 +15557,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D117" t="s">
         <v>134</v>
@@ -15673,7 +15673,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D118" t="s">
         <v>134</v>
@@ -15789,10 +15789,10 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D119" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E119" t="s">
         <v>252</v>
@@ -15816,13 +15816,13 @@
         <v>568</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M119">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -15905,7 +15905,7 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D120" t="s">
         <v>134</v>
@@ -15932,13 +15932,13 @@
         <v>568</v>
       </c>
       <c r="L120">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M120">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N120">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15980,10 +15980,10 @@
         <v>0</v>
       </c>
       <c r="AB120">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC120">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -16021,7 +16021,7 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D121" t="s">
         <v>134</v>
@@ -16253,7 +16253,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
@@ -16369,7 +16369,7 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D124" t="s">
         <v>134</v>
@@ -16512,13 +16512,13 @@
         <v>568</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16560,10 +16560,10 @@
         <v>0</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD125">
         <v>0</v>
@@ -16601,10 +16601,10 @@
         <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E126" t="s">
         <v>259</v>
@@ -16628,13 +16628,13 @@
         <v>568</v>
       </c>
       <c r="L126">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16676,10 +16676,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16717,10 +16717,10 @@
         <v>55</v>
       </c>
       <c r="C127" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D127" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E127" t="s">
         <v>260</v>
@@ -16833,7 +16833,7 @@
         <v>55</v>
       </c>
       <c r="C128" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D128" t="s">
         <v>134</v>
@@ -16976,13 +16976,13 @@
         <v>568</v>
       </c>
       <c r="L129">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M129">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -17024,10 +17024,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC129">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -17065,7 +17065,7 @@
         <v>56</v>
       </c>
       <c r="C130" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D130" t="s">
         <v>134</v>
@@ -17092,13 +17092,13 @@
         <v>568</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -17181,7 +17181,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -17208,13 +17208,13 @@
         <v>568</v>
       </c>
       <c r="L131">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="M131">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N131">
-        <v>3.8</v>
+        <v>3.19</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17297,7 +17297,7 @@
         <v>56</v>
       </c>
       <c r="C132" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D132" t="s">
         <v>134</v>
@@ -17324,13 +17324,13 @@
         <v>568</v>
       </c>
       <c r="L132">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="M132">
-        <v>3.33</v>
+        <v>2.94</v>
       </c>
       <c r="N132">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD132">
         <v>0</v>
@@ -17672,13 +17672,13 @@
         <v>568</v>
       </c>
       <c r="L135">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="M135">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N135">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17720,10 +17720,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17761,10 +17761,10 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E136" t="s">
         <v>269</v>
@@ -17788,13 +17788,13 @@
         <v>568</v>
       </c>
       <c r="L136">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="M136">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="N136">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17836,10 +17836,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC136">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17877,10 +17877,10 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D137" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E137" t="s">
         <v>270</v>
@@ -17904,13 +17904,13 @@
         <v>568</v>
       </c>
       <c r="L137">
-        <v>3.39</v>
+        <v>1.75</v>
       </c>
       <c r="M137">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="N137">
-        <v>1.8</v>
+        <v>3.71</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AB137">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC137">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD137">
         <v>0</v>
@@ -17993,10 +17993,10 @@
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D138" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E138" t="s">
         <v>271</v>
@@ -18020,13 +18020,13 @@
         <v>568</v>
       </c>
       <c r="L138">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="M138">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="N138">
-        <v>2.44</v>
+        <v>3.94</v>
       </c>
       <c r="O138">
         <v>0</v>
@@ -18074,10 +18074,10 @@
         <v>0</v>
       </c>
       <c r="AD138">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE138">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF138">
         <v>0</v>
@@ -18109,7 +18109,7 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D139" t="s">
         <v>134</v>
@@ -18228,7 +18228,7 @@
         <v>120</v>
       </c>
       <c r="D140" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E140" t="s">
         <v>273</v>
@@ -18252,13 +18252,13 @@
         <v>568</v>
       </c>
       <c r="L140">
-        <v>1.82</v>
+        <v>3.39</v>
       </c>
       <c r="M140">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="N140">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -18300,10 +18300,10 @@
         <v>0</v>
       </c>
       <c r="AB140">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC140">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD140">
         <v>0</v>
@@ -18341,7 +18341,7 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D141" t="s">
         <v>134</v>
@@ -18368,13 +18368,13 @@
         <v>568</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18457,10 +18457,10 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D142" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E142" t="s">
         <v>275</v>
@@ -18484,13 +18484,13 @@
         <v>568</v>
       </c>
       <c r="L142">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="M142">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N142">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="O142">
         <v>0</v>
@@ -18532,10 +18532,10 @@
         <v>0</v>
       </c>
       <c r="AB142">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC142">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD142">
         <v>0</v>
@@ -18573,10 +18573,10 @@
         <v>58</v>
       </c>
       <c r="C143" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D143" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
@@ -18600,13 +18600,13 @@
         <v>568</v>
       </c>
       <c r="L143">
-        <v>6</v>
+        <v>2.41</v>
       </c>
       <c r="M143">
-        <v>3.97</v>
+        <v>3.39</v>
       </c>
       <c r="N143">
-        <v>1.43</v>
+        <v>2.44</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -18648,16 +18648,16 @@
         <v>0</v>
       </c>
       <c r="AB143">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF143">
         <v>0</v>
@@ -18689,7 +18689,7 @@
         <v>58</v>
       </c>
       <c r="C144" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D144" t="s">
         <v>134</v>
@@ -18716,13 +18716,13 @@
         <v>568</v>
       </c>
       <c r="L144">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="M144">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N144">
-        <v>1.8</v>
+        <v>3.47</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -18764,10 +18764,10 @@
         <v>0</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD144">
         <v>0</v>
@@ -18805,7 +18805,7 @@
         <v>59</v>
       </c>
       <c r="C145" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D145" t="s">
         <v>134</v>
@@ -19037,10 +19037,10 @@
         <v>60</v>
       </c>
       <c r="C147" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E147" t="s">
         <v>280</v>
@@ -19153,7 +19153,7 @@
         <v>60</v>
       </c>
       <c r="C148" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D148" t="s">
         <v>134</v>
@@ -19180,13 +19180,13 @@
         <v>568</v>
       </c>
       <c r="L148">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M148">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N148">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -19228,16 +19228,16 @@
         <v>0</v>
       </c>
       <c r="AB148">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC148">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD148">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE148">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF148">
         <v>0</v>
@@ -19269,10 +19269,10 @@
         <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D149" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E149" t="s">
         <v>282</v>
@@ -19296,13 +19296,13 @@
         <v>568</v>
       </c>
       <c r="L149">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M149">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -19344,16 +19344,16 @@
         <v>0</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF149">
         <v>0</v>
@@ -19501,7 +19501,7 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D151" t="s">
         <v>134</v>
@@ -19528,13 +19528,13 @@
         <v>568</v>
       </c>
       <c r="L151">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="M151">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N151">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -19576,16 +19576,16 @@
         <v>0</v>
       </c>
       <c r="AB151">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC151">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD151">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AE151">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF151">
         <v>0</v>
@@ -19617,10 +19617,10 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D152" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E152" t="s">
         <v>285</v>
@@ -19644,13 +19644,13 @@
         <v>568</v>
       </c>
       <c r="L152">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M152">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19698,10 +19698,10 @@
         <v>0</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF152">
         <v>0</v>
@@ -19733,7 +19733,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D153" t="s">
         <v>134</v>
@@ -19760,13 +19760,13 @@
         <v>568</v>
       </c>
       <c r="L153">
-        <v>6.9</v>
+        <v>2.91</v>
       </c>
       <c r="M153">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="N153">
-        <v>1.34</v>
+        <v>2.23</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -19808,16 +19808,16 @@
         <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC153">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD153">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE153">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF153">
         <v>0</v>
@@ -19849,10 +19849,10 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D154" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E154" t="s">
         <v>287</v>
@@ -19876,13 +19876,13 @@
         <v>568</v>
       </c>
       <c r="L154">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M154">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N154">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -19930,10 +19930,10 @@
         <v>0</v>
       </c>
       <c r="AD154">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE154">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF154">
         <v>0</v>
@@ -19965,7 +19965,7 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D155" t="s">
         <v>134</v>
@@ -19992,13 +19992,13 @@
         <v>568</v>
       </c>
       <c r="L155">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="M155">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N155">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -20040,16 +20040,16 @@
         <v>0</v>
       </c>
       <c r="AB155">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC155">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD155">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF155">
         <v>0</v>
@@ -20313,7 +20313,7 @@
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D158" t="s">
         <v>134</v>
@@ -20429,7 +20429,7 @@
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D159" t="s">
         <v>134</v>
@@ -20545,7 +20545,7 @@
         <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D160" t="s">
         <v>134</v>
@@ -20569,7 +20569,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -20685,7 +20685,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -21009,7 +21009,7 @@
         <v>64</v>
       </c>
       <c r="C164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D164" t="s">
         <v>134</v>
@@ -21125,7 +21125,7 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D165" t="s">
         <v>134</v>
@@ -21152,13 +21152,13 @@
         <v>568</v>
       </c>
       <c r="L165">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M165">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N165">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="AB165">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC165">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD165">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>64</v>
       </c>
       <c r="C166" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D166" t="s">
         <v>134</v>
@@ -21357,7 +21357,7 @@
         <v>64</v>
       </c>
       <c r="C167" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D167" t="s">
         <v>134</v>
@@ -21384,13 +21384,13 @@
         <v>568</v>
       </c>
       <c r="L167">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M167">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -21432,10 +21432,10 @@
         <v>0</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD167">
         <v>0</v>
@@ -21473,7 +21473,7 @@
         <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D168" t="s">
         <v>134</v>
@@ -21500,13 +21500,13 @@
         <v>568</v>
       </c>
       <c r="L168">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="M168">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N168">
-        <v>2.83</v>
+        <v>6.8</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -21548,16 +21548,16 @@
         <v>0</v>
       </c>
       <c r="AB168">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC168">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF168">
         <v>0</v>
@@ -21589,7 +21589,7 @@
         <v>65</v>
       </c>
       <c r="C169" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D169" t="s">
         <v>134</v>
@@ -21616,10 +21616,10 @@
         <v>568</v>
       </c>
       <c r="L169">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M169">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="N169">
         <v>6.8</v>
@@ -21670,10 +21670,10 @@
         <v>0</v>
       </c>
       <c r="AD169">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AE169">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AF169">
         <v>0</v>
@@ -21705,7 +21705,7 @@
         <v>65</v>
       </c>
       <c r="C170" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="D170" t="s">
         <v>134</v>
@@ -21732,13 +21732,13 @@
         <v>568</v>
       </c>
       <c r="L170">
-        <v>3.71</v>
+        <v>2.26</v>
       </c>
       <c r="M170">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N170">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -21780,10 +21780,10 @@
         <v>0</v>
       </c>
       <c r="AB170">
+        <v>1.57</v>
+      </c>
+      <c r="AC170">
         <v>2.15</v>
-      </c>
-      <c r="AC170">
-        <v>1.7</v>
       </c>
       <c r="AD170">
         <v>0</v>
@@ -21821,7 +21821,7 @@
         <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D171" t="s">
         <v>134</v>
@@ -21848,13 +21848,13 @@
         <v>568</v>
       </c>
       <c r="L171">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="M171">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -21896,10 +21896,10 @@
         <v>0</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD171">
         <v>0</v>
@@ -22053,7 +22053,7 @@
         <v>66</v>
       </c>
       <c r="C173" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D173" t="s">
         <v>134</v>
@@ -22169,7 +22169,7 @@
         <v>67</v>
       </c>
       <c r="C174" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D174" t="s">
         <v>133</v>
@@ -22178,7 +22178,7 @@
         <v>307</v>
       </c>
       <c r="F174" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -22285,16 +22285,16 @@
         <v>67</v>
       </c>
       <c r="C175" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E175" t="s">
         <v>308</v>
       </c>
       <c r="F175" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -22312,13 +22312,13 @@
         <v>568</v>
       </c>
       <c r="L175">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M175">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O175">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>0</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD175">
         <v>0</v>
@@ -22410,7 +22410,7 @@
         <v>309</v>
       </c>
       <c r="F176" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -22517,16 +22517,16 @@
         <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D177" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E177" t="s">
         <v>310</v>
       </c>
       <c r="F177" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -22660,13 +22660,13 @@
         <v>568</v>
       </c>
       <c r="L178">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M178">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N178">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O178">
         <v>0</v>
@@ -22708,10 +22708,10 @@
         <v>0</v>
       </c>
       <c r="AB178">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC178">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD178">
         <v>0</v>
@@ -24632,13 +24632,13 @@
         <v>568</v>
       </c>
       <c r="L195">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M195">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N195">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -24680,10 +24680,10 @@
         <v>0</v>
       </c>
       <c r="AB195">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC195">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD195">
         <v>0</v>
@@ -24864,13 +24864,13 @@
         <v>568</v>
       </c>
       <c r="L197">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M197">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -24912,10 +24912,10 @@
         <v>0</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD197">
         <v>0</v>
@@ -25765,7 +25765,7 @@
         <v>72</v>
       </c>
       <c r="C205" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D205" t="s">
         <v>133</v>
@@ -25792,13 +25792,13 @@
         <v>568</v>
       </c>
       <c r="L205">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M205">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N205">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O205">
         <v>0</v>
@@ -25840,10 +25840,10 @@
         <v>0</v>
       </c>
       <c r="AB205">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC205">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD205">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>72</v>
       </c>
       <c r="C206" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D206" t="s">
         <v>133</v>
@@ -25908,13 +25908,13 @@
         <v>568</v>
       </c>
       <c r="L206">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M206">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O206">
         <v>0</v>
@@ -25956,10 +25956,10 @@
         <v>0</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC206">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD206">
         <v>0</v>
@@ -26113,7 +26113,7 @@
         <v>73</v>
       </c>
       <c r="C208" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D208" t="s">
         <v>133</v>
@@ -26345,7 +26345,7 @@
         <v>73</v>
       </c>
       <c r="C210" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D210" t="s">
         <v>133</v>
@@ -26461,7 +26461,7 @@
         <v>74</v>
       </c>
       <c r="C211" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D211" t="s">
         <v>133</v>
@@ -26488,13 +26488,13 @@
         <v>568</v>
       </c>
       <c r="L211">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="M211">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N211">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -26536,10 +26536,10 @@
         <v>0</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD211">
         <v>0</v>
@@ -26577,7 +26577,7 @@
         <v>74</v>
       </c>
       <c r="C212" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D212" t="s">
         <v>133</v>
@@ -26604,13 +26604,13 @@
         <v>568</v>
       </c>
       <c r="L212">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="M212">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N212">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -26652,10 +26652,10 @@
         <v>0</v>
       </c>
       <c r="AB212">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC212">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD212">
         <v>0</v>
@@ -26952,13 +26952,13 @@
         <v>568</v>
       </c>
       <c r="L215">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="M215">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N215">
-        <v>2.29</v>
+        <v>4.6</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -27000,10 +27000,10 @@
         <v>0</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD215">
         <v>0</v>
@@ -27068,13 +27068,13 @@
         <v>568</v>
       </c>
       <c r="L216">
-        <v>1.61</v>
+        <v>2.95</v>
       </c>
       <c r="M216">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N216">
-        <v>4.6</v>
+        <v>2.29</v>
       </c>
       <c r="O216">
         <v>0</v>
@@ -27116,10 +27116,10 @@
         <v>0</v>
       </c>
       <c r="AB216">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC216">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD216">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -259,24 +259,24 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
     <t>China China League One</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>England EFL League Two</t>
   </si>
   <si>
@@ -319,22 +319,31 @@
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Scotland Championship</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Czech Republic First League</t>
@@ -346,18 +355,9 @@
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t>Switzerland Super League</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Slovakia Super Liga</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -445,45 +445,45 @@
     <t>Ventforet Kofu</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
     <t>Fujieda MYFC</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
   </si>
   <si>
     <t>JEF United</t>
   </si>
   <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
@@ -493,42 +493,42 @@
     <t>Shaanxi Union</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
+    <t>Paderborn</t>
+  </si>
+  <si>
+    <t>Elversberg</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Darmstadt 98</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Elversberg</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
+    <t>Karlsruher SC</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
-    <t>Paderborn</t>
-  </si>
-  <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
@@ -544,21 +544,21 @@
     <t>Astana</t>
   </si>
   <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
@@ -592,163 +592,205 @@
     <t>Nieciecza</t>
   </si>
   <si>
+    <t>Naftan</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
     <t>Utsikten</t>
   </si>
   <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Naftan</t>
+    <t>Ufa</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Trelleborg</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Ufa</t>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Colchester United</t>
+  </si>
+  <si>
+    <t>Grimsby Town</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Salford City</t>
+  </si>
+  <si>
+    <t>Shrewsbury Town</t>
+  </si>
+  <si>
+    <t>Cambridge United</t>
   </si>
   <si>
     <t>Milton Keynes Dons</t>
   </si>
   <si>
-    <t>Walsall</t>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Termez Surkhon</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Burton Albion</t>
+  </si>
+  <si>
+    <t>Lincoln City</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>Egersund</t>
   </si>
   <si>
     <t>Newport County</t>
   </si>
   <si>
-    <t>Blackpool</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Barnet</t>
-  </si>
-  <si>
-    <t>Salford City</t>
-  </si>
-  <si>
-    <t>Bristol Rovers</t>
-  </si>
-  <si>
-    <t>Shrewsbury Town</t>
-  </si>
-  <si>
-    <t>Chesterfield</t>
-  </si>
-  <si>
-    <t>Colchester United</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Lincoln City</t>
-  </si>
-  <si>
-    <t>Cambridge United</t>
-  </si>
-  <si>
-    <t>Grimsby Town</t>
-  </si>
-  <si>
-    <t>Termez Surkhon</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
   </si>
   <si>
     <t>Plymouth Argyle</t>
   </si>
   <si>
-    <t>ÍBV</t>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>KuPS</t>
+  </si>
+  <si>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Huddersfield Town</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Airdrieonians</t>
+  </si>
+  <si>
+    <t>St. Johnstone</t>
   </si>
   <si>
     <t>Raith Rovers</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
+    <t>Greenock Morton</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
   </si>
   <si>
     <t>Ural</t>
   </si>
   <si>
-    <t>Stabæk</t>
-  </si>
-  <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>KuPS</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Greenock Morton</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Huddersfield Town</t>
-  </si>
-  <si>
-    <t>St. Johnstone</t>
-  </si>
-  <si>
-    <t>Airdrieonians</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>KVC Westerlo</t>
+    <t>MSV Duisburg</t>
   </si>
   <si>
     <t>KAMAZ</t>
   </si>
   <si>
-    <t>MSV Duisburg</t>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Karviná</t>
   </si>
   <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
     <t>Rostov</t>
   </si>
   <si>
+    <t>Slavia</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
     <t>Hajduk Split</t>
   </si>
   <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Levski Sofia</t>
+  </si>
+  <si>
     <t>Zorya</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
   </si>
   <si>
     <t>Rijeka</t>
@@ -757,184 +799,145 @@
     <t>Posusje</t>
   </si>
   <si>
-    <t>Varaždin</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
     <t>Velež</t>
   </si>
   <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Slavia</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
-  </si>
-  <si>
-    <t>Teplice</t>
+    <t>Stal Rzeszów</t>
   </si>
   <si>
     <t>Mura</t>
   </si>
   <si>
+    <t>Argeș</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
     <t>Widzew Łódź</t>
   </si>
   <si>
-    <t>Stal Rzeszów</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
     <t>Diósgyőr</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
     <t>Servette</t>
   </si>
   <si>
     <t>Oulu</t>
   </si>
   <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
-    <t>Zemplín Michalovce</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
     <t>Magallanes</t>
   </si>
   <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
     <t>Unión Española</t>
   </si>
   <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
     <t>Ried</t>
   </si>
   <si>
+    <t>Olimpiyets</t>
+  </si>
+  <si>
     <t>Krasnodar</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>07 Vestur</t>
-  </si>
-  <si>
-    <t>Olimpiyets</t>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>LFK Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
   </si>
   <si>
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Austria Wien II</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>LFK Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
+    <t>Primorje</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
+  </si>
+  <si>
+    <t>Ferencváros</t>
   </si>
   <si>
     <t>Ludogorets</t>
   </si>
   <si>
-    <t>Primorje</t>
-  </si>
-  <si>
-    <t>Ferencváros</t>
-  </si>
-  <si>
-    <t>Lech Poznań</t>
+    <t>Dinamo Bucureşti</t>
+  </si>
+  <si>
+    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Basel</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Dinamo Bucureşti</t>
+    <t>KAA Gent</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>KAA Gent</t>
+    <t>Coquimbo Unido</t>
   </si>
   <si>
     <t>Cobreloa</t>
@@ -943,54 +946,51 @@
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Coquimbo Unido</t>
+    <t>Novorizontino</t>
   </si>
   <si>
     <t>Osijek</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
     <t>Temperley</t>
   </si>
   <si>
@@ -1096,45 +1096,45 @@
     <t>Montedio Yamagata</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
     <t>Renofa Yamaguchi</t>
   </si>
   <si>
-    <t>Seongnam</t>
+    <t>Ehime</t>
+  </si>
+  <si>
+    <t>Imabari</t>
   </si>
   <si>
     <t>Iwaki</t>
   </si>
   <si>
-    <t>Imabari</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Ehime</t>
-  </si>
-  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
@@ -1144,42 +1144,42 @@
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Telavi</t>
+  </si>
+  <si>
+    <t>Gareji</t>
+  </si>
+  <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Kolkheti Poti</t>
   </si>
   <si>
-    <t>Telavi</t>
-  </si>
-  <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>Guangzhou E-Power</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Gagra</t>
+    <t>Preußen Münster</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Preußen Münster</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Gareji</t>
-  </si>
-  <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
@@ -1195,21 +1195,21 @@
     <t>Kaisar</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Alemannia Aachen</t>
+  </si>
+  <si>
     <t>Saarbrucken</t>
   </si>
   <si>
+    <t>Ulytau</t>
+  </si>
+  <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Alemannia Aachen</t>
-  </si>
-  <si>
-    <t>Ulytau</t>
-  </si>
-  <si>
     <t>Tobol</t>
   </si>
   <si>
@@ -1243,163 +1243,205 @@
     <t>Pogoń Szczecin</t>
   </si>
   <si>
+    <t>Minsk</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Minsk</t>
+    <t>Shinnik</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
   </si>
   <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Shinnik</t>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Tranmere Rovers</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Swindon Town</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Crewe Alexandra</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Cheltenham Town</t>
   </si>
   <si>
     <t>Oldham Athletic</t>
   </si>
   <si>
-    <t>Swindon Town</t>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Mansfield Town</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Harrogate Town</t>
+  </si>
+  <si>
+    <t>Odd</t>
   </si>
   <si>
     <t>Notts County</t>
   </si>
   <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Gillingham</t>
-  </si>
-  <si>
-    <t>Kokand-1912</t>
-  </si>
-  <si>
-    <t>Fleetwood Town</t>
-  </si>
-  <si>
-    <t>Crewe Alexandra</t>
-  </si>
-  <si>
-    <t>Harrogate Town</t>
-  </si>
-  <si>
-    <t>Bromley</t>
-  </si>
-  <si>
-    <t>Barrow</t>
-  </si>
-  <si>
-    <t>Tranmere Rovers</t>
-  </si>
-  <si>
-    <t>Mansfield Town</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Cheltenham Town</t>
-  </si>
-  <si>
-    <t>Crawley Town</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Wycombe Wanderers</t>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
   </si>
   <si>
     <t>Barnsley</t>
   </si>
   <si>
-    <t>KR</t>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Haka</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Ross County</t>
+  </si>
+  <si>
+    <t>Partick Thistle</t>
   </si>
   <si>
     <t>Queen's Park</t>
   </si>
   <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
+    <t>Dunfermline Athletic</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
   </si>
   <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Kongsvinger</t>
-  </si>
-  <si>
-    <t>Haka</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Northampton Town</t>
-  </si>
-  <si>
-    <t>Dunfermline Athletic</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Exeter City</t>
-  </si>
-  <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Leyton Orient</t>
-  </si>
-  <si>
-    <t>Partick Thistle</t>
-  </si>
-  <si>
-    <t>Ross County</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
+    <t>Stuttgart II</t>
   </si>
   <si>
     <t>Chelyabinsk</t>
   </si>
   <si>
-    <t>Stuttgart II</t>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
   </si>
   <si>
     <t>Zlín</t>
   </si>
   <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
+    <t>Isloch</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
     <t>Istra 1961</t>
   </si>
   <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
     <t>LNZ Cherkasy</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
   </si>
   <si>
     <t>Slaven Koprivnica</t>
@@ -1408,235 +1450,193 @@
     <t>Željezničar</t>
   </si>
   <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
     <t>Borac Banja Luka</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Isloch</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
+    <t>Chrobry Głogów</t>
   </si>
   <si>
     <t>Aluminij</t>
   </si>
   <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>St. Gallen</t>
   </si>
   <si>
     <t>Jaro</t>
   </si>
   <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>Skalica</t>
+  </si>
+  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Skalica</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
-    <t>CSKA Sofia</t>
-  </si>
-  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Komárno</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
     <t>Curicó Unido</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
     <t>La Serena</t>
   </si>
   <si>
     <t>Volga Ulyanovsk</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
     <t>Salzburg</t>
   </si>
   <si>
+    <t>Lokomotiv Moskva</t>
+  </si>
+  <si>
     <t>Dinamo Moskva</t>
   </si>
   <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>Lokomotiv Moskva</t>
+    <t>Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>IMT Novi Beograd</t>
   </si>
   <si>
     <t>Spartak Subotica</t>
   </si>
   <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>St. Pölten</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>IMT Novi Beograd</t>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Górnik Zabrze</t>
+  </si>
+  <si>
+    <t>Kazincbarcika</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Kazincbarcika</t>
-  </si>
-  <si>
-    <t>Górnik Zabrze</t>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Podbrezová</t>
   </si>
   <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Podbrezová</t>
-  </si>
-  <si>
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
-    <t>FCSB</t>
+    <t>RAAL La Louvière</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
+    <t>Deportes Limache</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Deportes Limache</t>
+    <t>Avaí</t>
   </si>
   <si>
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
   </si>
   <si>
     <t>San Telmo</t>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC6">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
         <v>133</v>
@@ -3172,13 +3172,13 @@
         <v>568</v>
       </c>
       <c r="L10">
-        <v>2.36</v>
+        <v>1.64</v>
       </c>
       <c r="M10">
-        <v>2.98</v>
+        <v>3.67</v>
       </c>
       <c r="N10">
-        <v>2.77</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -3288,13 +3288,13 @@
         <v>568</v>
       </c>
       <c r="L11">
-        <v>1.88</v>
+        <v>4.5</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N11">
-        <v>3.51</v>
+        <v>1.5</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -3336,10 +3336,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -3404,13 +3404,13 @@
         <v>568</v>
       </c>
       <c r="L12">
-        <v>2.07</v>
+        <v>2.57</v>
       </c>
       <c r="M12">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="N12">
-        <v>3.03</v>
+        <v>2.49</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -3452,10 +3452,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -3520,13 +3520,13 @@
         <v>568</v>
       </c>
       <c r="L13">
-        <v>2.86</v>
+        <v>4.9</v>
       </c>
       <c r="M13">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="N13">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3574,10 +3574,10 @@
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -3609,7 +3609,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>133</v>
@@ -3636,13 +3636,13 @@
         <v>568</v>
       </c>
       <c r="L14">
-        <v>3.41</v>
+        <v>2.38</v>
       </c>
       <c r="M14">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N14">
-        <v>1.88</v>
+        <v>2.54</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -3752,13 +3752,13 @@
         <v>568</v>
       </c>
       <c r="L15">
-        <v>2.38</v>
+        <v>3.41</v>
       </c>
       <c r="M15">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="N15">
-        <v>2.54</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC15">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>568</v>
       </c>
       <c r="L16">
-        <v>1.64</v>
+        <v>3.18</v>
       </c>
       <c r="M16">
-        <v>3.67</v>
+        <v>3.05</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>2.09</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -3984,13 +3984,13 @@
         <v>568</v>
       </c>
       <c r="L17">
-        <v>2.57</v>
+        <v>1.88</v>
       </c>
       <c r="M17">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="N17">
-        <v>2.49</v>
+        <v>3.51</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4032,10 +4032,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4100,13 +4100,13 @@
         <v>568</v>
       </c>
       <c r="L18">
-        <v>4.5</v>
+        <v>3.23</v>
       </c>
       <c r="M18">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="N18">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4216,13 +4216,13 @@
         <v>568</v>
       </c>
       <c r="L19">
-        <v>4.9</v>
+        <v>2.36</v>
       </c>
       <c r="M19">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="N19">
-        <v>1.53</v>
+        <v>2.77</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4264,10 +4264,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4332,13 +4332,13 @@
         <v>568</v>
       </c>
       <c r="L20">
-        <v>3.18</v>
+        <v>1.62</v>
       </c>
       <c r="M20">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="N20">
-        <v>2.09</v>
+        <v>4.6</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -4421,7 +4421,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4448,13 +4448,13 @@
         <v>568</v>
       </c>
       <c r="L21">
-        <v>3.23</v>
+        <v>2.86</v>
       </c>
       <c r="M21">
-        <v>3.38</v>
+        <v>2.87</v>
       </c>
       <c r="N21">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AC21">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4564,13 +4564,13 @@
         <v>568</v>
       </c>
       <c r="L22">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="M22">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4612,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -5028,13 +5028,13 @@
         <v>568</v>
       </c>
       <c r="L26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -5117,7 +5117,7 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
         <v>133</v>
@@ -5233,7 +5233,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>133</v>
@@ -5349,10 +5349,10 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
         <v>162</v>
@@ -5376,13 +5376,13 @@
         <v>568</v>
       </c>
       <c r="L29">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -5424,16 +5424,16 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF29">
         <v>0</v>
@@ -5465,7 +5465,7 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>133</v>
@@ -5492,13 +5492,13 @@
         <v>568</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5540,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -5608,13 +5608,13 @@
         <v>568</v>
       </c>
       <c r="L31">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="M31">
-        <v>3.84</v>
+        <v>3.66</v>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5656,16 +5656,16 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE31">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -5697,10 +5697,10 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
         <v>165</v>
@@ -5724,13 +5724,13 @@
         <v>568</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5772,16 +5772,16 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
         <v>133</v>
@@ -5929,10 +5929,10 @@
         <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
@@ -5956,13 +5956,13 @@
         <v>568</v>
       </c>
       <c r="L34">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -6072,13 +6072,13 @@
         <v>568</v>
       </c>
       <c r="L35">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="M35">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="N35">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -6120,16 +6120,16 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE35">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -6161,10 +6161,10 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
         <v>169</v>
@@ -6188,13 +6188,13 @@
         <v>568</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -6236,10 +6236,10 @@
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -6277,7 +6277,7 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
         <v>133</v>
@@ -6973,10 +6973,10 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
         <v>176</v>
@@ -7089,10 +7089,10 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
         <v>177</v>
@@ -7205,10 +7205,10 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E45" t="s">
         <v>178</v>
@@ -7321,10 +7321,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
         <v>179</v>
@@ -8214,10 +8214,10 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -8829,7 +8829,7 @@
         <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
         <v>133</v>
@@ -8856,13 +8856,13 @@
         <v>568</v>
       </c>
       <c r="L59">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="M59">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N59">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
         <v>133</v>
@@ -9020,10 +9020,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -9061,7 +9061,7 @@
         <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
         <v>133</v>
@@ -9088,13 +9088,13 @@
         <v>568</v>
       </c>
       <c r="L61">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="M61">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N61">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -9136,10 +9136,10 @@
         <v>0</v>
       </c>
       <c r="AB61">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC61">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -9177,10 +9177,10 @@
         <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E62" t="s">
         <v>195</v>
@@ -9204,13 +9204,13 @@
         <v>568</v>
       </c>
       <c r="L62">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -9293,7 +9293,7 @@
         <v>52</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D63" t="s">
         <v>133</v>
@@ -9409,10 +9409,10 @@
         <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
         <v>197</v>
@@ -9436,13 +9436,13 @@
         <v>568</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -9484,10 +9484,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -9552,58 +9552,58 @@
         <v>568</v>
       </c>
       <c r="L65">
+        <v>2.74</v>
+      </c>
+      <c r="M65">
+        <v>2.91</v>
+      </c>
+      <c r="N65">
+        <v>2.44</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>2.1</v>
+      </c>
+      <c r="AC65">
         <v>1.67</v>
-      </c>
-      <c r="M65">
-        <v>3.79</v>
-      </c>
-      <c r="N65">
-        <v>3.89</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>1.83</v>
-      </c>
-      <c r="AC65">
-        <v>1.87</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9668,13 +9668,13 @@
         <v>568</v>
       </c>
       <c r="L66">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="M66">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="N66">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AC66">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9784,13 +9784,13 @@
         <v>568</v>
       </c>
       <c r="L67">
-        <v>4.6</v>
+        <v>2.02</v>
       </c>
       <c r="M67">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="N67">
-        <v>1.57</v>
+        <v>3.01</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9873,7 +9873,7 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
@@ -9900,13 +9900,13 @@
         <v>568</v>
       </c>
       <c r="L68">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M68">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N68">
-        <v>3.59</v>
+        <v>2.92</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9948,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC68">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -10016,13 +10016,13 @@
         <v>568</v>
       </c>
       <c r="L69">
-        <v>2.74</v>
+        <v>1.9</v>
       </c>
       <c r="M69">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="N69">
-        <v>2.44</v>
+        <v>3.47</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10064,10 +10064,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC69">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E70" t="s">
         <v>203</v>
@@ -10132,13 +10132,13 @@
         <v>568</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10180,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD70">
         <v>0</v>
@@ -10248,13 +10248,13 @@
         <v>568</v>
       </c>
       <c r="L71">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="M71">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="N71">
-        <v>3.47</v>
+        <v>2.68</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10296,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AC71">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -10364,13 +10364,13 @@
         <v>568</v>
       </c>
       <c r="L72">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="M72">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
       <c r="N72">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10412,10 +10412,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC72">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -10480,13 +10480,13 @@
         <v>568</v>
       </c>
       <c r="L73">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="M73">
-        <v>3.32</v>
+        <v>3.79</v>
       </c>
       <c r="N73">
-        <v>3.79</v>
+        <v>3.89</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="AB73">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AC73">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AD73">
         <v>0</v>
@@ -10569,7 +10569,7 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -10596,13 +10596,13 @@
         <v>568</v>
       </c>
       <c r="L74">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="M74">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N74">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10644,10 +10644,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC74">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10685,10 +10685,10 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E75" t="s">
         <v>208</v>
@@ -10712,13 +10712,13 @@
         <v>568</v>
       </c>
       <c r="L75">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10760,10 +10760,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10801,10 +10801,10 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E76" t="s">
         <v>209</v>
@@ -10828,13 +10828,13 @@
         <v>568</v>
       </c>
       <c r="L76">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10876,10 +10876,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10917,7 +10917,7 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D77" t="s">
         <v>134</v>
@@ -10944,13 +10944,13 @@
         <v>568</v>
       </c>
       <c r="L77">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="M77">
-        <v>3.31</v>
+        <v>3.61</v>
       </c>
       <c r="N77">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC77">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11033,10 +11033,10 @@
         <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D78" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E78" t="s">
         <v>211</v>
@@ -11060,13 +11060,13 @@
         <v>568</v>
       </c>
       <c r="L78">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11108,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11149,7 +11149,7 @@
         <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D79" t="s">
         <v>134</v>
@@ -11176,13 +11176,13 @@
         <v>568</v>
       </c>
       <c r="L79">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="M79">
-        <v>3.47</v>
+        <v>3.06</v>
       </c>
       <c r="N79">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC79">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11265,7 +11265,7 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D80" t="s">
         <v>134</v>
@@ -11292,13 +11292,13 @@
         <v>568</v>
       </c>
       <c r="L80">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="M80">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N80">
-        <v>3.01</v>
+        <v>2.63</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11340,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC80">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -11381,10 +11381,10 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E81" t="s">
         <v>214</v>
@@ -11408,13 +11408,13 @@
         <v>568</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11497,7 +11497,7 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D82" t="s">
         <v>134</v>
@@ -11524,13 +11524,13 @@
         <v>568</v>
       </c>
       <c r="L82">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="M82">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="N82">
-        <v>2.68</v>
+        <v>3.79</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11572,10 +11572,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC82">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11613,10 +11613,10 @@
         <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D83" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s">
         <v>216</v>
@@ -11640,13 +11640,13 @@
         <v>568</v>
       </c>
       <c r="L83">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="M83">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="N83">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11688,10 +11688,10 @@
         <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E84" t="s">
         <v>217</v>
@@ -11756,13 +11756,13 @@
         <v>568</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E85" t="s">
         <v>218</v>
@@ -11872,13 +11872,13 @@
         <v>568</v>
       </c>
       <c r="L85">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="M85">
-        <v>4.7</v>
+        <v>3.41</v>
       </c>
       <c r="N85">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC85">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11961,10 +11961,10 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E86" t="s">
         <v>219</v>
@@ -11988,13 +11988,13 @@
         <v>568</v>
       </c>
       <c r="L86">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="M86">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="N86">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -12036,10 +12036,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -12080,7 +12080,7 @@
         <v>103</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E87" t="s">
         <v>220</v>
@@ -12104,13 +12104,13 @@
         <v>568</v>
       </c>
       <c r="L87">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -12152,10 +12152,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -12193,7 +12193,7 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s">
         <v>134</v>
@@ -12220,13 +12220,13 @@
         <v>568</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -12268,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD88">
         <v>0</v>
@@ -12309,7 +12309,7 @@
         <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D89" t="s">
         <v>133</v>
@@ -12425,7 +12425,7 @@
         <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
         <v>133</v>
@@ -12452,13 +12452,13 @@
         <v>568</v>
       </c>
       <c r="L90">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N90">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -12541,7 +12541,7 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D91" t="s">
         <v>133</v>
@@ -12568,13 +12568,13 @@
         <v>568</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D92" t="s">
         <v>134</v>
@@ -12684,13 +12684,13 @@
         <v>568</v>
       </c>
       <c r="L92">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="M92">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N92">
-        <v>3.45</v>
+        <v>2.82</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -12732,10 +12732,10 @@
         <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC92">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AD92">
         <v>0</v>
@@ -12773,10 +12773,10 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E93" t="s">
         <v>226</v>
@@ -12800,13 +12800,13 @@
         <v>568</v>
       </c>
       <c r="L93">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="M93">
-        <v>3.01</v>
+        <v>5</v>
       </c>
       <c r="N93">
-        <v>3.18</v>
+        <v>6.2</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AB93">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD93">
         <v>0</v>
@@ -12889,7 +12889,7 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D94" t="s">
         <v>134</v>
@@ -12916,13 +12916,13 @@
         <v>568</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -12964,10 +12964,10 @@
         <v>0</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD94">
         <v>0</v>
@@ -13005,10 +13005,10 @@
         <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D95" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E95" t="s">
         <v>228</v>
@@ -13032,13 +13032,13 @@
         <v>568</v>
       </c>
       <c r="L95">
-        <v>5.6</v>
+        <v>2.11</v>
       </c>
       <c r="M95">
-        <v>4.6</v>
+        <v>3.01</v>
       </c>
       <c r="N95">
-        <v>1.46</v>
+        <v>3.18</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD95">
         <v>0</v>
@@ -13121,10 +13121,10 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E96" t="s">
         <v>229</v>
@@ -13148,13 +13148,13 @@
         <v>568</v>
       </c>
       <c r="L96">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="M96">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N96">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -13196,10 +13196,10 @@
         <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13237,10 +13237,10 @@
         <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E97" t="s">
         <v>230</v>
@@ -13264,13 +13264,13 @@
         <v>568</v>
       </c>
       <c r="L97">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="M97">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N97">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>0</v>
       </c>
       <c r="AB97">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC97">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD97">
         <v>0</v>
@@ -13353,10 +13353,10 @@
         <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E98" t="s">
         <v>231</v>
@@ -13380,13 +13380,13 @@
         <v>568</v>
       </c>
       <c r="L98">
-        <v>1.39</v>
+        <v>3.65</v>
       </c>
       <c r="M98">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="N98">
-        <v>6.2</v>
+        <v>1.87</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD98">
         <v>0</v>
@@ -13469,7 +13469,7 @@
         <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D99" t="s">
         <v>134</v>
@@ -13496,13 +13496,13 @@
         <v>568</v>
       </c>
       <c r="L99">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="M99">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="N99">
-        <v>3.47</v>
+        <v>4.22</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13544,10 +13544,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13585,7 +13585,7 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
         <v>134</v>
@@ -13612,13 +13612,13 @@
         <v>568</v>
       </c>
       <c r="L100">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="M100">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="N100">
-        <v>4.22</v>
+        <v>8</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13660,10 +13660,10 @@
         <v>0</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13701,7 +13701,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
         <v>134</v>
@@ -13728,13 +13728,13 @@
         <v>568</v>
       </c>
       <c r="L101">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M101">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N101">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13776,10 +13776,10 @@
         <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC101">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD101">
         <v>0</v>
@@ -13817,10 +13817,10 @@
         <v>53</v>
       </c>
       <c r="C102" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D102" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E102" t="s">
         <v>235</v>
@@ -13844,13 +13844,13 @@
         <v>568</v>
       </c>
       <c r="L102">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="M102">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N102">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD102">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D103" t="s">
         <v>133</v>
@@ -13960,13 +13960,13 @@
         <v>568</v>
       </c>
       <c r="L103">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="M103">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N103">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -14049,7 +14049,7 @@
         <v>53</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D104" t="s">
         <v>134</v>
@@ -14165,7 +14165,7 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D105" t="s">
         <v>134</v>
@@ -14281,7 +14281,7 @@
         <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D106" t="s">
         <v>134</v>
@@ -14424,13 +14424,13 @@
         <v>568</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -14472,10 +14472,10 @@
         <v>0</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD107">
         <v>0</v>
@@ -14540,13 +14540,13 @@
         <v>568</v>
       </c>
       <c r="L108">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M108">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -14588,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="AB108">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD108">
         <v>0</v>
@@ -14656,13 +14656,13 @@
         <v>568</v>
       </c>
       <c r="L109">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD109">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D110" t="s">
         <v>134</v>
@@ -14772,13 +14772,13 @@
         <v>568</v>
       </c>
       <c r="L110">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M110">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14820,10 +14820,10 @@
         <v>0</v>
       </c>
       <c r="AB110">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD110">
         <v>0</v>
@@ -14861,7 +14861,7 @@
         <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D111" t="s">
         <v>134</v>
@@ -14977,10 +14977,10 @@
         <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D112" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E112" t="s">
         <v>245</v>
@@ -15004,13 +15004,13 @@
         <v>568</v>
       </c>
       <c r="L112">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -15052,10 +15052,10 @@
         <v>0</v>
       </c>
       <c r="AB112">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -15093,10 +15093,10 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E113" t="s">
         <v>246</v>
@@ -15120,13 +15120,13 @@
         <v>568</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -15209,7 +15209,7 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D114" t="s">
         <v>134</v>
@@ -15236,13 +15236,13 @@
         <v>568</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M114">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -15284,10 +15284,10 @@
         <v>0</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD114">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D115" t="s">
         <v>133</v>
@@ -15352,13 +15352,13 @@
         <v>568</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -15400,10 +15400,10 @@
         <v>0</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD115">
         <v>0</v>
@@ -15441,7 +15441,7 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D116" t="s">
         <v>134</v>
@@ -15557,7 +15557,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D117" t="s">
         <v>134</v>
@@ -15673,7 +15673,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D118" t="s">
         <v>134</v>
@@ -15700,13 +15700,13 @@
         <v>568</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M118">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15748,10 +15748,10 @@
         <v>0</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD118">
         <v>0</v>
@@ -15789,10 +15789,10 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D119" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E119" t="s">
         <v>252</v>
@@ -15816,13 +15816,13 @@
         <v>568</v>
       </c>
       <c r="L119">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N119">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -15905,7 +15905,7 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D120" t="s">
         <v>134</v>
@@ -16021,7 +16021,7 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
         <v>134</v>
@@ -16137,7 +16137,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D122" t="s">
         <v>134</v>
@@ -16253,7 +16253,7 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
@@ -16280,13 +16280,13 @@
         <v>568</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -16328,10 +16328,10 @@
         <v>0</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -16369,7 +16369,7 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D124" t="s">
         <v>134</v>
@@ -16485,7 +16485,7 @@
         <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D125" t="s">
         <v>134</v>
@@ -16512,13 +16512,13 @@
         <v>568</v>
       </c>
       <c r="L125">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M125">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N125">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16560,10 +16560,10 @@
         <v>0</v>
       </c>
       <c r="AB125">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD125">
         <v>0</v>
@@ -16601,10 +16601,10 @@
         <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D126" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E126" t="s">
         <v>259</v>
@@ -16628,13 +16628,13 @@
         <v>568</v>
       </c>
       <c r="L126">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="M126">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N126">
-        <v>4.01</v>
+        <v>6</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16676,10 +16676,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC126">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16717,7 +16717,7 @@
         <v>55</v>
       </c>
       <c r="C127" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D127" t="s">
         <v>134</v>
@@ -16833,7 +16833,7 @@
         <v>55</v>
       </c>
       <c r="C128" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D128" t="s">
         <v>134</v>
@@ -16949,7 +16949,7 @@
         <v>56</v>
       </c>
       <c r="C129" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="D129" t="s">
         <v>134</v>
@@ -16976,13 +16976,13 @@
         <v>568</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -17065,7 +17065,7 @@
         <v>56</v>
       </c>
       <c r="C130" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D130" t="s">
         <v>134</v>
@@ -17092,13 +17092,13 @@
         <v>568</v>
       </c>
       <c r="L130">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M130">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N130">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -17181,7 +17181,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -17208,13 +17208,13 @@
         <v>568</v>
       </c>
       <c r="L131">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="M131">
-        <v>3.33</v>
+        <v>2.94</v>
       </c>
       <c r="N131">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17256,10 +17256,10 @@
         <v>0</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD131">
         <v>0</v>
@@ -17297,10 +17297,10 @@
         <v>56</v>
       </c>
       <c r="C132" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D132" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E132" t="s">
         <v>265</v>
@@ -17324,13 +17324,13 @@
         <v>568</v>
       </c>
       <c r="L132">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="M132">
-        <v>2.94</v>
+        <v>3.33</v>
       </c>
       <c r="N132">
-        <v>2.87</v>
+        <v>1.82</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -17372,10 +17372,10 @@
         <v>0</v>
       </c>
       <c r="AB132">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AC132">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AD132">
         <v>0</v>
@@ -17413,10 +17413,10 @@
         <v>56</v>
       </c>
       <c r="C133" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D133" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E133" t="s">
         <v>266</v>
@@ -17440,13 +17440,13 @@
         <v>568</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -17672,13 +17672,13 @@
         <v>568</v>
       </c>
       <c r="L135">
-        <v>1.82</v>
+        <v>6</v>
       </c>
       <c r="M135">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="N135">
-        <v>3.53</v>
+        <v>1.43</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17761,10 +17761,10 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D136" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E136" t="s">
         <v>269</v>
@@ -17788,13 +17788,13 @@
         <v>568</v>
       </c>
       <c r="L136">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="M136">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N136">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17836,10 +17836,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC136">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17877,7 +17877,7 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D137" t="s">
         <v>134</v>
@@ -17904,13 +17904,13 @@
         <v>568</v>
       </c>
       <c r="L137">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M137">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N137">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -17993,10 +17993,10 @@
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D138" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E138" t="s">
         <v>271</v>
@@ -18020,14 +18020,14 @@
         <v>568</v>
       </c>
       <c r="L138">
+        <v>3.39</v>
+      </c>
+      <c r="M138">
+        <v>3.74</v>
+      </c>
+      <c r="N138">
         <v>1.8</v>
       </c>
-      <c r="M138">
-        <v>3.23</v>
-      </c>
-      <c r="N138">
-        <v>3.94</v>
-      </c>
       <c r="O138">
         <v>0</v>
       </c>
@@ -18068,10 +18068,10 @@
         <v>0</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD138">
         <v>0</v>
@@ -18109,7 +18109,7 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D139" t="s">
         <v>134</v>
@@ -18136,13 +18136,13 @@
         <v>568</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M139">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -18184,10 +18184,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -18225,7 +18225,7 @@
         <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D140" t="s">
         <v>133</v>
@@ -18252,13 +18252,13 @@
         <v>568</v>
       </c>
       <c r="L140">
-        <v>3.39</v>
+        <v>1.89</v>
       </c>
       <c r="M140">
-        <v>3.74</v>
+        <v>3.26</v>
       </c>
       <c r="N140">
-        <v>1.8</v>
+        <v>3.53</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -18300,10 +18300,10 @@
         <v>0</v>
       </c>
       <c r="AB140">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC140">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AD140">
         <v>0</v>
@@ -18341,7 +18341,7 @@
         <v>58</v>
       </c>
       <c r="C141" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D141" t="s">
         <v>134</v>
@@ -18368,13 +18368,13 @@
         <v>568</v>
       </c>
       <c r="L141">
-        <v>6</v>
+        <v>1.79</v>
       </c>
       <c r="M141">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="N141">
-        <v>1.43</v>
+        <v>3.47</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AC141">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18457,7 +18457,7 @@
         <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D142" t="s">
         <v>134</v>
@@ -18484,13 +18484,13 @@
         <v>568</v>
       </c>
       <c r="L142">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="M142">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N142">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="O142">
         <v>0</v>
@@ -18573,10 +18573,10 @@
         <v>58</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="D143" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
@@ -18600,13 +18600,13 @@
         <v>568</v>
       </c>
       <c r="L143">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="M143">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="N143">
-        <v>2.44</v>
+        <v>3.71</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -18654,10 +18654,10 @@
         <v>0</v>
       </c>
       <c r="AD143">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE143">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF143">
         <v>0</v>
@@ -18689,10 +18689,10 @@
         <v>58</v>
       </c>
       <c r="C144" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="D144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E144" t="s">
         <v>277</v>
@@ -18716,13 +18716,13 @@
         <v>568</v>
       </c>
       <c r="L144">
-        <v>1.79</v>
+        <v>2.41</v>
       </c>
       <c r="M144">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="N144">
-        <v>3.47</v>
+        <v>2.44</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -18764,16 +18764,16 @@
         <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC144">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF144">
         <v>0</v>
@@ -18805,7 +18805,7 @@
         <v>59</v>
       </c>
       <c r="C145" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D145" t="s">
         <v>134</v>
@@ -19037,10 +19037,10 @@
         <v>60</v>
       </c>
       <c r="C147" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E147" t="s">
         <v>280</v>
@@ -19064,13 +19064,13 @@
         <v>568</v>
       </c>
       <c r="L147">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M147">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O147">
         <v>0</v>
@@ -19112,16 +19112,16 @@
         <v>0</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF147">
         <v>0</v>
@@ -19153,10 +19153,10 @@
         <v>60</v>
       </c>
       <c r="C148" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D148" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E148" t="s">
         <v>281</v>
@@ -19269,7 +19269,7 @@
         <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D149" t="s">
         <v>134</v>
@@ -19296,13 +19296,13 @@
         <v>568</v>
       </c>
       <c r="L149">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M149">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N149">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -19344,16 +19344,16 @@
         <v>0</v>
       </c>
       <c r="AB149">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC149">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD149">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE149">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF149">
         <v>0</v>
@@ -19501,10 +19501,10 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D151" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E151" t="s">
         <v>284</v>
@@ -19528,13 +19528,13 @@
         <v>568</v>
       </c>
       <c r="L151">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="M151">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N151">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -19576,16 +19576,16 @@
         <v>0</v>
       </c>
       <c r="AB151">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC151">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD151">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE151">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151">
         <v>0</v>
@@ -19617,7 +19617,7 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D152" t="s">
         <v>134</v>
@@ -19644,13 +19644,13 @@
         <v>568</v>
       </c>
       <c r="L152">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="M152">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="N152">
-        <v>3.61</v>
+        <v>2.23</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19692,16 +19692,16 @@
         <v>0</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD152">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE152">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF152">
         <v>0</v>
@@ -19733,7 +19733,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D153" t="s">
         <v>134</v>
@@ -19760,13 +19760,13 @@
         <v>568</v>
       </c>
       <c r="L153">
-        <v>2.91</v>
+        <v>6.9</v>
       </c>
       <c r="M153">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="N153">
-        <v>2.23</v>
+        <v>1.34</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -19808,16 +19808,16 @@
         <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC153">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF153">
         <v>0</v>
@@ -19849,10 +19849,10 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D154" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E154" t="s">
         <v>287</v>
@@ -19876,13 +19876,13 @@
         <v>568</v>
       </c>
       <c r="L154">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M154">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -19924,16 +19924,16 @@
         <v>0</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF154">
         <v>0</v>
@@ -19965,7 +19965,7 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D155" t="s">
         <v>134</v>
@@ -19992,13 +19992,13 @@
         <v>568</v>
       </c>
       <c r="L155">
-        <v>4.8</v>
+        <v>1.97</v>
       </c>
       <c r="M155">
-        <v>4</v>
+        <v>3.51</v>
       </c>
       <c r="N155">
-        <v>1.63</v>
+        <v>3.61</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -20040,16 +20040,16 @@
         <v>0</v>
       </c>
       <c r="AB155">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC155">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD155">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AE155">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF155">
         <v>0</v>
@@ -20313,7 +20313,7 @@
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="D158" t="s">
         <v>134</v>
@@ -20337,7 +20337,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -20429,7 +20429,7 @@
         <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="D159" t="s">
         <v>134</v>
@@ -20545,7 +20545,7 @@
         <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D160" t="s">
         <v>134</v>
@@ -20569,7 +20569,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -20661,7 +20661,7 @@
         <v>63</v>
       </c>
       <c r="C161" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D161" t="s">
         <v>134</v>
@@ -21009,7 +21009,7 @@
         <v>64</v>
       </c>
       <c r="C164" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D164" t="s">
         <v>134</v>
@@ -21036,13 +21036,13 @@
         <v>568</v>
       </c>
       <c r="L164">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M164">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="N164">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -21125,7 +21125,7 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D165" t="s">
         <v>134</v>
@@ -21152,13 +21152,13 @@
         <v>568</v>
       </c>
       <c r="L165">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M165">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD165">
         <v>0</v>
@@ -21357,7 +21357,7 @@
         <v>64</v>
       </c>
       <c r="C167" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D167" t="s">
         <v>134</v>
@@ -21384,13 +21384,13 @@
         <v>568</v>
       </c>
       <c r="L167">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M167">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="N167">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -21432,10 +21432,10 @@
         <v>0</v>
       </c>
       <c r="AB167">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC167">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD167">
         <v>0</v>
@@ -21473,7 +21473,7 @@
         <v>65</v>
       </c>
       <c r="C168" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D168" t="s">
         <v>134</v>
@@ -21500,13 +21500,13 @@
         <v>568</v>
       </c>
       <c r="L168">
-        <v>1.33</v>
+        <v>3.71</v>
       </c>
       <c r="M168">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="N168">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -21548,16 +21548,16 @@
         <v>0</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD168">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF168">
         <v>0</v>
@@ -21705,7 +21705,7 @@
         <v>65</v>
       </c>
       <c r="C170" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D170" t="s">
         <v>134</v>
@@ -21732,13 +21732,13 @@
         <v>568</v>
       </c>
       <c r="L170">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="M170">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N170">
-        <v>2.83</v>
+        <v>6.8</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -21780,16 +21780,16 @@
         <v>0</v>
       </c>
       <c r="AB170">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC170">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF170">
         <v>0</v>
@@ -21821,7 +21821,7 @@
         <v>65</v>
       </c>
       <c r="C171" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D171" t="s">
         <v>134</v>
@@ -21848,13 +21848,13 @@
         <v>568</v>
       </c>
       <c r="L171">
-        <v>3.71</v>
+        <v>2.26</v>
       </c>
       <c r="M171">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N171">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -21896,10 +21896,10 @@
         <v>0</v>
       </c>
       <c r="AB171">
+        <v>1.57</v>
+      </c>
+      <c r="AC171">
         <v>2.15</v>
-      </c>
-      <c r="AC171">
-        <v>1.7</v>
       </c>
       <c r="AD171">
         <v>0</v>
@@ -21937,10 +21937,10 @@
         <v>66</v>
       </c>
       <c r="C172" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E172" t="s">
         <v>305</v>
@@ -21964,13 +21964,13 @@
         <v>568</v>
       </c>
       <c r="L172">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M172">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N172">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O172">
         <v>0</v>
@@ -22053,10 +22053,10 @@
         <v>66</v>
       </c>
       <c r="C173" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D173" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E173" t="s">
         <v>306</v>
@@ -22080,13 +22080,13 @@
         <v>568</v>
       </c>
       <c r="L173">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M173">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -22169,7 +22169,7 @@
         <v>67</v>
       </c>
       <c r="C174" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D174" t="s">
         <v>133</v>
@@ -22178,7 +22178,7 @@
         <v>307</v>
       </c>
       <c r="F174" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>67</v>
       </c>
       <c r="C175" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D175" t="s">
         <v>133</v>
@@ -22294,7 +22294,7 @@
         <v>308</v>
       </c>
       <c r="F175" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -22312,13 +22312,13 @@
         <v>568</v>
       </c>
       <c r="L175">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M175">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N175">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O175">
         <v>0</v>
@@ -22360,10 +22360,10 @@
         <v>0</v>
       </c>
       <c r="AB175">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC175">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD175">
         <v>0</v>
@@ -22401,7 +22401,7 @@
         <v>67</v>
       </c>
       <c r="C176" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D176" t="s">
         <v>133</v>
@@ -22428,13 +22428,13 @@
         <v>568</v>
       </c>
       <c r="L176">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M176">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O176">
         <v>0</v>
@@ -22476,10 +22476,10 @@
         <v>0</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD176">
         <v>0</v>
@@ -22517,10 +22517,10 @@
         <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D177" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E177" t="s">
         <v>310</v>
@@ -22544,13 +22544,13 @@
         <v>568</v>
       </c>
       <c r="L177">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M177">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O177">
         <v>0</v>
@@ -22586,10 +22586,10 @@
         <v>0</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB177">
         <v>0</v>
@@ -22633,10 +22633,10 @@
         <v>67</v>
       </c>
       <c r="C178" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D178" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E178" t="s">
         <v>311</v>
@@ -23240,13 +23240,13 @@
         <v>568</v>
       </c>
       <c r="L183">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M183">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O183">
         <v>0</v>
@@ -23282,10 +23282,10 @@
         <v>0</v>
       </c>
       <c r="Z183">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB183">
         <v>0</v>
@@ -23588,13 +23588,13 @@
         <v>568</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M186">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O186">
         <v>0</v>
@@ -23636,10 +23636,10 @@
         <v>0</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD186">
         <v>0</v>
@@ -23936,13 +23936,13 @@
         <v>568</v>
       </c>
       <c r="L189">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M189">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O189">
         <v>0</v>
@@ -23978,10 +23978,10 @@
         <v>0</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB189">
         <v>0</v>
@@ -24168,13 +24168,13 @@
         <v>568</v>
       </c>
       <c r="L191">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O191">
         <v>0</v>
@@ -24210,10 +24210,10 @@
         <v>0</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB191">
         <v>0</v>
@@ -24284,13 +24284,13 @@
         <v>568</v>
       </c>
       <c r="L192">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M192">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O192">
         <v>0</v>
@@ -24326,10 +24326,10 @@
         <v>0</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB192">
         <v>0</v>
@@ -24400,13 +24400,13 @@
         <v>568</v>
       </c>
       <c r="L193">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M193">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O193">
         <v>0</v>
@@ -24442,10 +24442,10 @@
         <v>0</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB193">
         <v>0</v>
@@ -24632,13 +24632,13 @@
         <v>568</v>
       </c>
       <c r="L195">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M195">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -24674,16 +24674,16 @@
         <v>0</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD195">
         <v>0</v>
@@ -26140,13 +26140,13 @@
         <v>568</v>
       </c>
       <c r="L208">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M208">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O208">
         <v>0</v>
@@ -26182,10 +26182,10 @@
         <v>0</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA208">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB208">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -310,21 +310,21 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>England EFL League Two</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Scotland Championship</t>
   </si>
   <si>
-    <t>England EFL League Two</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
@@ -337,42 +337,42 @@
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-  </si>
-  <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -397,24 +397,24 @@
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>USA NWSL</t>
   </si>
   <si>
@@ -613,60 +613,60 @@
     <t>Ufa</t>
   </si>
   <si>
+    <t>Plymouth Argyle</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Burton Albion</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
     <t>Airdrieonians</t>
   </si>
   <si>
-    <t>Milton Keynes Dons</t>
-  </si>
-  <si>
-    <t>Plymouth Argyle</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
+    <t>Åsane</t>
+  </si>
+  <si>
+    <t>Huddersfield Town</t>
+  </si>
+  <si>
+    <t>KVC Westerlo</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
   </si>
   <si>
     <t>Aalesund</t>
   </si>
   <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Stabæk</t>
   </si>
   <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Åsane</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>KVC Westerlo</t>
-  </si>
-  <si>
-    <t>Huddersfield Town</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
     <t>Ural</t>
   </si>
   <si>
@@ -739,108 +739,108 @@
     <t>MSV Duisburg</t>
   </si>
   <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>Zorya</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
     <t>Rostov</t>
   </si>
   <si>
-    <t>Zorya</t>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>Posusje</t>
   </si>
   <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Slavia</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Varaždin</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Slavia</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
+    <t>Widzew Łódź</t>
+  </si>
+  <si>
+    <t>Mura</t>
+  </si>
+  <si>
+    <t>Argeș</t>
   </si>
   <si>
     <t>Stal Rzeszów</t>
   </si>
   <si>
-    <t>Argeș</t>
-  </si>
-  <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Mura</t>
-  </si>
-  <si>
-    <t>Widzew Łódź</t>
-  </si>
-  <si>
     <t>Diósgyőr</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Servette</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Oulu</t>
+  </si>
+  <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Ružomberok</t>
+  </si>
+  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Ružomberok</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Zemplín Michalovce</t>
-  </si>
-  <si>
     <t>Bellinzona</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>Oulu</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
@@ -850,61 +850,64 @@
     <t>Al Faisaly</t>
   </si>
   <si>
+    <t>Chayka</t>
+  </si>
+  <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Magallanes</t>
   </si>
   <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
     <t>Olimpiyets</t>
   </si>
   <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
     <t>Ried</t>
   </si>
   <si>
-    <t>07 Vestur</t>
-  </si>
-  <si>
     <t>Krasnodar</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
+    <t>Austria Wien II</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
   </si>
   <si>
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
     <t>LFK Mladost Lučani</t>
   </si>
   <si>
-    <t>Austria Wien II</t>
+    <t>Ferencváros</t>
+  </si>
+  <si>
+    <t>Ludogorets</t>
+  </si>
+  <si>
+    <t>Lech Poznań</t>
   </si>
   <si>
     <t>Primorje</t>
   </si>
   <si>
-    <t>Lech Poznań</t>
-  </si>
-  <si>
-    <t>Ludogorets</t>
-  </si>
-  <si>
-    <t>Ferencváros</t>
+    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Basel</t>
@@ -913,31 +916,43 @@
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
     <t>Dinamo Bucureşti</t>
   </si>
   <si>
+    <t>KAA Gent</t>
+  </si>
+  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>KAA Gent</t>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Osijek</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
   </si>
   <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
-    <t>Sport Recife</t>
-  </si>
-  <si>
-    <t>Osijek</t>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
   </si>
   <si>
     <t>Almirante Brown</t>
@@ -946,85 +961,73 @@
     <t>Club Atlético Mitre</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Temperley</t>
   </si>
   <si>
     <t>Colón</t>
   </si>
   <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Talleres Remedios</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
+    <t>Chaco For Ever</t>
   </si>
   <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Mirassol</t>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>San Luis</t>
   </si>
   <si>
     <t>Concepción</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
+    <t>Santiago Morning</t>
   </si>
   <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Santiago Morning</t>
+    <t>Forge FC</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Forge FC</t>
+    <t>Amazonas</t>
   </si>
   <si>
     <t>Carolina Core</t>
@@ -1033,9 +1036,6 @@
     <t>North Carolina Courage</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
@@ -1048,12 +1048,12 @@
     <t>North Texas</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
-  </si>
-  <si>
     <t>Bay</t>
   </si>
   <si>
@@ -1249,60 +1249,60 @@
     <t>Shinnik</t>
   </si>
   <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Oldham Athletic</t>
+  </si>
+  <si>
+    <t>Lyn</t>
+  </si>
+  <si>
+    <t>Wycombe Wanderers</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
+  </si>
+  <si>
+    <t>Mansfield Town</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>Ross County</t>
   </si>
   <si>
-    <t>Oldham Athletic</t>
-  </si>
-  <si>
-    <t>Barnsley</t>
-  </si>
-  <si>
-    <t>Mansfield Town</t>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Leyton Orient</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Exeter City</t>
+  </si>
+  <si>
+    <t>Hødd</t>
   </si>
   <si>
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>Port Vale</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
     <t>Moss</t>
   </si>
   <si>
-    <t>Wycombe Wanderers</t>
-  </si>
-  <si>
-    <t>Northampton Town</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Lyn</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Leyton Orient</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Port Vale</t>
-  </si>
-  <si>
-    <t>Exeter City</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
     <t>Rodina Moskva</t>
   </si>
   <si>
@@ -1375,108 +1375,108 @@
     <t>Stuttgart II</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
+    <t>LNZ Cherkasy</t>
+  </si>
+  <si>
+    <t>Bohemians 1905</t>
+  </si>
+  <si>
     <t>Krylya Sovetov</t>
   </si>
   <si>
-    <t>LNZ Cherkasy</t>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
   </si>
   <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Gorica</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Isloch</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Bohemians 1905</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Gorica</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Isloch</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Aluminij</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
   </si>
   <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>Csikszereda</t>
-  </si>
-  <si>
     <t>GAIS</t>
   </si>
   <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
     <t>St. Gallen</t>
   </si>
   <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>Skalica</t>
+  </si>
+  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Skalica</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Komárno</t>
-  </si>
-  <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
     <t>CSKA Sofia</t>
   </si>
   <si>
-    <t>Jaro</t>
-  </si>
-  <si>
-    <t>Young Boys</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
@@ -1486,61 +1486,64 @@
     <t>Al Jazeera</t>
   </si>
   <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
     <t>Curicó Unido</t>
   </si>
   <si>
     <t>Arsenal Dzyarzhynsk</t>
   </si>
   <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
     <t>Lokomotiv Moskva</t>
   </si>
   <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Salzburg</t>
   </si>
   <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
     <t>Dinamo Moskva</t>
   </si>
   <si>
-    <t>Polonia Warszawa</t>
+    <t>St. Pölten</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Javor Ivanjica</t>
   </si>
   <si>
     <t>Spartak Subotica</t>
   </si>
   <si>
-    <t>Javor Ivanjica</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>St. Pölten</t>
+    <t>Kazincbarcika</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Bravo</t>
   </si>
   <si>
-    <t>Górnik Zabrze</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
-    <t>Kazincbarcika</t>
+    <t>Podbrezová</t>
   </si>
   <si>
     <t>Grasshopper</t>
@@ -1549,28 +1552,40 @@
     <t>Fortuna Düsseldorf</t>
   </si>
   <si>
-    <t>Podbrezová</t>
-  </si>
-  <si>
     <t>FCSB</t>
   </si>
   <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Avaí</t>
   </si>
   <si>
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
   </si>
   <si>
     <t>Central Norte</t>
@@ -1579,85 +1594,73 @@
     <t>Gimnasia Jujuy</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
   </si>
   <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
+    <t>Gimnasia Mendoza</t>
   </si>
   <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Vasco da Gama</t>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
+    <t>Univ. Concepción</t>
   </si>
   <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
-    <t>Unión San Felipe</t>
+    <t>Recoleta</t>
   </si>
   <si>
     <t>San Marcos</t>
   </si>
   <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
+    <t>Valour FC</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
   </si>
   <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Valour FC</t>
+    <t>Goiás</t>
   </si>
   <si>
     <t>New England II</t>
@@ -1666,9 +1669,6 @@
     <t>San Diego Wave</t>
   </si>
   <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
@@ -1681,10 +1681,10 @@
     <t>Colorado Rapids II</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>Sacramento Republic</t>
-  </si>
-  <si>
-    <t>Las Vegas Lights</t>
   </si>
   <si>
     <t>Houston Dash</t>
@@ -9495,7 +9495,7 @@
         <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D65" t="s">
         <v>135</v>
@@ -9522,13 +9522,13 @@
         <v>559</v>
       </c>
       <c r="L65">
-        <v>3.65</v>
+        <v>1.93</v>
       </c>
       <c r="M65">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="N65">
-        <v>1.87</v>
+        <v>3.06</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9570,10 +9570,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9611,7 +9611,7 @@
         <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
         <v>135</v>
@@ -9727,10 +9727,10 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -9754,13 +9754,13 @@
         <v>559</v>
       </c>
       <c r="L67">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="M67">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="N67">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC67">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9870,13 +9870,13 @@
         <v>559</v>
       </c>
       <c r="L68">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="M68">
-        <v>3.31</v>
+        <v>3.06</v>
       </c>
       <c r="N68">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9918,10 +9918,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC68">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9959,10 +9959,10 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E69" t="s">
         <v>203</v>
@@ -9986,13 +9986,13 @@
         <v>559</v>
       </c>
       <c r="L69">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="M69">
-        <v>3.9</v>
+        <v>3.01</v>
       </c>
       <c r="N69">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -10034,10 +10034,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC69">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -10075,10 +10075,10 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E70" t="s">
         <v>204</v>
@@ -10102,13 +10102,13 @@
         <v>559</v>
       </c>
       <c r="L70">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="M70">
-        <v>4.4</v>
+        <v>3.31</v>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -10150,16 +10150,16 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD70">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF70">
         <v>0</v>
@@ -10191,10 +10191,10 @@
         <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E71" t="s">
         <v>205</v>
@@ -10218,13 +10218,13 @@
         <v>559</v>
       </c>
       <c r="L71">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="M71">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="N71">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -10266,10 +10266,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC71">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -10307,7 +10307,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
         <v>135</v>
@@ -10334,13 +10334,13 @@
         <v>559</v>
       </c>
       <c r="L72">
-        <v>2.11</v>
+        <v>3.65</v>
       </c>
       <c r="M72">
-        <v>3.01</v>
+        <v>3.65</v>
       </c>
       <c r="N72">
-        <v>3.18</v>
+        <v>1.87</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -10382,10 +10382,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC72">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -10539,10 +10539,10 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E74" t="s">
         <v>208</v>
@@ -10566,13 +10566,13 @@
         <v>559</v>
       </c>
       <c r="L74">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="M74">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="N74">
-        <v>2.7</v>
+        <v>3.47</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10614,10 +10614,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AC74">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10655,7 +10655,7 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D75" t="s">
         <v>135</v>
@@ -10771,10 +10771,10 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E76" t="s">
         <v>210</v>
@@ -10798,13 +10798,13 @@
         <v>559</v>
       </c>
       <c r="L76">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="M76">
-        <v>3.77</v>
+        <v>5</v>
       </c>
       <c r="N76">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10846,16 +10846,16 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF76">
         <v>0</v>
@@ -10887,10 +10887,10 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E77" t="s">
         <v>211</v>
@@ -10914,13 +10914,13 @@
         <v>559</v>
       </c>
       <c r="L77">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="M77">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="N77">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10962,10 +10962,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -11003,10 +11003,10 @@
         <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E78" t="s">
         <v>212</v>
@@ -11030,13 +11030,13 @@
         <v>559</v>
       </c>
       <c r="L78">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="M78">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N78">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -11078,10 +11078,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AC78">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -11119,10 +11119,10 @@
         <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E79" t="s">
         <v>213</v>
@@ -11146,13 +11146,13 @@
         <v>559</v>
       </c>
       <c r="L79">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="M79">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="N79">
-        <v>3.72</v>
+        <v>2.9</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -11194,10 +11194,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AC79">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -11235,10 +11235,10 @@
         <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D80" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E80" t="s">
         <v>214</v>
@@ -11262,13 +11262,13 @@
         <v>559</v>
       </c>
       <c r="L80">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="M80">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="N80">
-        <v>6.2</v>
+        <v>2.82</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -11310,16 +11310,16 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD80">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF80">
         <v>0</v>
@@ -11351,7 +11351,7 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D81" t="s">
         <v>134</v>
@@ -11378,13 +11378,13 @@
         <v>559</v>
       </c>
       <c r="L81">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N81">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -11426,10 +11426,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC81">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11467,7 +11467,7 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D82" t="s">
         <v>134</v>
@@ -11494,13 +11494,13 @@
         <v>559</v>
       </c>
       <c r="L82">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="M82">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="N82">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11542,16 +11542,16 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF82">
         <v>0</v>
@@ -11699,7 +11699,7 @@
         <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
         <v>135</v>
@@ -11815,7 +11815,7 @@
         <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D85" t="s">
         <v>135</v>
@@ -12163,7 +12163,7 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D88" t="s">
         <v>135</v>
@@ -12395,7 +12395,7 @@
         <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D90" t="s">
         <v>135</v>
@@ -12511,7 +12511,7 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D91" t="s">
         <v>135</v>
@@ -12743,7 +12743,7 @@
         <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" t="s">
         <v>135</v>
@@ -12859,7 +12859,7 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D94" t="s">
         <v>135</v>
@@ -12975,7 +12975,7 @@
         <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D95" t="s">
         <v>135</v>
@@ -13091,7 +13091,7 @@
         <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s">
         <v>135</v>
@@ -13555,7 +13555,7 @@
         <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" t="s">
         <v>135</v>
@@ -13671,7 +13671,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D101" t="s">
         <v>135</v>
@@ -13787,7 +13787,7 @@
         <v>53</v>
       </c>
       <c r="C102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D102" t="s">
         <v>135</v>
@@ -13903,7 +13903,7 @@
         <v>53</v>
       </c>
       <c r="C103" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D103" t="s">
         <v>135</v>
@@ -14019,7 +14019,7 @@
         <v>53</v>
       </c>
       <c r="C104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D104" t="s">
         <v>135</v>
@@ -14394,13 +14394,13 @@
         <v>559</v>
       </c>
       <c r="L107">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N107">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -14442,10 +14442,10 @@
         <v>0</v>
       </c>
       <c r="AB107">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC107">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD107">
         <v>0</v>
@@ -14483,7 +14483,7 @@
         <v>55</v>
       </c>
       <c r="C108" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D108" t="s">
         <v>135</v>
@@ -14510,13 +14510,13 @@
         <v>559</v>
       </c>
       <c r="L108">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M108">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -14558,10 +14558,10 @@
         <v>0</v>
       </c>
       <c r="AB108">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD108">
         <v>0</v>
@@ -14626,13 +14626,13 @@
         <v>559</v>
       </c>
       <c r="L109">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -14674,10 +14674,10 @@
         <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD109">
         <v>0</v>
@@ -14715,10 +14715,10 @@
         <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D110" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E110" t="s">
         <v>244</v>
@@ -14742,13 +14742,13 @@
         <v>559</v>
       </c>
       <c r="L110">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M110">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14790,10 +14790,10 @@
         <v>0</v>
       </c>
       <c r="AB110">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD110">
         <v>0</v>
@@ -14831,7 +14831,7 @@
         <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D111" t="s">
         <v>135</v>
@@ -14858,13 +14858,13 @@
         <v>559</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14906,10 +14906,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -15063,7 +15063,7 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D113" t="s">
         <v>135</v>
@@ -15090,13 +15090,13 @@
         <v>559</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -15138,10 +15138,10 @@
         <v>0</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -15179,10 +15179,10 @@
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E114" t="s">
         <v>248</v>
@@ -15295,10 +15295,10 @@
         <v>55</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E115" t="s">
         <v>249</v>
@@ -15411,7 +15411,7 @@
         <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D116" t="s">
         <v>135</v>
@@ -15438,13 +15438,13 @@
         <v>559</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -15486,10 +15486,10 @@
         <v>0</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD116">
         <v>0</v>
@@ -15527,7 +15527,7 @@
         <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D117" t="s">
         <v>135</v>
@@ -15643,7 +15643,7 @@
         <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D118" t="s">
         <v>135</v>
@@ -15759,7 +15759,7 @@
         <v>55</v>
       </c>
       <c r="C119" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D119" t="s">
         <v>135</v>
@@ -15875,10 +15875,10 @@
         <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D120" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E120" t="s">
         <v>254</v>
@@ -15902,13 +15902,13 @@
         <v>559</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15950,10 +15950,10 @@
         <v>0</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -15991,7 +15991,7 @@
         <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D121" t="s">
         <v>135</v>
@@ -16107,7 +16107,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D122" t="s">
         <v>135</v>
@@ -16223,10 +16223,10 @@
         <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D123" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E123" t="s">
         <v>257</v>
@@ -16250,13 +16250,13 @@
         <v>559</v>
       </c>
       <c r="L123">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M123">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N123">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -16339,10 +16339,10 @@
         <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D124" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E124" t="s">
         <v>258</v>
@@ -16366,13 +16366,13 @@
         <v>559</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -16414,10 +16414,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16455,7 +16455,7 @@
         <v>56</v>
       </c>
       <c r="C125" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D125" t="s">
         <v>135</v>
@@ -16482,13 +16482,13 @@
         <v>559</v>
       </c>
       <c r="L125">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="M125">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="N125">
-        <v>3.19</v>
+        <v>3.8</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16598,13 +16598,13 @@
         <v>559</v>
       </c>
       <c r="L126">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N126">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16646,10 +16646,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16687,10 +16687,10 @@
         <v>56</v>
       </c>
       <c r="C127" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E127" t="s">
         <v>261</v>
@@ -16714,13 +16714,13 @@
         <v>559</v>
       </c>
       <c r="L127">
-        <v>3.7</v>
+        <v>2.32</v>
       </c>
       <c r="M127">
-        <v>3.33</v>
+        <v>2.94</v>
       </c>
       <c r="N127">
-        <v>1.82</v>
+        <v>2.87</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16762,10 +16762,10 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AC127">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AD127">
         <v>0</v>
@@ -16803,7 +16803,7 @@
         <v>56</v>
       </c>
       <c r="C128" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D128" t="s">
         <v>135</v>
@@ -16830,13 +16830,13 @@
         <v>559</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16919,10 +16919,10 @@
         <v>56</v>
       </c>
       <c r="C129" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D129" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E129" t="s">
         <v>263</v>
@@ -16946,13 +16946,13 @@
         <v>559</v>
       </c>
       <c r="L129">
-        <v>1.79</v>
+        <v>3.7</v>
       </c>
       <c r="M129">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N129">
-        <v>3.8</v>
+        <v>1.82</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>58</v>
       </c>
       <c r="C131" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D131" t="s">
         <v>135</v>
@@ -17178,13 +17178,13 @@
         <v>559</v>
       </c>
       <c r="L131">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M131">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N131">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -17226,16 +17226,16 @@
         <v>0</v>
       </c>
       <c r="AB131">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC131">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD131">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE131">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF131">
         <v>0</v>
@@ -17267,10 +17267,10 @@
         <v>58</v>
       </c>
       <c r="C132" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D132" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E132" t="s">
         <v>266</v>
@@ -17294,13 +17294,13 @@
         <v>559</v>
       </c>
       <c r="L132">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="M132">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="N132">
-        <v>2.44</v>
+        <v>3.53</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -17342,16 +17342,16 @@
         <v>0</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD132">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AE132">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AF132">
         <v>0</v>
@@ -17383,7 +17383,7 @@
         <v>58</v>
       </c>
       <c r="C133" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D133" t="s">
         <v>135</v>
@@ -17410,13 +17410,13 @@
         <v>559</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -17458,16 +17458,16 @@
         <v>0</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF133">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>117</v>
       </c>
       <c r="D134" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E134" t="s">
         <v>268</v>
@@ -17526,14 +17526,14 @@
         <v>559</v>
       </c>
       <c r="L134">
+        <v>3.39</v>
+      </c>
+      <c r="M134">
+        <v>3.74</v>
+      </c>
+      <c r="N134">
         <v>1.8</v>
       </c>
-      <c r="M134">
-        <v>3.23</v>
-      </c>
-      <c r="N134">
-        <v>3.94</v>
-      </c>
       <c r="O134">
         <v>0</v>
       </c>
@@ -17574,10 +17574,10 @@
         <v>0</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD134">
         <v>0</v>
@@ -17615,7 +17615,7 @@
         <v>58</v>
       </c>
       <c r="C135" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D135" t="s">
         <v>134</v>
@@ -17642,13 +17642,13 @@
         <v>559</v>
       </c>
       <c r="L135">
-        <v>3.39</v>
+        <v>1.89</v>
       </c>
       <c r="M135">
-        <v>3.74</v>
+        <v>3.26</v>
       </c>
       <c r="N135">
-        <v>1.8</v>
+        <v>3.53</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17690,10 +17690,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC135">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17731,7 +17731,7 @@
         <v>58</v>
       </c>
       <c r="C136" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D136" t="s">
         <v>135</v>
@@ -17847,7 +17847,7 @@
         <v>58</v>
       </c>
       <c r="C137" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D137" t="s">
         <v>135</v>
@@ -17874,13 +17874,13 @@
         <v>559</v>
       </c>
       <c r="L137">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M137">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N137">
-        <v>3.71</v>
+        <v>3.94</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -17963,10 +17963,10 @@
         <v>58</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E138" t="s">
         <v>272</v>
@@ -17990,13 +17990,13 @@
         <v>559</v>
       </c>
       <c r="L138">
-        <v>4.2</v>
+        <v>2.41</v>
       </c>
       <c r="M138">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N138">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="O138">
         <v>0</v>
@@ -18044,10 +18044,10 @@
         <v>0</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF138">
         <v>0</v>
@@ -18079,10 +18079,10 @@
         <v>58</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D139" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E139" t="s">
         <v>273</v>
@@ -18106,13 +18106,13 @@
         <v>559</v>
       </c>
       <c r="L139">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="M139">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="N139">
-        <v>3.53</v>
+        <v>3.71</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -18154,10 +18154,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC139">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -18195,7 +18195,7 @@
         <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D140" t="s">
         <v>135</v>
@@ -18222,13 +18222,13 @@
         <v>559</v>
       </c>
       <c r="L140">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="M140">
-        <v>3.97</v>
+        <v>3.3</v>
       </c>
       <c r="N140">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -18270,16 +18270,16 @@
         <v>0</v>
       </c>
       <c r="AB140">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC140">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD140">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE140">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF140">
         <v>0</v>
@@ -18311,7 +18311,7 @@
         <v>59</v>
       </c>
       <c r="C141" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D141" t="s">
         <v>135</v>
@@ -18659,7 +18659,7 @@
         <v>60</v>
       </c>
       <c r="C144" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D144" t="s">
         <v>135</v>
@@ -18686,13 +18686,13 @@
         <v>559</v>
       </c>
       <c r="L144">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M144">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N144">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -18734,16 +18734,16 @@
         <v>0</v>
       </c>
       <c r="AB144">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC144">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD144">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE144">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF144">
         <v>0</v>
@@ -18775,7 +18775,7 @@
         <v>60</v>
       </c>
       <c r="C145" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D145" t="s">
         <v>135</v>
@@ -18802,13 +18802,13 @@
         <v>559</v>
       </c>
       <c r="L145">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M145">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O145">
         <v>0</v>
@@ -18850,16 +18850,16 @@
         <v>0</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF145">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>62</v>
       </c>
       <c r="C148" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D148" t="s">
         <v>135</v>
@@ -19150,13 +19150,13 @@
         <v>559</v>
       </c>
       <c r="L148">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="M148">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="N148">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -19198,16 +19198,16 @@
         <v>0</v>
       </c>
       <c r="AB148">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC148">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD148">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE148">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF148">
         <v>0</v>
@@ -19239,7 +19239,7 @@
         <v>62</v>
       </c>
       <c r="C149" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D149" t="s">
         <v>135</v>
@@ -19266,13 +19266,13 @@
         <v>559</v>
       </c>
       <c r="L149">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="M149">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N149">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -19314,16 +19314,16 @@
         <v>0</v>
       </c>
       <c r="AB149">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC149">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD149">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AE149">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF149">
         <v>0</v>
@@ -19471,7 +19471,7 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D151" t="s">
         <v>135</v>
@@ -19498,13 +19498,13 @@
         <v>559</v>
       </c>
       <c r="L151">
-        <v>1.97</v>
+        <v>6.9</v>
       </c>
       <c r="M151">
-        <v>3.51</v>
+        <v>4.4</v>
       </c>
       <c r="N151">
-        <v>3.61</v>
+        <v>1.34</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -19546,16 +19546,16 @@
         <v>0</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD151">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AE151">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF151">
         <v>0</v>
@@ -19587,7 +19587,7 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D152" t="s">
         <v>135</v>
@@ -19614,13 +19614,13 @@
         <v>559</v>
       </c>
       <c r="L152">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="M152">
-        <v>3.05</v>
+        <v>3.51</v>
       </c>
       <c r="N152">
-        <v>2.23</v>
+        <v>3.61</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -19662,16 +19662,16 @@
         <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC152">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF152">
         <v>0</v>
@@ -19703,7 +19703,7 @@
         <v>63</v>
       </c>
       <c r="C153" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="D153" t="s">
         <v>135</v>
@@ -19819,7 +19819,7 @@
         <v>63</v>
       </c>
       <c r="C154" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D154" t="s">
         <v>135</v>
@@ -20051,7 +20051,7 @@
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D156" t="s">
         <v>135</v>
@@ -20283,7 +20283,7 @@
         <v>63</v>
       </c>
       <c r="C158" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D158" t="s">
         <v>135</v>
@@ -20399,7 +20399,7 @@
         <v>64</v>
       </c>
       <c r="C159" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D159" t="s">
         <v>135</v>
@@ -20515,7 +20515,7 @@
         <v>64</v>
       </c>
       <c r="C160" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D160" t="s">
         <v>135</v>
@@ -20542,13 +20542,13 @@
         <v>559</v>
       </c>
       <c r="L160">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M160">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="N160">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="O160">
         <v>0</v>
@@ -20590,10 +20590,10 @@
         <v>0</v>
       </c>
       <c r="AB160">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC160">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD160">
         <v>0</v>
@@ -20631,7 +20631,7 @@
         <v>64</v>
       </c>
       <c r="C161" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D161" t="s">
         <v>135</v>
@@ -20658,13 +20658,13 @@
         <v>559</v>
       </c>
       <c r="L161">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="M161">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="N161">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="O161">
         <v>0</v>
@@ -20706,10 +20706,10 @@
         <v>0</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD161">
         <v>0</v>
@@ -20747,7 +20747,7 @@
         <v>64</v>
       </c>
       <c r="C162" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D162" t="s">
         <v>135</v>
@@ -20863,7 +20863,7 @@
         <v>65</v>
       </c>
       <c r="C163" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D163" t="s">
         <v>135</v>
@@ -20890,10 +20890,10 @@
         <v>559</v>
       </c>
       <c r="L163">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M163">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="N163">
         <v>6.8</v>
@@ -20944,10 +20944,10 @@
         <v>0</v>
       </c>
       <c r="AD163">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AE163">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AF163">
         <v>0</v>
@@ -20979,7 +20979,7 @@
         <v>65</v>
       </c>
       <c r="C164" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D164" t="s">
         <v>135</v>
@@ -21006,13 +21006,13 @@
         <v>559</v>
       </c>
       <c r="L164">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="M164">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N164">
-        <v>2.83</v>
+        <v>6.8</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -21054,16 +21054,16 @@
         <v>0</v>
       </c>
       <c r="AB164">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC164">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF164">
         <v>0</v>
@@ -21095,7 +21095,7 @@
         <v>65</v>
       </c>
       <c r="C165" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D165" t="s">
         <v>135</v>
@@ -21122,13 +21122,13 @@
         <v>559</v>
       </c>
       <c r="L165">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="M165">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="N165">
-        <v>6.8</v>
+        <v>2.83</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -21170,16 +21170,16 @@
         <v>0</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD165">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE165">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF165">
         <v>0</v>
@@ -21211,7 +21211,7 @@
         <v>65</v>
       </c>
       <c r="C166" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D166" t="s">
         <v>135</v>
@@ -21327,10 +21327,10 @@
         <v>66</v>
       </c>
       <c r="C167" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D167" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E167" t="s">
         <v>301</v>
@@ -21354,13 +21354,13 @@
         <v>559</v>
       </c>
       <c r="L167">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M167">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N167">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -21402,10 +21402,10 @@
         <v>0</v>
       </c>
       <c r="AB167">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC167">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD167">
         <v>0</v>
@@ -21443,10 +21443,10 @@
         <v>66</v>
       </c>
       <c r="C168" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D168" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E168" t="s">
         <v>302</v>
@@ -21470,13 +21470,13 @@
         <v>559</v>
       </c>
       <c r="L168">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M168">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -21518,10 +21518,10 @@
         <v>0</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD168">
         <v>0</v>
@@ -21559,7 +21559,7 @@
         <v>67</v>
       </c>
       <c r="C169" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D169" t="s">
         <v>134</v>
@@ -21568,7 +21568,7 @@
         <v>303</v>
       </c>
       <c r="F169" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -21586,13 +21586,13 @@
         <v>559</v>
       </c>
       <c r="L169">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M169">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O169">
         <v>0</v>
@@ -21675,16 +21675,16 @@
         <v>67</v>
       </c>
       <c r="C170" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D170" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E170" t="s">
         <v>304</v>
       </c>
       <c r="F170" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="G170">
         <v>0</v>
@@ -21702,13 +21702,13 @@
         <v>559</v>
       </c>
       <c r="L170">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M170">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N170">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -21818,13 +21818,13 @@
         <v>559</v>
       </c>
       <c r="L171">
-        <v>1.91</v>
+        <v>2.76</v>
       </c>
       <c r="M171">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="N171">
-        <v>3.78</v>
+        <v>2.39</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -21860,16 +21860,16 @@
         <v>0</v>
       </c>
       <c r="Z171">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA171">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD171">
         <v>0</v>
@@ -21934,13 +21934,13 @@
         <v>559</v>
       </c>
       <c r="L172">
-        <v>2.76</v>
+        <v>1.91</v>
       </c>
       <c r="M172">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="N172">
-        <v>2.39</v>
+        <v>3.78</v>
       </c>
       <c r="O172">
         <v>0</v>
@@ -21976,16 +21976,16 @@
         <v>0</v>
       </c>
       <c r="Z172">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB172">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC172">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD172">
         <v>0</v>
@@ -22023,10 +22023,10 @@
         <v>67</v>
       </c>
       <c r="C173" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D173" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E173" t="s">
         <v>307</v>
@@ -22166,13 +22166,13 @@
         <v>559</v>
       </c>
       <c r="L174">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M174">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O174">
         <v>0</v>
@@ -22208,10 +22208,10 @@
         <v>0</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB174">
         <v>0</v>
@@ -22398,13 +22398,13 @@
         <v>559</v>
       </c>
       <c r="L176">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O176">
         <v>0</v>
@@ -22440,10 +22440,10 @@
         <v>0</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB176">
         <v>0</v>
@@ -22514,13 +22514,13 @@
         <v>559</v>
       </c>
       <c r="L177">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M177">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N177">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O177">
         <v>0</v>
@@ -22562,10 +22562,10 @@
         <v>0</v>
       </c>
       <c r="AB177">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC177">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD177">
         <v>0</v>
@@ -22746,13 +22746,13 @@
         <v>559</v>
       </c>
       <c r="L179">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M179">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N179">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O179">
         <v>0</v>
@@ -22788,10 +22788,10 @@
         <v>0</v>
       </c>
       <c r="Z179">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA179">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB179">
         <v>0</v>
@@ -23094,13 +23094,13 @@
         <v>559</v>
       </c>
       <c r="L182">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M182">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O182">
         <v>0</v>
@@ -23136,10 +23136,10 @@
         <v>0</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB182">
         <v>0</v>
@@ -23210,13 +23210,13 @@
         <v>559</v>
       </c>
       <c r="L183">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M183">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N183">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O183">
         <v>0</v>
@@ -23252,10 +23252,10 @@
         <v>0</v>
       </c>
       <c r="Z183">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA183">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB183">
         <v>0</v>
@@ -23326,13 +23326,13 @@
         <v>559</v>
       </c>
       <c r="L184">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M184">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N184">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O184">
         <v>0</v>
@@ -23368,10 +23368,10 @@
         <v>0</v>
       </c>
       <c r="Z184">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA184">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB184">
         <v>0</v>
@@ -23442,13 +23442,13 @@
         <v>559</v>
       </c>
       <c r="L185">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M185">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O185">
         <v>0</v>
@@ -23484,10 +23484,10 @@
         <v>0</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB185">
         <v>0</v>
@@ -23558,13 +23558,13 @@
         <v>559</v>
       </c>
       <c r="L186">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="M186">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N186">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O186">
         <v>0</v>
@@ -23600,16 +23600,16 @@
         <v>0</v>
       </c>
       <c r="Z186">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA186">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD186">
         <v>0</v>
@@ -23674,13 +23674,13 @@
         <v>559</v>
       </c>
       <c r="L187">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M187">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O187">
         <v>0</v>
@@ -23716,10 +23716,10 @@
         <v>0</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB187">
         <v>0</v>
@@ -23790,13 +23790,13 @@
         <v>559</v>
       </c>
       <c r="L188">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M188">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N188">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O188">
         <v>0</v>
@@ -23832,10 +23832,10 @@
         <v>0</v>
       </c>
       <c r="Z188">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA188">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB188">
         <v>0</v>
@@ -23995,7 +23995,7 @@
         <v>70</v>
       </c>
       <c r="C190" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D190" t="s">
         <v>134</v>
@@ -24022,13 +24022,13 @@
         <v>559</v>
       </c>
       <c r="L190">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M190">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O190">
         <v>0</v>
@@ -24070,10 +24070,10 @@
         <v>0</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD190">
         <v>0</v>
@@ -24111,7 +24111,7 @@
         <v>70</v>
       </c>
       <c r="C191" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D191" t="s">
         <v>134</v>
@@ -24138,13 +24138,13 @@
         <v>559</v>
       </c>
       <c r="L191">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M191">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N191">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O191">
         <v>0</v>
@@ -24180,16 +24180,16 @@
         <v>0</v>
       </c>
       <c r="Z191">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA191">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB191">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC191">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD191">
         <v>0</v>
@@ -24254,13 +24254,13 @@
         <v>559</v>
       </c>
       <c r="L192">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="M192">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="N192">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="O192">
         <v>0</v>
@@ -24296,16 +24296,16 @@
         <v>0</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB192">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC192">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AD192">
         <v>0</v>
@@ -24486,13 +24486,13 @@
         <v>559</v>
       </c>
       <c r="L194">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M194">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N194">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -24602,13 +24602,13 @@
         <v>559</v>
       </c>
       <c r="L195">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M195">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -25155,7 +25155,7 @@
         <v>72</v>
       </c>
       <c r="C200" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D200" t="s">
         <v>134</v>
@@ -25271,7 +25271,7 @@
         <v>72</v>
       </c>
       <c r="C201" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D201" t="s">
         <v>134</v>
@@ -25387,7 +25387,7 @@
         <v>72</v>
       </c>
       <c r="C202" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D202" t="s">
         <v>134</v>
@@ -25503,7 +25503,7 @@
         <v>73</v>
       </c>
       <c r="C203" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D203" t="s">
         <v>134</v>
@@ -25530,13 +25530,13 @@
         <v>559</v>
       </c>
       <c r="L203">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M203">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -25572,10 +25572,10 @@
         <v>0</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB203">
         <v>0</v>
@@ -25619,7 +25619,7 @@
         <v>73</v>
       </c>
       <c r="C204" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D204" t="s">
         <v>134</v>
@@ -25646,13 +25646,13 @@
         <v>559</v>
       </c>
       <c r="L204">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M204">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N204">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O204">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AB204">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC204">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD204">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>73</v>
       </c>
       <c r="C205" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D205" t="s">
         <v>134</v>
@@ -25762,13 +25762,13 @@
         <v>559</v>
       </c>
       <c r="L205">
-        <v>3.11</v>
+        <v>2.6</v>
       </c>
       <c r="M205">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="N205">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="O205">
         <v>0</v>
@@ -25804,16 +25804,16 @@
         <v>0</v>
       </c>
       <c r="Z205">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA205">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD205">
         <v>0</v>
@@ -25967,7 +25967,7 @@
         <v>74</v>
       </c>
       <c r="C207" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D207" t="s">
         <v>134</v>
@@ -26083,7 +26083,7 @@
         <v>74</v>
       </c>
       <c r="C208" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D208" t="s">
         <v>134</v>
@@ -26315,7 +26315,7 @@
         <v>76</v>
       </c>
       <c r="C210" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D210" t="s">
         <v>134</v>
@@ -26342,13 +26342,13 @@
         <v>559</v>
       </c>
       <c r="L210">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="M210">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N210">
-        <v>2.29</v>
+        <v>4.6</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -26390,10 +26390,10 @@
         <v>0</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD210">
         <v>0</v>
@@ -26431,7 +26431,7 @@
         <v>76</v>
       </c>
       <c r="C211" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D211" t="s">
         <v>134</v>
@@ -26458,13 +26458,13 @@
         <v>559</v>
       </c>
       <c r="L211">
-        <v>1.61</v>
+        <v>2.95</v>
       </c>
       <c r="M211">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N211">
-        <v>4.6</v>
+        <v>2.29</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -26506,10 +26506,10 @@
         <v>0</v>
       </c>
       <c r="AB211">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC211">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD211">
         <v>0</v>
@@ -26663,7 +26663,7 @@
         <v>78</v>
       </c>
       <c r="C213" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D213" t="s">
         <v>134</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.01</v>
+        <v>3.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="M14" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.41</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>3.51</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>4.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.51</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="N18" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.38</v>
+        <v>3.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="N19" t="n">
-        <v>2.54</v>
+        <v>1.88</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="N20" t="n">
-        <v>1.5</v>
+        <v>2.77</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,14 +3182,14 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.03</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.49</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,14 +3314,14 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.9</v>
+        <v>1.62</v>
       </c>
       <c r="M22" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N22" t="n">
         <v>4.6</v>
       </c>
-      <c r="N22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.64</v>
+        <v>3.23</v>
       </c>
       <c r="M23" t="n">
-        <v>3.67</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>1.94</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.02</v>
+        <v>3.41</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="M35" t="n">
-        <v>3.47</v>
+        <v>3.84</v>
       </c>
       <c r="N35" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>3.09</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,16 +6530,16 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>8.699999999999999</v>
+        <v>2.69</v>
       </c>
       <c r="M55" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>1.36</v>
+        <v>2.41</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N56" t="n">
-        <v>2.41</v>
+        <v>1.36</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="N58" t="n">
-        <v>2.32</v>
+        <v>3.07</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="M59" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,16 +8510,16 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="M63" t="n">
-        <v>3.69</v>
+        <v>3.95</v>
       </c>
       <c r="N63" t="n">
-        <v>3.07</v>
+        <v>3.47</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,16 +8774,16 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,14 +9122,14 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N66" t="n">
         <v>3.06</v>
       </c>
-      <c r="N66" t="n">
-        <v>2.68</v>
-      </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
@@ -9170,16 +9170,16 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD66" t="n">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.77</v>
+        <v>3.41</v>
       </c>
       <c r="N67" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="M68" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="N68" t="n">
-        <v>3.18</v>
+        <v>2.68</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,16 +9434,16 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.65</v>
+        <v>1.83</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N71" t="n">
-        <v>3.9</v>
+        <v>2.02</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,16 +9830,16 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.08</v>
+        <v>1.39</v>
       </c>
       <c r="M72" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,16 +9962,16 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="M74" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="N74" t="n">
-        <v>6.2</v>
+        <v>3.59</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,16 +10226,16 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="M75" t="n">
-        <v>3.41</v>
+        <v>3.85</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="M76" t="n">
-        <v>4.4</v>
+        <v>3.47</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,16 +10490,16 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="M77" t="n">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="N77" t="n">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,16 +10622,16 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="M79" t="n">
-        <v>3.23</v>
+        <v>4.4</v>
       </c>
       <c r="N79" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,16 +10886,16 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="M80" t="n">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="N80" t="n">
-        <v>4.08</v>
+        <v>2.9</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.77</v>
+        <v>5.6</v>
       </c>
       <c r="M81" t="n">
-        <v>3.47</v>
+        <v>4.6</v>
       </c>
       <c r="N81" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -11150,10 +11150,10 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M82" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>3.19</v>
+        <v>3.79</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AC82" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="M83" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="N83" t="n">
-        <v>2.82</v>
+        <v>4.08</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.81</v>
+        <v>1.34</v>
       </c>
       <c r="M84" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="N84" t="n">
-        <v>3.72</v>
+        <v>8</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,16 +11546,16 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="M86" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="N86" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="M87" t="n">
-        <v>3.61</v>
+        <v>3.23</v>
       </c>
       <c r="N87" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M89" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N89" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M90" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N90" t="n">
-        <v>3.47</v>
+        <v>2.92</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="M91" t="n">
-        <v>3.59</v>
+        <v>3.36</v>
       </c>
       <c r="N91" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="M92" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N92" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC92" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="M94" t="n">
-        <v>3.03</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>3.34</v>
+        <v>3.01</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="M96" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="N96" t="n">
-        <v>2.68</v>
+        <v>3.18</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>5.6</v>
+        <v>1.76</v>
       </c>
       <c r="M97" t="n">
-        <v>4.6</v>
+        <v>3.77</v>
       </c>
       <c r="N97" t="n">
-        <v>1.46</v>
+        <v>3.47</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>4.6</v>
+        <v>1.81</v>
       </c>
       <c r="M98" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="N98" t="n">
-        <v>1.57</v>
+        <v>3.72</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,16 +13394,16 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF98" t="n">
         <v>0</v>
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="M100" t="n">
-        <v>4.7</v>
+        <v>3.61</v>
       </c>
       <c r="N100" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="M101" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N101" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="N102" t="n">
-        <v>3.59</v>
+        <v>3.34</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.74</v>
+        <v>3.65</v>
       </c>
       <c r="M103" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="N103" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,22 +14630,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14714,10 +14714,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -14762,22 +14762,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14978,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD110" t="n">
         <v>0</v>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.7</v>
+        <v>1.98</v>
       </c>
       <c r="M124" t="n">
         <v>3.33</v>
       </c>
       <c r="N124" t="n">
-        <v>1.82</v>
+        <v>3.19</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="M125" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="N125" t="n">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,58 +17042,58 @@
         </is>
       </c>
       <c r="L126" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
         <v>2.38</v>
       </c>
-      <c r="M126" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N126" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC126" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.98</v>
+        <v>3.7</v>
       </c>
       <c r="M127" t="n">
         <v>3.33</v>
       </c>
       <c r="N127" t="n">
-        <v>3.19</v>
+        <v>1.82</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.79</v>
+        <v>2.38</v>
       </c>
       <c r="M128" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N128" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17354,10 +17354,10 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -17534,22 +17534,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,16 +17618,16 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF130" t="n">
         <v>0</v>
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.39</v>
+        <v>1.75</v>
       </c>
       <c r="M131" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="N131" t="n">
-        <v>1.8</v>
+        <v>3.71</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="M132" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N132" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,16 +17882,16 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF132" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="M133" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N133" t="n">
-        <v>3.47</v>
+        <v>1.8</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.82</v>
+        <v>6</v>
       </c>
       <c r="M134" t="n">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="N134" t="n">
-        <v>3.53</v>
+        <v>1.43</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M135" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N135" t="n">
-        <v>3.71</v>
+        <v>3.94</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18326,22 +18326,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="M136" t="n">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="N136" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,22 +18458,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>6</v>
+        <v>3.39</v>
       </c>
       <c r="M137" t="n">
-        <v>3.97</v>
+        <v>3.74</v>
       </c>
       <c r="N137" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,16 +18542,16 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC137" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD137" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.41</v>
+        <v>1.89</v>
       </c>
       <c r="M139" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="N139" t="n">
-        <v>2.44</v>
+        <v>3.53</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,16 +18806,16 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC139" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AD139" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>5.9</v>
+        <v>2.32</v>
       </c>
       <c r="M142" t="n">
-        <v>4.9</v>
+        <v>3.22</v>
       </c>
       <c r="N142" t="n">
-        <v>1.34</v>
+        <v>3.14</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,16 +19202,16 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.32</v>
+        <v>5.9</v>
       </c>
       <c r="M143" t="n">
-        <v>3.22</v>
+        <v>4.9</v>
       </c>
       <c r="N143" t="n">
-        <v>3.14</v>
+        <v>1.34</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,16 +19334,16 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF143" t="n">
         <v>0</v>
@@ -19382,22 +19382,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19514,22 +19514,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19778,22 +19778,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19868,10 +19868,10 @@
         <v>0</v>
       </c>
       <c r="AD147" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF147" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="M148" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N148" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19994,16 +19994,16 @@
         <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC148" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD148" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF148" t="n">
         <v>0</v>
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>4.8</v>
+        <v>1.97</v>
       </c>
       <c r="M149" t="n">
-        <v>4</v>
+        <v>3.51</v>
       </c>
       <c r="N149" t="n">
-        <v>1.63</v>
+        <v>3.61</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,16 +20126,16 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF149" t="n">
         <v>0</v>
@@ -20306,22 +20306,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20390,16 +20390,16 @@
         <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC151" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD151" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF151" t="n">
         <v>0</v>
@@ -20438,22 +20438,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20474,13 +20474,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.42</v>
+        <v>3.64</v>
       </c>
       <c r="M153" t="n">
-        <v>3.81</v>
+        <v>3.59</v>
       </c>
       <c r="N153" t="n">
-        <v>6.6</v>
+        <v>1.77</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC153" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20702,22 +20702,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -21050,10 +21050,10 @@
         <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD156" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.64</v>
+        <v>1.42</v>
       </c>
       <c r="M157" t="n">
-        <v>3.59</v>
+        <v>3.81</v>
       </c>
       <c r="N157" t="n">
-        <v>1.77</v>
+        <v>6.6</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
         <v>0</v>
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="M158" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="N158" t="n">
-        <v>4.73</v>
+        <v>5.4</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="M160" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="N160" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.61</v>
+        <v>2.54</v>
       </c>
       <c r="M162" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="N162" t="n">
-        <v>4.8</v>
+        <v>2.48</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="M163" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="N163" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21980,10 +21980,10 @@
         <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF163" t="n">
         <v>0</v>
@@ -22022,22 +22022,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22106,10 +22106,10 @@
         <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
         <v>0</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="M165" t="n">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="N165" t="n">
-        <v>6.8</v>
+        <v>2.83</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -22238,16 +22238,16 @@
         <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD165" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF165" t="n">
         <v>0</v>
@@ -22286,22 +22286,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22814,22 +22814,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22850,13 +22850,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>3.55</v>
+        <v>1.6</v>
       </c>
       <c r="M170" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N170" t="n">
-        <v>1.96</v>
+        <v>4.7</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22898,16 +22898,16 @@
         <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD170" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE170" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF170" t="n">
         <v>0</v>
@@ -22946,22 +22946,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22982,13 +22982,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.6</v>
+        <v>3.55</v>
       </c>
       <c r="M171" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N171" t="n">
-        <v>4.7</v>
+        <v>1.96</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -23030,16 +23030,16 @@
         <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC171" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AD171" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF171" t="n">
         <v>0</v>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23114,13 +23114,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -23162,10 +23162,10 @@
         <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD172" t="n">
         <v>0</v>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23246,13 +23246,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -23294,10 +23294,10 @@
         <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC173" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD173" t="n">
         <v>0</v>
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23954,10 +23954,10 @@
         <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD178" t="n">
         <v>0</v>
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -24080,10 +24080,10 @@
         <v>0</v>
       </c>
       <c r="Z179" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
         <v>0</v>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>4.25</v>
+        <v>2.45</v>
       </c>
       <c r="M180" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N180" t="n">
-        <v>1.93</v>
+        <v>3.05</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24302,13 +24302,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -24344,10 +24344,10 @@
         <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB181" t="n">
         <v>0</v>
@@ -24408,12 +24408,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24434,13 +24434,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M182" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N182" t="n">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA182" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB182" t="n">
         <v>0</v>
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="M183" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N183" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24608,10 +24608,10 @@
         <v>0</v>
       </c>
       <c r="Z183" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AA183" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB183" t="n">
         <v>0</v>
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24746,10 +24746,10 @@
         <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC184" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD184" t="n">
         <v>0</v>
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24962,13 +24962,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25004,10 +25004,10 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB186" t="n">
         <v>0</v>
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25354,17 +25354,17 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25400,10 +25400,10 @@
         <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
         <v>0</v>
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25486,7 +25486,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25618,7 +25618,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25928,16 +25928,16 @@
         <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC193" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD193" t="n">
         <v>0</v>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC194" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD194" t="n">
         <v>0</v>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -26124,12 +26124,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -26150,13 +26150,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="M195" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="N195" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -26192,16 +26192,16 @@
         <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB195" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC195" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AD195" t="n">
         <v>0</v>
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26784,12 +26784,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27202,44 +27202,44 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="M203" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N203" t="n">
-        <v>4.52</v>
+        <v>1.95</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S203" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T203" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U203" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V203" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W203" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X203" t="n">
         <v>0</v>
@@ -27248,34 +27248,34 @@
         <v>0</v>
       </c>
       <c r="Z203" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC203" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD203" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH203" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AI203" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27334,44 +27334,44 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="M204" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N204" t="n">
-        <v>1.95</v>
+        <v>4.52</v>
       </c>
       <c r="O204" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P204" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Q204" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T204" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V204" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W204" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X204" t="n">
         <v>0</v>
@@ -27380,34 +27380,34 @@
         <v>0</v>
       </c>
       <c r="Z204" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD204" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF204" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH204" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AI204" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="M206" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N206" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC206" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>

--- a/jogos_2025-08-02.xlsx
+++ b/jogos_2025-08-02.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,14 +1994,14 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.86</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,14 +2390,14 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N15" t="n">
         <v>1.88</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.51</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>3.26</v>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.26</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.41</v>
+        <v>1.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.88</v>
+        <v>3.51</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>3.18</v>
       </c>
       <c r="M20" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.77</v>
+        <v>2.09</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>3.23</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="N21" t="n">
-        <v>3.03</v>
+        <v>1.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.62</v>
+        <v>4.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.23</v>
+        <v>1.64</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,64 +3710,64 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6536,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N55" t="n">
-        <v>2.41</v>
+        <v>1.36</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>8.699999999999999</v>
+        <v>2.69</v>
       </c>
       <c r="M56" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>1.36</v>
+        <v>2.41</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.91</v>
+        <v>4.33</v>
       </c>
       <c r="M58" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="N58" t="n">
-        <v>3.07</v>
+        <v>1.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.82</v>
+        <v>1.73</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N59" t="n">
-        <v>2.32</v>
+        <v>3.47</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,16 +8246,16 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="M60" t="n">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>1.6</v>
+        <v>3.05</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>3.69</v>
       </c>
       <c r="N61" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.73</v>
+        <v>2.82</v>
       </c>
       <c r="M63" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>3.47</v>
+        <v>2.32</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,16 +8774,16 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="M64" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="M65" t="n">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="N65" t="n">
-        <v>2.44</v>
+        <v>3.72</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,16 +9038,16 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,16 +9170,16 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="M67" t="n">
-        <v>3.41</v>
+        <v>3.01</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,16 +9434,16 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,58 +9518,58 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="M69" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="N69" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
         <v>1.57</v>
       </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC69" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>3.59</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.95</v>
+        <v>1.34</v>
       </c>
       <c r="M71" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="N71" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,16 +9830,16 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9968,10 +9968,10 @@
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="M74" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N74" t="n">
-        <v>3.59</v>
+        <v>2.6</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="M75" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N75" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,16 +10358,16 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="M76" t="n">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.9</v>
+        <v>1.39</v>
       </c>
       <c r="M77" t="n">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,16 +10622,16 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="N78" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,16 +10754,16 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="M79" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,16 +10886,16 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="M80" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11237,10 +11237,10 @@
         <v>1.8</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="N82" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="M83" t="n">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="N83" t="n">
-        <v>4.08</v>
+        <v>3.47</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="M84" t="n">
-        <v>4.7</v>
+        <v>3.06</v>
       </c>
       <c r="N84" t="n">
-        <v>8</v>
+        <v>2.68</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,16 +11546,16 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF84" t="n">
         <v>0</v>
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="M86" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="N86" t="n">
-        <v>3.45</v>
+        <v>3.06</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M87" t="n">
-        <v>3.23</v>
+        <v>3.79</v>
       </c>
       <c r="N87" t="n">
-        <v>3.45</v>
+        <v>3.89</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="M89" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N89" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="M90" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N90" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="M91" t="n">
-        <v>3.36</v>
+        <v>2.91</v>
       </c>
       <c r="N91" t="n">
-        <v>3.19</v>
+        <v>2.44</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC92" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N94" t="n">
-        <v>3.01</v>
+        <v>3.47</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="M95" t="n">
-        <v>3.79</v>
+        <v>3.23</v>
       </c>
       <c r="N95" t="n">
-        <v>3.89</v>
+        <v>3.45</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="M96" t="n">
-        <v>3.01</v>
+        <v>3.61</v>
       </c>
       <c r="N96" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="M97" t="n">
-        <v>3.77</v>
+        <v>3.36</v>
       </c>
       <c r="N97" t="n">
-        <v>3.47</v>
+        <v>4.08</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M98" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="N98" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,16 +13394,16 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AD98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.21</v>
+        <v>3.65</v>
       </c>
       <c r="M99" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="M100" t="n">
-        <v>3.61</v>
+        <v>3.9</v>
       </c>
       <c r="N100" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,10 +13658,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M101" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N101" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.65</v>
+        <v>2.04</v>
       </c>
       <c r="M103" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="N103" t="n">
-        <v>1.87</v>
+        <v>3.34</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="AC1